--- a/docs/missioni-bt3.xlsx
+++ b/docs/missioni-bt3.xlsx
@@ -543,6 +543,9 @@
           <t>sì</t>
         </is>
       </c>
+      <c r="L2" t="n">
+        <v>300</v>
+      </c>
       <c r="O2" t="n">
         <v>2</v>
       </c>
@@ -573,6 +576,9 @@
           <t>sì</t>
         </is>
       </c>
+      <c r="L3" t="n">
+        <v>300</v>
+      </c>
       <c r="O3" t="n">
         <v>2</v>
       </c>
@@ -603,6 +609,9 @@
           <t>sì</t>
         </is>
       </c>
+      <c r="L4" t="n">
+        <v>300</v>
+      </c>
       <c r="O4" t="n">
         <v>1</v>
       </c>
@@ -628,6 +637,9 @@
           <t>sì</t>
         </is>
       </c>
+      <c r="L5" t="n">
+        <v>300</v>
+      </c>
       <c r="O5" t="n">
         <v>2</v>
       </c>
@@ -656,6 +668,9 @@
           <t>sì</t>
         </is>
       </c>
+      <c r="L6" t="n">
+        <v>700</v>
+      </c>
       <c r="O6" t="n">
         <v>1</v>
       </c>
@@ -686,6 +701,9 @@
           <t>sì</t>
         </is>
       </c>
+      <c r="L7" t="n">
+        <v>300</v>
+      </c>
       <c r="O7" t="n">
         <v>2</v>
       </c>
@@ -716,6 +734,9 @@
           <t>sì</t>
         </is>
       </c>
+      <c r="L8" t="n">
+        <v>300</v>
+      </c>
       <c r="O8" t="n">
         <v>2</v>
       </c>
@@ -746,6 +767,9 @@
           <t>sì</t>
         </is>
       </c>
+      <c r="L9" t="n">
+        <v>300</v>
+      </c>
       <c r="O9" t="n">
         <v>1</v>
       </c>
@@ -771,6 +795,9 @@
           <t>sì</t>
         </is>
       </c>
+      <c r="L10" t="n">
+        <v>300</v>
+      </c>
       <c r="O10" t="n">
         <v>2</v>
       </c>
@@ -799,6 +826,9 @@
           <t>sì</t>
         </is>
       </c>
+      <c r="L11" t="n">
+        <v>1100</v>
+      </c>
       <c r="O11" t="n">
         <v>1</v>
       </c>
@@ -827,6 +857,9 @@
           <t>sì</t>
         </is>
       </c>
+      <c r="L12" t="n">
+        <v>700</v>
+      </c>
       <c r="O12" t="n">
         <v>1</v>
       </c>
@@ -851,7 +884,7 @@
         <v>2</v>
       </c>
       <c r="L13" t="n">
-        <v>400</v>
+        <v>1200</v>
       </c>
       <c r="O13" t="n">
         <v>2</v>
@@ -877,7 +910,7 @@
         <v>1</v>
       </c>
       <c r="L14" t="n">
-        <v>600</v>
+        <v>1200</v>
       </c>
       <c r="O14" t="n">
         <v>1</v>
@@ -900,7 +933,7 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>300</v>
+        <v>600</v>
       </c>
       <c r="O15" t="n">
         <v>2</v>
@@ -930,6 +963,9 @@
           <t>Son Goten</t>
         </is>
       </c>
+      <c r="L16" t="n">
+        <v>1200</v>
+      </c>
       <c r="O16" t="n">
         <v>2</v>
       </c>
@@ -951,7 +987,7 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>300</v>
+        <v>600</v>
       </c>
       <c r="O17" t="n">
         <v>1</v>
@@ -981,6 +1017,9 @@
           <t>Trunks (bambino)</t>
         </is>
       </c>
+      <c r="L18" t="n">
+        <v>1200</v>
+      </c>
       <c r="O18" t="n">
         <v>1</v>
       </c>
@@ -1017,7 +1056,7 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>800</v>
+        <v>1500</v>
       </c>
       <c r="M19" t="inlineStr">
         <is>
@@ -1059,6 +1098,9 @@
           <t>sì</t>
         </is>
       </c>
+      <c r="L20" t="n">
+        <v>300</v>
+      </c>
       <c r="N20" t="inlineStr">
         <is>
           <t>Metal Cooler</t>
@@ -1099,6 +1141,9 @@
           <t>sì</t>
         </is>
       </c>
+      <c r="L21" t="n">
+        <v>300</v>
+      </c>
       <c r="N21" t="inlineStr">
         <is>
           <t>Freeza (forma finale)</t>
@@ -1134,6 +1179,9 @@
           <t>sì</t>
         </is>
       </c>
+      <c r="L22" t="n">
+        <v>300</v>
+      </c>
       <c r="N22" t="inlineStr">
         <is>
           <t>Cell (perfetto, massima potenza)</t>
@@ -1169,6 +1217,9 @@
           <t>sì</t>
         </is>
       </c>
+      <c r="L23" t="n">
+        <v>300</v>
+      </c>
       <c r="O23" t="n">
         <v>1</v>
       </c>
@@ -1199,6 +1250,9 @@
           <t>sì</t>
         </is>
       </c>
+      <c r="L24" t="n">
+        <v>300</v>
+      </c>
       <c r="O24" t="n">
         <v>1</v>
       </c>
@@ -1229,6 +1283,9 @@
           <t>sì</t>
         </is>
       </c>
+      <c r="L25" t="n">
+        <v>300</v>
+      </c>
       <c r="O25" t="n">
         <v>2</v>
       </c>
@@ -1264,6 +1321,9 @@
           <t>sì</t>
         </is>
       </c>
+      <c r="L26" t="n">
+        <v>300</v>
+      </c>
       <c r="O26" t="n">
         <v>1</v>
       </c>
@@ -1294,6 +1354,9 @@
           <t>sì</t>
         </is>
       </c>
+      <c r="L27" t="n">
+        <v>300</v>
+      </c>
       <c r="O27" t="n">
         <v>1</v>
       </c>
@@ -1329,6 +1392,9 @@
           <t>sì</t>
         </is>
       </c>
+      <c r="L28" t="n">
+        <v>300</v>
+      </c>
       <c r="O28" t="n">
         <v>1</v>
       </c>
@@ -1359,6 +1425,9 @@
           <t>sì</t>
         </is>
       </c>
+      <c r="L29" t="n">
+        <v>300</v>
+      </c>
       <c r="O29" t="n">
         <v>1</v>
       </c>
@@ -1384,6 +1453,9 @@
           <t>sì</t>
         </is>
       </c>
+      <c r="L30" t="n">
+        <v>300</v>
+      </c>
       <c r="O30" t="n">
         <v>1</v>
       </c>
@@ -1419,6 +1491,9 @@
           <t>sì</t>
         </is>
       </c>
+      <c r="L31" t="n">
+        <v>300</v>
+      </c>
       <c r="O31" t="n">
         <v>1</v>
       </c>
@@ -1449,6 +1524,9 @@
           <t>sì</t>
         </is>
       </c>
+      <c r="L32" t="n">
+        <v>300</v>
+      </c>
       <c r="O32" t="n">
         <v>1</v>
       </c>
@@ -1479,6 +1557,9 @@
           <t>sì</t>
         </is>
       </c>
+      <c r="L33" t="n">
+        <v>300</v>
+      </c>
       <c r="O33" t="n">
         <v>1</v>
       </c>
@@ -1509,6 +1590,9 @@
           <t>sì</t>
         </is>
       </c>
+      <c r="L34" t="n">
+        <v>300</v>
+      </c>
       <c r="O34" t="n">
         <v>1</v>
       </c>
@@ -1539,6 +1623,9 @@
           <t>sì</t>
         </is>
       </c>
+      <c r="L35" t="n">
+        <v>300</v>
+      </c>
       <c r="O35" t="n">
         <v>1</v>
       </c>
@@ -1569,6 +1656,9 @@
           <t>sì</t>
         </is>
       </c>
+      <c r="L36" t="n">
+        <v>300</v>
+      </c>
       <c r="O36" t="n">
         <v>1</v>
       </c>
@@ -1604,6 +1694,9 @@
           <t>sì</t>
         </is>
       </c>
+      <c r="L37" t="n">
+        <v>300</v>
+      </c>
       <c r="O37" t="n">
         <v>1</v>
       </c>
@@ -1644,6 +1737,9 @@
           <t>sì</t>
         </is>
       </c>
+      <c r="L38" t="n">
+        <v>300</v>
+      </c>
       <c r="O38" t="n">
         <v>1</v>
       </c>
@@ -1674,6 +1770,9 @@
           <t>sì</t>
         </is>
       </c>
+      <c r="L39" t="n">
+        <v>300</v>
+      </c>
       <c r="O39" t="n">
         <v>1</v>
       </c>
@@ -1704,6 +1803,9 @@
           <t>sì</t>
         </is>
       </c>
+      <c r="L40" t="n">
+        <v>300</v>
+      </c>
       <c r="O40" t="n">
         <v>1</v>
       </c>
@@ -1734,6 +1836,9 @@
           <t>sì</t>
         </is>
       </c>
+      <c r="L41" t="n">
+        <v>300</v>
+      </c>
       <c r="O41" t="n">
         <v>1</v>
       </c>
@@ -1764,6 +1869,9 @@
           <t>sì</t>
         </is>
       </c>
+      <c r="L42" t="n">
+        <v>300</v>
+      </c>
       <c r="O42" t="n">
         <v>1</v>
       </c>
@@ -1794,6 +1902,9 @@
           <t>sì</t>
         </is>
       </c>
+      <c r="L43" t="n">
+        <v>300</v>
+      </c>
       <c r="O43" t="n">
         <v>1</v>
       </c>
@@ -1822,6 +1933,9 @@
           <t>sì</t>
         </is>
       </c>
+      <c r="L44" t="n">
+        <v>700</v>
+      </c>
       <c r="O44" t="n">
         <v>1</v>
       </c>
@@ -1852,6 +1966,9 @@
           <t>sì</t>
         </is>
       </c>
+      <c r="L45" t="n">
+        <v>300</v>
+      </c>
       <c r="O45" t="n">
         <v>1</v>
       </c>
@@ -1882,6 +1999,9 @@
           <t>sì</t>
         </is>
       </c>
+      <c r="L46" t="n">
+        <v>300</v>
+      </c>
       <c r="O46" t="n">
         <v>1</v>
       </c>
@@ -1912,6 +2032,9 @@
           <t>sì</t>
         </is>
       </c>
+      <c r="L47" t="n">
+        <v>300</v>
+      </c>
       <c r="O47" t="n">
         <v>1</v>
       </c>
@@ -1947,6 +2070,9 @@
           <t>sì</t>
         </is>
       </c>
+      <c r="L48" t="n">
+        <v>300</v>
+      </c>
       <c r="O48" t="n">
         <v>1</v>
       </c>
@@ -1977,6 +2103,9 @@
           <t>sì</t>
         </is>
       </c>
+      <c r="L49" t="n">
+        <v>300</v>
+      </c>
       <c r="O49" t="n">
         <v>1</v>
       </c>
@@ -2007,6 +2136,9 @@
           <t>sì</t>
         </is>
       </c>
+      <c r="L50" t="n">
+        <v>300</v>
+      </c>
       <c r="O50" t="n">
         <v>1</v>
       </c>
@@ -2047,6 +2179,9 @@
           <t>sì</t>
         </is>
       </c>
+      <c r="L51" t="n">
+        <v>300</v>
+      </c>
       <c r="O51" t="n">
         <v>1</v>
       </c>
@@ -2077,6 +2212,9 @@
           <t>sì</t>
         </is>
       </c>
+      <c r="L52" t="n">
+        <v>300</v>
+      </c>
       <c r="O52" t="n">
         <v>1</v>
       </c>
@@ -2105,6 +2243,9 @@
           <t>sì</t>
         </is>
       </c>
+      <c r="L53" t="n">
+        <v>700</v>
+      </c>
       <c r="O53" t="n">
         <v>1</v>
       </c>
@@ -2145,6 +2286,9 @@
           <t>sì</t>
         </is>
       </c>
+      <c r="L54" t="n">
+        <v>300</v>
+      </c>
       <c r="O54" t="n">
         <v>1</v>
       </c>
@@ -2185,6 +2329,9 @@
           <t>sì</t>
         </is>
       </c>
+      <c r="L55" t="n">
+        <v>300</v>
+      </c>
       <c r="O55" t="n">
         <v>1</v>
       </c>
@@ -2215,6 +2362,9 @@
           <t>sì</t>
         </is>
       </c>
+      <c r="L56" t="n">
+        <v>300</v>
+      </c>
       <c r="O56" t="n">
         <v>1</v>
       </c>
@@ -2245,6 +2395,9 @@
           <t>sì</t>
         </is>
       </c>
+      <c r="L57" t="n">
+        <v>300</v>
+      </c>
       <c r="O57" t="n">
         <v>1</v>
       </c>
@@ -2275,6 +2428,9 @@
           <t>sì</t>
         </is>
       </c>
+      <c r="L58" t="n">
+        <v>300</v>
+      </c>
       <c r="O58" t="n">
         <v>1</v>
       </c>
@@ -2310,6 +2466,9 @@
           <t>sì</t>
         </is>
       </c>
+      <c r="L59" t="n">
+        <v>300</v>
+      </c>
       <c r="O59" t="n">
         <v>1</v>
       </c>
@@ -2340,6 +2499,9 @@
           <t>sì</t>
         </is>
       </c>
+      <c r="L60" t="n">
+        <v>300</v>
+      </c>
       <c r="O60" t="n">
         <v>1</v>
       </c>
@@ -2370,6 +2532,9 @@
           <t>sì</t>
         </is>
       </c>
+      <c r="L61" t="n">
+        <v>300</v>
+      </c>
       <c r="O61" t="n">
         <v>1</v>
       </c>
@@ -2400,6 +2565,9 @@
           <t>sì</t>
         </is>
       </c>
+      <c r="L62" t="n">
+        <v>300</v>
+      </c>
       <c r="O62" t="n">
         <v>1</v>
       </c>
@@ -2430,6 +2598,9 @@
           <t>sì</t>
         </is>
       </c>
+      <c r="L63" t="n">
+        <v>300</v>
+      </c>
       <c r="O63" t="n">
         <v>1</v>
       </c>
@@ -2460,6 +2631,9 @@
           <t>sì</t>
         </is>
       </c>
+      <c r="L64" t="n">
+        <v>300</v>
+      </c>
       <c r="O64" t="n">
         <v>1</v>
       </c>
@@ -2488,6 +2662,9 @@
           <t>sì</t>
         </is>
       </c>
+      <c r="L65" t="n">
+        <v>700</v>
+      </c>
       <c r="O65" t="n">
         <v>1</v>
       </c>
@@ -2518,6 +2695,9 @@
           <t>sì</t>
         </is>
       </c>
+      <c r="L66" t="n">
+        <v>300</v>
+      </c>
       <c r="O66" t="n">
         <v>1</v>
       </c>
@@ -2548,6 +2728,9 @@
           <t>sì</t>
         </is>
       </c>
+      <c r="L67" t="n">
+        <v>300</v>
+      </c>
       <c r="O67" t="n">
         <v>1</v>
       </c>
@@ -2576,6 +2759,9 @@
           <t>sì</t>
         </is>
       </c>
+      <c r="L68" t="n">
+        <v>700</v>
+      </c>
       <c r="O68" t="n">
         <v>1</v>
       </c>
@@ -2606,6 +2792,9 @@
           <t>sì</t>
         </is>
       </c>
+      <c r="L69" t="n">
+        <v>300</v>
+      </c>
       <c r="O69" t="n">
         <v>1</v>
       </c>
@@ -2636,6 +2825,9 @@
           <t>sì</t>
         </is>
       </c>
+      <c r="L70" t="n">
+        <v>300</v>
+      </c>
       <c r="O70" t="n">
         <v>1</v>
       </c>
@@ -2666,6 +2858,9 @@
           <t>sì</t>
         </is>
       </c>
+      <c r="L71" t="n">
+        <v>300</v>
+      </c>
       <c r="O71" t="n">
         <v>1</v>
       </c>
@@ -2696,6 +2891,9 @@
           <t>sì</t>
         </is>
       </c>
+      <c r="L72" t="n">
+        <v>300</v>
+      </c>
       <c r="O72" t="n">
         <v>1</v>
       </c>
@@ -2726,6 +2924,9 @@
           <t>sì</t>
         </is>
       </c>
+      <c r="L73" t="n">
+        <v>300</v>
+      </c>
       <c r="O73" t="n">
         <v>1</v>
       </c>
@@ -2756,6 +2957,9 @@
           <t>sì</t>
         </is>
       </c>
+      <c r="L74" t="n">
+        <v>300</v>
+      </c>
       <c r="O74" t="n">
         <v>1</v>
       </c>
@@ -2791,6 +2995,9 @@
           <t>sì</t>
         </is>
       </c>
+      <c r="L75" t="n">
+        <v>300</v>
+      </c>
       <c r="O75" t="n">
         <v>1</v>
       </c>
@@ -2821,6 +3028,9 @@
           <t>sì</t>
         </is>
       </c>
+      <c r="L76" t="n">
+        <v>300</v>
+      </c>
       <c r="O76" t="n">
         <v>1</v>
       </c>
@@ -2851,6 +3061,9 @@
           <t>sì</t>
         </is>
       </c>
+      <c r="L77" t="n">
+        <v>300</v>
+      </c>
       <c r="O77" t="n">
         <v>1</v>
       </c>
@@ -2881,6 +3094,9 @@
           <t>sì</t>
         </is>
       </c>
+      <c r="L78" t="n">
+        <v>300</v>
+      </c>
       <c r="O78" t="n">
         <v>1</v>
       </c>
@@ -2921,6 +3137,9 @@
           <t>sì</t>
         </is>
       </c>
+      <c r="L79" t="n">
+        <v>300</v>
+      </c>
       <c r="O79" t="n">
         <v>1</v>
       </c>
@@ -2951,6 +3170,9 @@
           <t>sì</t>
         </is>
       </c>
+      <c r="L80" t="n">
+        <v>300</v>
+      </c>
       <c r="O80" t="n">
         <v>1</v>
       </c>
@@ -2981,6 +3203,9 @@
           <t>sì</t>
         </is>
       </c>
+      <c r="L81" t="n">
+        <v>300</v>
+      </c>
       <c r="O81" t="n">
         <v>1</v>
       </c>
@@ -3011,6 +3236,9 @@
           <t>sì</t>
         </is>
       </c>
+      <c r="L82" t="n">
+        <v>300</v>
+      </c>
       <c r="O82" t="n">
         <v>1</v>
       </c>
@@ -3041,6 +3269,9 @@
           <t>sì</t>
         </is>
       </c>
+      <c r="L83" t="n">
+        <v>300</v>
+      </c>
       <c r="O83" t="n">
         <v>1</v>
       </c>
@@ -3071,6 +3302,9 @@
           <t>sì</t>
         </is>
       </c>
+      <c r="L84" t="n">
+        <v>300</v>
+      </c>
       <c r="O84" t="n">
         <v>1</v>
       </c>
@@ -3101,6 +3335,9 @@
           <t>sì</t>
         </is>
       </c>
+      <c r="L85" t="n">
+        <v>300</v>
+      </c>
       <c r="O85" t="n">
         <v>1</v>
       </c>
@@ -3131,6 +3368,9 @@
           <t>sì</t>
         </is>
       </c>
+      <c r="L86" t="n">
+        <v>300</v>
+      </c>
       <c r="O86" t="n">
         <v>1</v>
       </c>
@@ -3161,6 +3401,9 @@
           <t>sì</t>
         </is>
       </c>
+      <c r="L87" t="n">
+        <v>300</v>
+      </c>
       <c r="O87" t="n">
         <v>1</v>
       </c>
@@ -3191,6 +3434,9 @@
           <t>sì</t>
         </is>
       </c>
+      <c r="L88" t="n">
+        <v>300</v>
+      </c>
       <c r="O88" t="n">
         <v>1</v>
       </c>
@@ -3221,6 +3467,9 @@
           <t>sì</t>
         </is>
       </c>
+      <c r="L89" t="n">
+        <v>300</v>
+      </c>
       <c r="O89" t="n">
         <v>1</v>
       </c>
@@ -3251,6 +3500,9 @@
           <t>sì</t>
         </is>
       </c>
+      <c r="L90" t="n">
+        <v>300</v>
+      </c>
       <c r="O90" t="n">
         <v>1</v>
       </c>
@@ -3281,6 +3533,9 @@
           <t>sì</t>
         </is>
       </c>
+      <c r="L91" t="n">
+        <v>300</v>
+      </c>
       <c r="O91" t="n">
         <v>1</v>
       </c>
@@ -3311,6 +3566,9 @@
           <t>sì</t>
         </is>
       </c>
+      <c r="L92" t="n">
+        <v>300</v>
+      </c>
       <c r="O92" t="n">
         <v>1</v>
       </c>
@@ -3341,6 +3599,9 @@
           <t>sì</t>
         </is>
       </c>
+      <c r="L93" t="n">
+        <v>300</v>
+      </c>
       <c r="O93" t="n">
         <v>1</v>
       </c>
@@ -3371,6 +3632,9 @@
           <t>sì</t>
         </is>
       </c>
+      <c r="L94" t="n">
+        <v>300</v>
+      </c>
       <c r="O94" t="n">
         <v>1</v>
       </c>
@@ -3406,6 +3670,9 @@
           <t>sì</t>
         </is>
       </c>
+      <c r="L95" t="n">
+        <v>300</v>
+      </c>
       <c r="O95" t="n">
         <v>1</v>
       </c>
@@ -3436,6 +3703,9 @@
           <t>sì</t>
         </is>
       </c>
+      <c r="L96" t="n">
+        <v>300</v>
+      </c>
       <c r="O96" t="n">
         <v>1</v>
       </c>
@@ -3471,6 +3741,9 @@
           <t>sì</t>
         </is>
       </c>
+      <c r="L97" t="n">
+        <v>300</v>
+      </c>
       <c r="O97" t="n">
         <v>1</v>
       </c>
@@ -3501,6 +3774,9 @@
           <t>sì</t>
         </is>
       </c>
+      <c r="L98" t="n">
+        <v>300</v>
+      </c>
       <c r="O98" t="n">
         <v>1</v>
       </c>
@@ -3531,6 +3807,9 @@
           <t>sì</t>
         </is>
       </c>
+      <c r="L99" t="n">
+        <v>300</v>
+      </c>
       <c r="O99" t="n">
         <v>1</v>
       </c>
@@ -3561,6 +3840,9 @@
           <t>sì</t>
         </is>
       </c>
+      <c r="L100" t="n">
+        <v>300</v>
+      </c>
       <c r="O100" t="n">
         <v>1</v>
       </c>
@@ -3591,6 +3873,9 @@
           <t>sì</t>
         </is>
       </c>
+      <c r="L101" t="n">
+        <v>300</v>
+      </c>
       <c r="O101" t="n">
         <v>1</v>
       </c>
@@ -3626,6 +3911,9 @@
           <t>sì</t>
         </is>
       </c>
+      <c r="L102" t="n">
+        <v>300</v>
+      </c>
       <c r="O102" t="n">
         <v>1</v>
       </c>
@@ -3656,6 +3944,9 @@
           <t>sì</t>
         </is>
       </c>
+      <c r="L103" t="n">
+        <v>300</v>
+      </c>
       <c r="O103" t="n">
         <v>1</v>
       </c>
@@ -3686,6 +3977,9 @@
           <t>sì</t>
         </is>
       </c>
+      <c r="L104" t="n">
+        <v>300</v>
+      </c>
       <c r="O104" t="n">
         <v>1</v>
       </c>
@@ -3721,6 +4015,9 @@
           <t>sì</t>
         </is>
       </c>
+      <c r="L105" t="n">
+        <v>300</v>
+      </c>
       <c r="O105" t="n">
         <v>1</v>
       </c>
@@ -3751,6 +4048,9 @@
           <t>sì</t>
         </is>
       </c>
+      <c r="L106" t="n">
+        <v>300</v>
+      </c>
       <c r="O106" t="n">
         <v>1</v>
       </c>
@@ -3781,6 +4081,9 @@
           <t>sì</t>
         </is>
       </c>
+      <c r="L107" t="n">
+        <v>300</v>
+      </c>
       <c r="O107" t="n">
         <v>1</v>
       </c>
@@ -3806,6 +4109,9 @@
           <t>sì</t>
         </is>
       </c>
+      <c r="L108" t="n">
+        <v>300</v>
+      </c>
       <c r="O108" t="n">
         <v>1</v>
       </c>
@@ -3831,6 +4137,9 @@
           <t>sì</t>
         </is>
       </c>
+      <c r="L109" t="n">
+        <v>300</v>
+      </c>
       <c r="O109" t="n">
         <v>1</v>
       </c>
@@ -3866,6 +4175,9 @@
           <t>sì</t>
         </is>
       </c>
+      <c r="L110" t="n">
+        <v>300</v>
+      </c>
       <c r="O110" t="n">
         <v>1</v>
       </c>
@@ -3896,6 +4208,9 @@
           <t>sì</t>
         </is>
       </c>
+      <c r="L111" t="n">
+        <v>300</v>
+      </c>
       <c r="O111" t="n">
         <v>1</v>
       </c>
@@ -3931,6 +4246,9 @@
           <t>sì</t>
         </is>
       </c>
+      <c r="L112" t="n">
+        <v>300</v>
+      </c>
       <c r="O112" t="n">
         <v>1</v>
       </c>
@@ -3961,6 +4279,9 @@
           <t>sì</t>
         </is>
       </c>
+      <c r="L113" t="n">
+        <v>300</v>
+      </c>
       <c r="O113" t="n">
         <v>1</v>
       </c>
@@ -3991,6 +4312,9 @@
           <t>sì</t>
         </is>
       </c>
+      <c r="L114" t="n">
+        <v>300</v>
+      </c>
       <c r="O114" t="n">
         <v>1</v>
       </c>
@@ -4021,6 +4345,9 @@
           <t>sì</t>
         </is>
       </c>
+      <c r="L115" t="n">
+        <v>300</v>
+      </c>
       <c r="O115" t="n">
         <v>1</v>
       </c>
@@ -4051,6 +4378,9 @@
           <t>sì</t>
         </is>
       </c>
+      <c r="L116" t="n">
+        <v>300</v>
+      </c>
       <c r="O116" t="n">
         <v>1</v>
       </c>
@@ -4081,6 +4411,9 @@
           <t>sì</t>
         </is>
       </c>
+      <c r="L117" t="n">
+        <v>300</v>
+      </c>
       <c r="O117" t="n">
         <v>1</v>
       </c>
@@ -4111,6 +4444,9 @@
           <t>sì</t>
         </is>
       </c>
+      <c r="L118" t="n">
+        <v>300</v>
+      </c>
       <c r="O118" t="n">
         <v>1</v>
       </c>
@@ -4146,6 +4482,9 @@
           <t>sì</t>
         </is>
       </c>
+      <c r="L119" t="n">
+        <v>300</v>
+      </c>
       <c r="O119" t="n">
         <v>1</v>
       </c>
@@ -4176,6 +4515,9 @@
           <t>sì</t>
         </is>
       </c>
+      <c r="L120" t="n">
+        <v>300</v>
+      </c>
       <c r="O120" t="n">
         <v>1</v>
       </c>
@@ -4211,6 +4553,9 @@
           <t>sì</t>
         </is>
       </c>
+      <c r="L121" t="n">
+        <v>300</v>
+      </c>
       <c r="O121" t="n">
         <v>1</v>
       </c>
@@ -4241,6 +4586,9 @@
           <t>sì</t>
         </is>
       </c>
+      <c r="L122" t="n">
+        <v>300</v>
+      </c>
       <c r="O122" t="n">
         <v>1</v>
       </c>
@@ -4271,6 +4619,9 @@
           <t>sì</t>
         </is>
       </c>
+      <c r="L123" t="n">
+        <v>300</v>
+      </c>
       <c r="O123" t="n">
         <v>1</v>
       </c>
@@ -4301,6 +4652,9 @@
           <t>sì</t>
         </is>
       </c>
+      <c r="L124" t="n">
+        <v>300</v>
+      </c>
       <c r="O124" t="n">
         <v>1</v>
       </c>
@@ -4331,6 +4685,9 @@
           <t>sì</t>
         </is>
       </c>
+      <c r="L125" t="n">
+        <v>300</v>
+      </c>
       <c r="O125" t="n">
         <v>1</v>
       </c>
@@ -4361,6 +4718,9 @@
           <t>sì</t>
         </is>
       </c>
+      <c r="L126" t="n">
+        <v>300</v>
+      </c>
       <c r="O126" t="n">
         <v>1</v>
       </c>
@@ -4391,6 +4751,9 @@
           <t>sì</t>
         </is>
       </c>
+      <c r="L127" t="n">
+        <v>300</v>
+      </c>
       <c r="O127" t="n">
         <v>1</v>
       </c>
@@ -4421,6 +4784,9 @@
           <t>sì</t>
         </is>
       </c>
+      <c r="L128" t="n">
+        <v>300</v>
+      </c>
       <c r="O128" t="n">
         <v>1</v>
       </c>
@@ -4450,6 +4816,9 @@
         <is>
           <t>sì</t>
         </is>
+      </c>
+      <c r="L129" t="n">
+        <v>300</v>
       </c>
       <c r="O129" t="n">
         <v>1</v>

--- a/docs/missioni-bt3.xlsx
+++ b/docs/missioni-bt3.xlsx
@@ -544,7 +544,7 @@
         </is>
       </c>
       <c r="L2" t="n">
-        <v>300</v>
+        <v>400</v>
       </c>
       <c r="O2" t="n">
         <v>2</v>
@@ -577,7 +577,7 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>300</v>
+        <v>400</v>
       </c>
       <c r="O3" t="n">
         <v>2</v>
@@ -610,7 +610,7 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>300</v>
+        <v>400</v>
       </c>
       <c r="O4" t="n">
         <v>1</v>
@@ -638,7 +638,7 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>300</v>
+        <v>400</v>
       </c>
       <c r="O5" t="n">
         <v>2</v>
@@ -669,7 +669,7 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>700</v>
+        <v>900</v>
       </c>
       <c r="O6" t="n">
         <v>1</v>
@@ -702,7 +702,7 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>300</v>
+        <v>400</v>
       </c>
       <c r="O7" t="n">
         <v>2</v>
@@ -735,7 +735,7 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>300</v>
+        <v>400</v>
       </c>
       <c r="O8" t="n">
         <v>2</v>
@@ -768,7 +768,7 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>300</v>
+        <v>400</v>
       </c>
       <c r="O9" t="n">
         <v>1</v>
@@ -796,7 +796,7 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>300</v>
+        <v>400</v>
       </c>
       <c r="O10" t="n">
         <v>2</v>
@@ -827,7 +827,7 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>1100</v>
+        <v>1400</v>
       </c>
       <c r="O11" t="n">
         <v>1</v>
@@ -858,7 +858,7 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>700</v>
+        <v>900</v>
       </c>
       <c r="O12" t="n">
         <v>1</v>
@@ -884,7 +884,7 @@
         <v>2</v>
       </c>
       <c r="L13" t="n">
-        <v>1200</v>
+        <v>1500</v>
       </c>
       <c r="O13" t="n">
         <v>2</v>
@@ -910,7 +910,7 @@
         <v>1</v>
       </c>
       <c r="L14" t="n">
-        <v>1200</v>
+        <v>1500</v>
       </c>
       <c r="O14" t="n">
         <v>1</v>
@@ -933,7 +933,7 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>600</v>
+        <v>800</v>
       </c>
       <c r="O15" t="n">
         <v>2</v>
@@ -964,7 +964,7 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>1200</v>
+        <v>1500</v>
       </c>
       <c r="O16" t="n">
         <v>2</v>
@@ -987,7 +987,7 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>600</v>
+        <v>800</v>
       </c>
       <c r="O17" t="n">
         <v>1</v>
@@ -1018,7 +1018,7 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>1200</v>
+        <v>1500</v>
       </c>
       <c r="O18" t="n">
         <v>1</v>
@@ -1056,7 +1056,7 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>1500</v>
+        <v>2000</v>
       </c>
       <c r="M19" t="inlineStr">
         <is>
@@ -1099,7 +1099,7 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>300</v>
+        <v>400</v>
       </c>
       <c r="N20" t="inlineStr">
         <is>
@@ -1142,7 +1142,7 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>300</v>
+        <v>400</v>
       </c>
       <c r="N21" t="inlineStr">
         <is>
@@ -1180,7 +1180,7 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>300</v>
+        <v>400</v>
       </c>
       <c r="N22" t="inlineStr">
         <is>
@@ -1218,7 +1218,7 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>300</v>
+        <v>400</v>
       </c>
       <c r="O23" t="n">
         <v>1</v>
@@ -1251,7 +1251,7 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>300</v>
+        <v>400</v>
       </c>
       <c r="O24" t="n">
         <v>1</v>
@@ -1284,7 +1284,7 @@
         </is>
       </c>
       <c r="L25" t="n">
-        <v>300</v>
+        <v>400</v>
       </c>
       <c r="O25" t="n">
         <v>2</v>
@@ -1322,7 +1322,7 @@
         </is>
       </c>
       <c r="L26" t="n">
-        <v>300</v>
+        <v>400</v>
       </c>
       <c r="O26" t="n">
         <v>1</v>
@@ -1355,7 +1355,7 @@
         </is>
       </c>
       <c r="L27" t="n">
-        <v>300</v>
+        <v>400</v>
       </c>
       <c r="O27" t="n">
         <v>1</v>
@@ -1393,7 +1393,7 @@
         </is>
       </c>
       <c r="L28" t="n">
-        <v>300</v>
+        <v>400</v>
       </c>
       <c r="O28" t="n">
         <v>1</v>
@@ -1426,7 +1426,7 @@
         </is>
       </c>
       <c r="L29" t="n">
-        <v>300</v>
+        <v>400</v>
       </c>
       <c r="O29" t="n">
         <v>1</v>
@@ -1454,7 +1454,7 @@
         </is>
       </c>
       <c r="L30" t="n">
-        <v>300</v>
+        <v>400</v>
       </c>
       <c r="O30" t="n">
         <v>1</v>
@@ -1492,7 +1492,7 @@
         </is>
       </c>
       <c r="L31" t="n">
-        <v>300</v>
+        <v>400</v>
       </c>
       <c r="O31" t="n">
         <v>1</v>
@@ -1525,7 +1525,7 @@
         </is>
       </c>
       <c r="L32" t="n">
-        <v>300</v>
+        <v>400</v>
       </c>
       <c r="O32" t="n">
         <v>1</v>
@@ -1558,7 +1558,7 @@
         </is>
       </c>
       <c r="L33" t="n">
-        <v>300</v>
+        <v>400</v>
       </c>
       <c r="O33" t="n">
         <v>1</v>
@@ -1591,7 +1591,7 @@
         </is>
       </c>
       <c r="L34" t="n">
-        <v>300</v>
+        <v>400</v>
       </c>
       <c r="O34" t="n">
         <v>1</v>
@@ -1624,7 +1624,7 @@
         </is>
       </c>
       <c r="L35" t="n">
-        <v>300</v>
+        <v>400</v>
       </c>
       <c r="O35" t="n">
         <v>1</v>
@@ -1657,7 +1657,7 @@
         </is>
       </c>
       <c r="L36" t="n">
-        <v>300</v>
+        <v>400</v>
       </c>
       <c r="O36" t="n">
         <v>1</v>
@@ -1695,7 +1695,7 @@
         </is>
       </c>
       <c r="L37" t="n">
-        <v>300</v>
+        <v>400</v>
       </c>
       <c r="O37" t="n">
         <v>1</v>
@@ -1738,7 +1738,7 @@
         </is>
       </c>
       <c r="L38" t="n">
-        <v>300</v>
+        <v>400</v>
       </c>
       <c r="O38" t="n">
         <v>1</v>
@@ -1771,7 +1771,7 @@
         </is>
       </c>
       <c r="L39" t="n">
-        <v>300</v>
+        <v>400</v>
       </c>
       <c r="O39" t="n">
         <v>1</v>
@@ -1804,7 +1804,7 @@
         </is>
       </c>
       <c r="L40" t="n">
-        <v>300</v>
+        <v>400</v>
       </c>
       <c r="O40" t="n">
         <v>1</v>
@@ -1837,7 +1837,7 @@
         </is>
       </c>
       <c r="L41" t="n">
-        <v>300</v>
+        <v>400</v>
       </c>
       <c r="O41" t="n">
         <v>1</v>
@@ -1870,7 +1870,7 @@
         </is>
       </c>
       <c r="L42" t="n">
-        <v>300</v>
+        <v>400</v>
       </c>
       <c r="O42" t="n">
         <v>1</v>
@@ -1903,7 +1903,7 @@
         </is>
       </c>
       <c r="L43" t="n">
-        <v>300</v>
+        <v>400</v>
       </c>
       <c r="O43" t="n">
         <v>1</v>
@@ -1934,7 +1934,7 @@
         </is>
       </c>
       <c r="L44" t="n">
-        <v>700</v>
+        <v>900</v>
       </c>
       <c r="O44" t="n">
         <v>1</v>
@@ -1967,7 +1967,7 @@
         </is>
       </c>
       <c r="L45" t="n">
-        <v>300</v>
+        <v>400</v>
       </c>
       <c r="O45" t="n">
         <v>1</v>
@@ -2000,7 +2000,7 @@
         </is>
       </c>
       <c r="L46" t="n">
-        <v>300</v>
+        <v>400</v>
       </c>
       <c r="O46" t="n">
         <v>1</v>
@@ -2033,7 +2033,7 @@
         </is>
       </c>
       <c r="L47" t="n">
-        <v>300</v>
+        <v>400</v>
       </c>
       <c r="O47" t="n">
         <v>1</v>
@@ -2071,7 +2071,7 @@
         </is>
       </c>
       <c r="L48" t="n">
-        <v>300</v>
+        <v>400</v>
       </c>
       <c r="O48" t="n">
         <v>1</v>
@@ -2104,7 +2104,7 @@
         </is>
       </c>
       <c r="L49" t="n">
-        <v>300</v>
+        <v>400</v>
       </c>
       <c r="O49" t="n">
         <v>1</v>
@@ -2137,7 +2137,7 @@
         </is>
       </c>
       <c r="L50" t="n">
-        <v>300</v>
+        <v>400</v>
       </c>
       <c r="O50" t="n">
         <v>1</v>
@@ -2180,7 +2180,7 @@
         </is>
       </c>
       <c r="L51" t="n">
-        <v>300</v>
+        <v>400</v>
       </c>
       <c r="O51" t="n">
         <v>1</v>
@@ -2213,7 +2213,7 @@
         </is>
       </c>
       <c r="L52" t="n">
-        <v>300</v>
+        <v>400</v>
       </c>
       <c r="O52" t="n">
         <v>1</v>
@@ -2244,7 +2244,7 @@
         </is>
       </c>
       <c r="L53" t="n">
-        <v>700</v>
+        <v>900</v>
       </c>
       <c r="O53" t="n">
         <v>1</v>
@@ -2287,7 +2287,7 @@
         </is>
       </c>
       <c r="L54" t="n">
-        <v>300</v>
+        <v>400</v>
       </c>
       <c r="O54" t="n">
         <v>1</v>
@@ -2330,7 +2330,7 @@
         </is>
       </c>
       <c r="L55" t="n">
-        <v>300</v>
+        <v>400</v>
       </c>
       <c r="O55" t="n">
         <v>1</v>
@@ -2363,7 +2363,7 @@
         </is>
       </c>
       <c r="L56" t="n">
-        <v>300</v>
+        <v>400</v>
       </c>
       <c r="O56" t="n">
         <v>1</v>
@@ -2396,7 +2396,7 @@
         </is>
       </c>
       <c r="L57" t="n">
-        <v>300</v>
+        <v>400</v>
       </c>
       <c r="O57" t="n">
         <v>1</v>
@@ -2429,7 +2429,7 @@
         </is>
       </c>
       <c r="L58" t="n">
-        <v>300</v>
+        <v>400</v>
       </c>
       <c r="O58" t="n">
         <v>1</v>
@@ -2467,7 +2467,7 @@
         </is>
       </c>
       <c r="L59" t="n">
-        <v>300</v>
+        <v>400</v>
       </c>
       <c r="O59" t="n">
         <v>1</v>
@@ -2500,7 +2500,7 @@
         </is>
       </c>
       <c r="L60" t="n">
-        <v>300</v>
+        <v>400</v>
       </c>
       <c r="O60" t="n">
         <v>1</v>
@@ -2533,7 +2533,7 @@
         </is>
       </c>
       <c r="L61" t="n">
-        <v>300</v>
+        <v>400</v>
       </c>
       <c r="O61" t="n">
         <v>1</v>
@@ -2566,7 +2566,7 @@
         </is>
       </c>
       <c r="L62" t="n">
-        <v>300</v>
+        <v>400</v>
       </c>
       <c r="O62" t="n">
         <v>1</v>
@@ -2599,7 +2599,7 @@
         </is>
       </c>
       <c r="L63" t="n">
-        <v>300</v>
+        <v>400</v>
       </c>
       <c r="O63" t="n">
         <v>1</v>
@@ -2632,7 +2632,7 @@
         </is>
       </c>
       <c r="L64" t="n">
-        <v>300</v>
+        <v>400</v>
       </c>
       <c r="O64" t="n">
         <v>1</v>
@@ -2663,7 +2663,7 @@
         </is>
       </c>
       <c r="L65" t="n">
-        <v>700</v>
+        <v>900</v>
       </c>
       <c r="O65" t="n">
         <v>1</v>
@@ -2696,7 +2696,7 @@
         </is>
       </c>
       <c r="L66" t="n">
-        <v>300</v>
+        <v>400</v>
       </c>
       <c r="O66" t="n">
         <v>1</v>
@@ -2729,7 +2729,7 @@
         </is>
       </c>
       <c r="L67" t="n">
-        <v>300</v>
+        <v>400</v>
       </c>
       <c r="O67" t="n">
         <v>1</v>
@@ -2760,7 +2760,7 @@
         </is>
       </c>
       <c r="L68" t="n">
-        <v>700</v>
+        <v>900</v>
       </c>
       <c r="O68" t="n">
         <v>1</v>
@@ -2793,7 +2793,7 @@
         </is>
       </c>
       <c r="L69" t="n">
-        <v>300</v>
+        <v>400</v>
       </c>
       <c r="O69" t="n">
         <v>1</v>
@@ -2826,7 +2826,7 @@
         </is>
       </c>
       <c r="L70" t="n">
-        <v>300</v>
+        <v>400</v>
       </c>
       <c r="O70" t="n">
         <v>1</v>
@@ -2859,7 +2859,7 @@
         </is>
       </c>
       <c r="L71" t="n">
-        <v>300</v>
+        <v>400</v>
       </c>
       <c r="O71" t="n">
         <v>1</v>
@@ -2892,7 +2892,7 @@
         </is>
       </c>
       <c r="L72" t="n">
-        <v>300</v>
+        <v>400</v>
       </c>
       <c r="O72" t="n">
         <v>1</v>
@@ -2925,7 +2925,7 @@
         </is>
       </c>
       <c r="L73" t="n">
-        <v>300</v>
+        <v>400</v>
       </c>
       <c r="O73" t="n">
         <v>1</v>
@@ -2958,7 +2958,7 @@
         </is>
       </c>
       <c r="L74" t="n">
-        <v>300</v>
+        <v>400</v>
       </c>
       <c r="O74" t="n">
         <v>1</v>
@@ -2996,7 +2996,7 @@
         </is>
       </c>
       <c r="L75" t="n">
-        <v>300</v>
+        <v>400</v>
       </c>
       <c r="O75" t="n">
         <v>1</v>
@@ -3029,7 +3029,7 @@
         </is>
       </c>
       <c r="L76" t="n">
-        <v>300</v>
+        <v>400</v>
       </c>
       <c r="O76" t="n">
         <v>1</v>
@@ -3062,7 +3062,7 @@
         </is>
       </c>
       <c r="L77" t="n">
-        <v>300</v>
+        <v>400</v>
       </c>
       <c r="O77" t="n">
         <v>1</v>
@@ -3095,7 +3095,7 @@
         </is>
       </c>
       <c r="L78" t="n">
-        <v>300</v>
+        <v>400</v>
       </c>
       <c r="O78" t="n">
         <v>1</v>
@@ -3138,7 +3138,7 @@
         </is>
       </c>
       <c r="L79" t="n">
-        <v>300</v>
+        <v>400</v>
       </c>
       <c r="O79" t="n">
         <v>1</v>
@@ -3171,7 +3171,7 @@
         </is>
       </c>
       <c r="L80" t="n">
-        <v>300</v>
+        <v>400</v>
       </c>
       <c r="O80" t="n">
         <v>1</v>
@@ -3204,7 +3204,7 @@
         </is>
       </c>
       <c r="L81" t="n">
-        <v>300</v>
+        <v>400</v>
       </c>
       <c r="O81" t="n">
         <v>1</v>
@@ -3237,7 +3237,7 @@
         </is>
       </c>
       <c r="L82" t="n">
-        <v>300</v>
+        <v>400</v>
       </c>
       <c r="O82" t="n">
         <v>1</v>
@@ -3270,7 +3270,7 @@
         </is>
       </c>
       <c r="L83" t="n">
-        <v>300</v>
+        <v>400</v>
       </c>
       <c r="O83" t="n">
         <v>1</v>
@@ -3303,7 +3303,7 @@
         </is>
       </c>
       <c r="L84" t="n">
-        <v>300</v>
+        <v>400</v>
       </c>
       <c r="O84" t="n">
         <v>1</v>
@@ -3336,7 +3336,7 @@
         </is>
       </c>
       <c r="L85" t="n">
-        <v>300</v>
+        <v>400</v>
       </c>
       <c r="O85" t="n">
         <v>1</v>
@@ -3369,7 +3369,7 @@
         </is>
       </c>
       <c r="L86" t="n">
-        <v>300</v>
+        <v>400</v>
       </c>
       <c r="O86" t="n">
         <v>1</v>
@@ -3402,7 +3402,7 @@
         </is>
       </c>
       <c r="L87" t="n">
-        <v>300</v>
+        <v>400</v>
       </c>
       <c r="O87" t="n">
         <v>1</v>
@@ -3435,7 +3435,7 @@
         </is>
       </c>
       <c r="L88" t="n">
-        <v>300</v>
+        <v>400</v>
       </c>
       <c r="O88" t="n">
         <v>1</v>
@@ -3468,7 +3468,7 @@
         </is>
       </c>
       <c r="L89" t="n">
-        <v>300</v>
+        <v>400</v>
       </c>
       <c r="O89" t="n">
         <v>1</v>
@@ -3501,7 +3501,7 @@
         </is>
       </c>
       <c r="L90" t="n">
-        <v>300</v>
+        <v>400</v>
       </c>
       <c r="O90" t="n">
         <v>1</v>
@@ -3534,7 +3534,7 @@
         </is>
       </c>
       <c r="L91" t="n">
-        <v>300</v>
+        <v>400</v>
       </c>
       <c r="O91" t="n">
         <v>1</v>
@@ -3567,7 +3567,7 @@
         </is>
       </c>
       <c r="L92" t="n">
-        <v>300</v>
+        <v>400</v>
       </c>
       <c r="O92" t="n">
         <v>1</v>
@@ -3600,7 +3600,7 @@
         </is>
       </c>
       <c r="L93" t="n">
-        <v>300</v>
+        <v>400</v>
       </c>
       <c r="O93" t="n">
         <v>1</v>
@@ -3633,7 +3633,7 @@
         </is>
       </c>
       <c r="L94" t="n">
-        <v>300</v>
+        <v>400</v>
       </c>
       <c r="O94" t="n">
         <v>1</v>
@@ -3671,7 +3671,7 @@
         </is>
       </c>
       <c r="L95" t="n">
-        <v>300</v>
+        <v>400</v>
       </c>
       <c r="O95" t="n">
         <v>1</v>
@@ -3704,7 +3704,7 @@
         </is>
       </c>
       <c r="L96" t="n">
-        <v>300</v>
+        <v>400</v>
       </c>
       <c r="O96" t="n">
         <v>1</v>
@@ -3742,7 +3742,7 @@
         </is>
       </c>
       <c r="L97" t="n">
-        <v>300</v>
+        <v>400</v>
       </c>
       <c r="O97" t="n">
         <v>1</v>
@@ -3775,7 +3775,7 @@
         </is>
       </c>
       <c r="L98" t="n">
-        <v>300</v>
+        <v>400</v>
       </c>
       <c r="O98" t="n">
         <v>1</v>
@@ -3808,7 +3808,7 @@
         </is>
       </c>
       <c r="L99" t="n">
-        <v>300</v>
+        <v>400</v>
       </c>
       <c r="O99" t="n">
         <v>1</v>
@@ -3841,7 +3841,7 @@
         </is>
       </c>
       <c r="L100" t="n">
-        <v>300</v>
+        <v>400</v>
       </c>
       <c r="O100" t="n">
         <v>1</v>
@@ -3874,7 +3874,7 @@
         </is>
       </c>
       <c r="L101" t="n">
-        <v>300</v>
+        <v>400</v>
       </c>
       <c r="O101" t="n">
         <v>1</v>
@@ -3912,7 +3912,7 @@
         </is>
       </c>
       <c r="L102" t="n">
-        <v>300</v>
+        <v>400</v>
       </c>
       <c r="O102" t="n">
         <v>1</v>
@@ -3945,7 +3945,7 @@
         </is>
       </c>
       <c r="L103" t="n">
-        <v>300</v>
+        <v>400</v>
       </c>
       <c r="O103" t="n">
         <v>1</v>
@@ -3978,7 +3978,7 @@
         </is>
       </c>
       <c r="L104" t="n">
-        <v>300</v>
+        <v>400</v>
       </c>
       <c r="O104" t="n">
         <v>1</v>
@@ -4016,7 +4016,7 @@
         </is>
       </c>
       <c r="L105" t="n">
-        <v>300</v>
+        <v>400</v>
       </c>
       <c r="O105" t="n">
         <v>1</v>
@@ -4049,7 +4049,7 @@
         </is>
       </c>
       <c r="L106" t="n">
-        <v>300</v>
+        <v>400</v>
       </c>
       <c r="O106" t="n">
         <v>1</v>
@@ -4082,7 +4082,7 @@
         </is>
       </c>
       <c r="L107" t="n">
-        <v>300</v>
+        <v>400</v>
       </c>
       <c r="O107" t="n">
         <v>1</v>
@@ -4110,7 +4110,7 @@
         </is>
       </c>
       <c r="L108" t="n">
-        <v>300</v>
+        <v>400</v>
       </c>
       <c r="O108" t="n">
         <v>1</v>
@@ -4138,7 +4138,7 @@
         </is>
       </c>
       <c r="L109" t="n">
-        <v>300</v>
+        <v>400</v>
       </c>
       <c r="O109" t="n">
         <v>1</v>
@@ -4176,7 +4176,7 @@
         </is>
       </c>
       <c r="L110" t="n">
-        <v>300</v>
+        <v>400</v>
       </c>
       <c r="O110" t="n">
         <v>1</v>
@@ -4209,7 +4209,7 @@
         </is>
       </c>
       <c r="L111" t="n">
-        <v>300</v>
+        <v>400</v>
       </c>
       <c r="O111" t="n">
         <v>1</v>
@@ -4247,7 +4247,7 @@
         </is>
       </c>
       <c r="L112" t="n">
-        <v>300</v>
+        <v>400</v>
       </c>
       <c r="O112" t="n">
         <v>1</v>
@@ -4280,7 +4280,7 @@
         </is>
       </c>
       <c r="L113" t="n">
-        <v>300</v>
+        <v>400</v>
       </c>
       <c r="O113" t="n">
         <v>1</v>
@@ -4313,7 +4313,7 @@
         </is>
       </c>
       <c r="L114" t="n">
-        <v>300</v>
+        <v>400</v>
       </c>
       <c r="O114" t="n">
         <v>1</v>
@@ -4346,7 +4346,7 @@
         </is>
       </c>
       <c r="L115" t="n">
-        <v>300</v>
+        <v>400</v>
       </c>
       <c r="O115" t="n">
         <v>1</v>
@@ -4379,7 +4379,7 @@
         </is>
       </c>
       <c r="L116" t="n">
-        <v>300</v>
+        <v>400</v>
       </c>
       <c r="O116" t="n">
         <v>1</v>
@@ -4412,7 +4412,7 @@
         </is>
       </c>
       <c r="L117" t="n">
-        <v>300</v>
+        <v>400</v>
       </c>
       <c r="O117" t="n">
         <v>1</v>
@@ -4445,7 +4445,7 @@
         </is>
       </c>
       <c r="L118" t="n">
-        <v>300</v>
+        <v>400</v>
       </c>
       <c r="O118" t="n">
         <v>1</v>
@@ -4483,7 +4483,7 @@
         </is>
       </c>
       <c r="L119" t="n">
-        <v>300</v>
+        <v>400</v>
       </c>
       <c r="O119" t="n">
         <v>1</v>
@@ -4516,7 +4516,7 @@
         </is>
       </c>
       <c r="L120" t="n">
-        <v>300</v>
+        <v>400</v>
       </c>
       <c r="O120" t="n">
         <v>1</v>
@@ -4554,7 +4554,7 @@
         </is>
       </c>
       <c r="L121" t="n">
-        <v>300</v>
+        <v>400</v>
       </c>
       <c r="O121" t="n">
         <v>1</v>
@@ -4587,7 +4587,7 @@
         </is>
       </c>
       <c r="L122" t="n">
-        <v>300</v>
+        <v>400</v>
       </c>
       <c r="O122" t="n">
         <v>1</v>
@@ -4620,7 +4620,7 @@
         </is>
       </c>
       <c r="L123" t="n">
-        <v>300</v>
+        <v>400</v>
       </c>
       <c r="O123" t="n">
         <v>1</v>
@@ -4653,7 +4653,7 @@
         </is>
       </c>
       <c r="L124" t="n">
-        <v>300</v>
+        <v>400</v>
       </c>
       <c r="O124" t="n">
         <v>1</v>
@@ -4686,7 +4686,7 @@
         </is>
       </c>
       <c r="L125" t="n">
-        <v>300</v>
+        <v>400</v>
       </c>
       <c r="O125" t="n">
         <v>1</v>
@@ -4719,7 +4719,7 @@
         </is>
       </c>
       <c r="L126" t="n">
-        <v>300</v>
+        <v>400</v>
       </c>
       <c r="O126" t="n">
         <v>1</v>
@@ -4752,7 +4752,7 @@
         </is>
       </c>
       <c r="L127" t="n">
-        <v>300</v>
+        <v>400</v>
       </c>
       <c r="O127" t="n">
         <v>1</v>
@@ -4785,7 +4785,7 @@
         </is>
       </c>
       <c r="L128" t="n">
-        <v>300</v>
+        <v>400</v>
       </c>
       <c r="O128" t="n">
         <v>1</v>
@@ -4818,7 +4818,7 @@
         </is>
       </c>
       <c r="L129" t="n">
-        <v>300</v>
+        <v>400</v>
       </c>
       <c r="O129" t="n">
         <v>1</v>

--- a/docs/missioni-bt3.xlsx
+++ b/docs/missioni-bt3.xlsx
@@ -419,7 +419,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P129"/>
+  <dimension ref="A1:P141"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -624,12 +624,17 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>cattivi</t>
+          <t>arruolabili</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>quiz</t>
+          <t>combattimento</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>vincere</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -645,23 +650,25 @@
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>I muscoli non bastano: voglio un alleato sveglio. | Rispondi giusto e combatterò per te.</t>
+          <t>Vediamo quanto sei forte! | Battimi e verrò con te.</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>cattivi</t>
+          <t>arruolabili</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>salta turni</t>
-        </is>
-      </c>
-      <c r="H6" t="n">
-        <v>1</v>
+          <t>combattimento</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>vincere</t>
+        </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
@@ -669,14 +676,14 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>900</v>
+        <v>400</v>
       </c>
       <c r="O6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Io non prendo ordini da nessuno. | Lavora per me {n} turno, poi ti seguirò.</t>
+          <t>Non mi unisco a chi non sa combattere. | Battimi e sarò dei vostri.</t>
         </is>
       </c>
     </row>
@@ -705,11 +712,11 @@
         <v>400</v>
       </c>
       <c r="O7" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Vediamo quanto sei forte! | Battimi e verrò con te.</t>
+          <t>Un vero scontro vale più di mille parole. | Battimi e combatterò al tuo fianco.</t>
         </is>
       </c>
     </row>
@@ -721,12 +728,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>combattimento</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>vincere</t>
+          <t>quiz</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
@@ -742,7 +744,7 @@
       </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Non mi unisco a chi non sa combattere. | Battimi e sarò dei vostri.</t>
+          <t>Prima di seguirti voglio sapere quanto ne sai. | Rispondi giusto e sarò dei vostri.</t>
         </is>
       </c>
     </row>
@@ -754,13 +756,11 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>combattimento</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>vincere</t>
-        </is>
+          <t>attendi</t>
+        </is>
+      </c>
+      <c r="H9" t="n">
+        <v>2</v>
       </c>
       <c r="J9" t="inlineStr">
         <is>
@@ -768,14 +768,14 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>400</v>
+        <v>1400</v>
       </c>
       <c r="O9" t="n">
         <v>1</v>
       </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Un vero scontro vale più di mille parole. | Battimi e combatterò al tuo fianco.</t>
+          <t>Devo finire il mio allenamento. | Torna tra {n} turni e verrò con te.</t>
         </is>
       </c>
     </row>
@@ -787,8 +787,11 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>quiz</t>
-        </is>
+          <t>salta turni</t>
+        </is>
+      </c>
+      <c r="H10" t="n">
+        <v>1</v>
       </c>
       <c r="J10" t="inlineStr">
         <is>
@@ -796,21 +799,21 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>400</v>
+        <v>900</v>
       </c>
       <c r="O10" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Prima di seguirti voglio sapere quanto ne sai. | Rispondi giusto e sarò dei vostri.</t>
+          <t>Allenarsi da soli non serve a niente. | Allenati con me per {n} turno e poi verrò con te.</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>arruolabili</t>
+          <t>storia</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -821,27 +824,22 @@
       <c r="H11" t="n">
         <v>2</v>
       </c>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>sì</t>
-        </is>
-      </c>
       <c r="L11" t="n">
-        <v>1400</v>
+        <v>1500</v>
       </c>
       <c r="O11" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Devo finire il mio allenamento. | Torna tra {n} turni e verrò con te.</t>
+          <t>Ho mille cose da fare e nessuno che mi aiuti. | Ripassa tra {n} turni e avrai {premio}.</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>arruolabili</t>
+          <t>storia</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -852,20 +850,15 @@
       <c r="H12" t="n">
         <v>1</v>
       </c>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t>sì</t>
-        </is>
-      </c>
       <c r="L12" t="n">
-        <v>900</v>
+        <v>1500</v>
       </c>
       <c r="O12" t="n">
         <v>1</v>
       </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Allenarsi da soli non serve a niente. | Allenati con me per {n} turno e poi verrò con te.</t>
+          <t>Mi serve una mano, subito. | Resta qui {n} turno ad aiutarmi e avrai {premio}.</t>
         </is>
       </c>
     </row>
@@ -877,54 +870,56 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>attendi</t>
-        </is>
-      </c>
-      <c r="H13" t="n">
-        <v>2</v>
+          <t>quiz</t>
+        </is>
       </c>
       <c r="L13" t="n">
-        <v>1500</v>
+        <v>800</v>
       </c>
       <c r="O13" t="n">
         <v>2</v>
       </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Ho mille cose da fare e nessuno che mi aiuti. | Ripassa tra {n} turni e avrai {premio}.</t>
+          <t>Vediamo se sei preparato. | Rispondi giusto e avrai {premio}.</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>storia</t>
+          <t>Chichi (adulta)</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>salta turni</t>
+          <t>attendi</t>
         </is>
       </c>
       <c r="H14" t="n">
-        <v>1</v>
+        <v>3</v>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>Son Goten</t>
+        </is>
       </c>
       <c r="L14" t="n">
         <v>1500</v>
       </c>
       <c r="O14" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Mi serve una mano, subito. | Resta qui {n} turno ad aiutarmi e avrai {premio}.</t>
+          <t>Goku è sempre in giro ad allenarsi... | Ripassa tra {n} turni: ti presento {premio}!</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>storia</t>
+          <t>Chichi (adulta)</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -936,18 +931,18 @@
         <v>800</v>
       </c>
       <c r="O15" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Vediamo se sei preparato. | Rispondi giusto e avrai {premio}.</t>
+          <t>Mio figlio deve studiare, non fare a botte! | Rispondi giusto e avrai {premio}.</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Chichi (adulta)</t>
+          <t>Bulma</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -960,30 +955,35 @@
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>Son Goten</t>
+          <t>Trunks (bambino)</t>
         </is>
       </c>
       <c r="L16" t="n">
         <v>1500</v>
       </c>
       <c r="O16" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Goku è sempre in giro ad allenarsi... | Ripassa tra {n} turni: ti presento {premio}!</t>
+          <t>Vegeta non si accorge di niente... | Torna tra {n} turni e avrai {premio}!</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Chichi (adulta)</t>
+          <t>Bulma</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>quiz</t>
+          <t>accompagnami da</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Son Goku (bambino)</t>
         </is>
       </c>
       <c r="L17" t="n">
@@ -994,7 +994,7 @@
       </c>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Mio figlio deve studiare, non fare a botte! | Rispondi giusto e avrai {premio}.</t>
+          <t>Sto cercando le sfere del drago, ma da sola ho paura. | Accompagnami da {obiettivo} e avrai {monete} monete.</t>
         </is>
       </c>
     </row>
@@ -1006,314 +1006,251 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>attendi</t>
-        </is>
-      </c>
-      <c r="H18" t="n">
-        <v>3</v>
-      </c>
-      <c r="K18" t="inlineStr">
+          <t>accompagnami da</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
         <is>
           <t>Trunks (bambino)</t>
         </is>
       </c>
       <c r="L18" t="n">
-        <v>1500</v>
+        <v>800</v>
       </c>
       <c r="O18" t="n">
         <v>1</v>
       </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Vegeta non si accorge di niente... | Torna tra {n} turni e avrai {premio}!</t>
+          <t>Trunks è sparito di nuovo con Goten! | Accompagnami da {obiettivo} e avrai {monete} monete.</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Bobbidi</t>
+          <t>Chichi (adulta)</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>combattimento</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>2v2</t>
-        </is>
-      </c>
-      <c r="D19" t="inlineStr">
-        <is>
-          <t>vincere</t>
-        </is>
-      </c>
-      <c r="E19" t="inlineStr">
-        <is>
-          <t>Dabura | Majin Buu (buono)</t>
+          <t>accompagnami da</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Son Goku (fine)</t>
         </is>
       </c>
       <c r="L19" t="n">
-        <v>2000</v>
-      </c>
-      <c r="M19" t="inlineStr">
-        <is>
-          <t>Senzu</t>
-        </is>
+        <v>800</v>
       </c>
       <c r="O19" t="n">
         <v>1</v>
       </c>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Io non mi sporco le mani! | Dabura, Majin Bu: pensateci voi! Batteteli e avrai {premio}.</t>
+          <t>Goku non torna a casa da giorni! | Accompagnami da {obiettivo} e avrai {monete} monete.</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Cooler</t>
+          <t>Chichi (adulta)</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>combattimento</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>1v1</t>
-        </is>
-      </c>
-      <c r="D20" t="inlineStr">
-        <is>
-          <t>trasformazione</t>
-        </is>
-      </c>
-      <c r="J20" t="inlineStr">
-        <is>
-          <t>sì</t>
+          <t>accompagnami da</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Son Gohan (bambino)</t>
         </is>
       </c>
       <c r="L20" t="n">
-        <v>400</v>
-      </c>
-      <c r="N20" t="inlineStr">
-        <is>
-          <t>Metal Cooler</t>
-        </is>
+        <v>800</v>
       </c>
       <c r="O20" t="n">
         <v>1</v>
       </c>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Mio fratello non era alla mia altezza. | Costringimi a trasformarmi, se ci riesci!</t>
+          <t>Gohan deve tornare a studiare! | Accompagnami da {obiettivo} e avrai {monete} monete.</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Freeza (prima forma)</t>
+          <t>Kami</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>combattimento</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>1v1</t>
-        </is>
-      </c>
-      <c r="D21" t="inlineStr">
-        <is>
-          <t>trasformazione</t>
-        </is>
-      </c>
-      <c r="J21" t="inlineStr">
-        <is>
-          <t>sì</t>
+          <t>accompagnami da</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Piccolo (inizio)</t>
         </is>
       </c>
       <c r="L21" t="n">
-        <v>400</v>
-      </c>
-      <c r="N21" t="inlineStr">
-        <is>
-          <t>Freeza (forma finale)</t>
-        </is>
+        <v>800</v>
       </c>
       <c r="O21" t="n">
         <v>1</v>
       </c>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Non hai idea di quante trasformazioni mi restino. | Costringimi a usarne una, se ci riesci!</t>
+          <t>Io e Piccolo siamo una cosa sola... | Accompagnami da {obiettivo} e avrai {monete} monete.</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Cell (prima forma)</t>
+          <t>Kami</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>combattimento</t>
-        </is>
-      </c>
-      <c r="D22" t="inlineStr">
-        <is>
-          <t>trasformazione</t>
-        </is>
-      </c>
-      <c r="J22" t="inlineStr">
-        <is>
-          <t>sì</t>
+          <t>accompagnami da</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Son Goku (inizio)</t>
         </is>
       </c>
       <c r="L22" t="n">
-        <v>400</v>
-      </c>
-      <c r="N22" t="inlineStr">
-        <is>
-          <t>Cell (perfetto, massima potenza)</t>
-        </is>
+        <v>800</v>
       </c>
       <c r="O22" t="n">
         <v>1</v>
       </c>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Mi manca poco per diventare perfetto... | Costringimi a trasformarmi e capirai il tuo errore.</t>
+          <t>Goku ha bisogno di un nuovo allenamento. | Accompagnami da {obiettivo} e avrai {monete} monete.</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
+          <t>Karin</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>accompagnami da</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
           <t>Son Goku (bambino)</t>
         </is>
       </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>batti</t>
-        </is>
-      </c>
-      <c r="F23" t="inlineStr">
-        <is>
-          <t>Tao Pai Pai</t>
-        </is>
-      </c>
-      <c r="J23" t="inlineStr">
-        <is>
-          <t>sì</t>
-        </is>
-      </c>
       <c r="L23" t="n">
-        <v>400</v>
+        <v>800</v>
       </c>
       <c r="O23" t="n">
         <v>1</v>
       </c>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Tao Pai Pai ha ucciso il papà di Upa. | Batti {obiettivo} e verrò con te.</t>
+          <t>Ho preparato i fagioli magici per quel ragazzino. | Accompagnami da {obiettivo} e avrai {monete} monete.</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Tao Pai Pai (cyborg)</t>
+          <t>Baba la Veggente</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>batti</t>
+          <t>accompagnami da</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Tenshinhan</t>
-        </is>
-      </c>
-      <c r="J24" t="inlineStr">
-        <is>
-          <t>sì</t>
+          <t>Muten Roshi (massima potenza)</t>
         </is>
       </c>
       <c r="L24" t="n">
-        <v>400</v>
+        <v>800</v>
       </c>
       <c r="O24" t="n">
         <v>1</v>
       </c>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Tenshinhan ha tradito il suo maestro. | Batti {obiettivo} e il killer più famoso del mondo lavorerà per te.</t>
+          <t>Mio fratello ha bisogno di me. | Accompagnami da {obiettivo} e avrai {monete} monete.</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Tenshinhan</t>
+          <t>Bobbidi</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>batti</t>
-        </is>
-      </c>
-      <c r="F25" t="inlineStr">
-        <is>
-          <t>Tao Pai Pai</t>
-        </is>
-      </c>
-      <c r="J25" t="inlineStr">
-        <is>
-          <t>sì</t>
+          <t>combattimento</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>2v2</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>vincere</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>Dabura | Majin Buu (buono)</t>
         </is>
       </c>
       <c r="L25" t="n">
-        <v>400</v>
+        <v>2000</v>
+      </c>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>Senzu</t>
+        </is>
       </c>
       <c r="O25" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Tao Pai Pai era il mio maestro: ora è solo un assassino. | Batti {obiettivo} e verrò con te.</t>
+          <t>Io non mi sporco le mani! | Dabura, Majin Bu: pensateci voi! Batteteli e avrai {premio}.</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Tenshinhan</t>
+          <t>Dabura</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>vai da</t>
+          <t>batti</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Krilin</t>
-        </is>
-      </c>
-      <c r="G26" t="inlineStr">
-        <is>
-          <t>sì</t>
+          <t>Majin Buu (buono) | Majin Buu (puro male) | Super Buu | Majin Buu (puro)</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
@@ -1329,24 +1266,29 @@
       </c>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Krilin non si fa vivo da un po'. | Vai a trovare {obiettivo} e torna: poi partiamo.</t>
+          <t>Majin Bu è una minaccia anche per i demoni. | Batti {obiettivo} e il re dei demoni verrà con te.</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Piccolo Daimao</t>
+          <t>Dabura</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>porta</t>
-        </is>
-      </c>
-      <c r="F27" t="inlineStr">
-        <is>
-          <t>Tambourine</t>
+          <t>combattimento</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>1v1</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>vincere</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
@@ -1357,34 +1299,39 @@
       <c r="L27" t="n">
         <v>400</v>
       </c>
+      <c r="N27" t="inlineStr">
+        <is>
+          <t>Super Buu</t>
+        </is>
+      </c>
       <c r="O27" t="n">
         <v>1</v>
       </c>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Tambourine è il più fedele dei miei figli. | Portami {obiettivo} e il Grande Mago Piccolo combatterà per te.</t>
+          <t>Majin Bu si è risvegliato... e sta cambiando. | Battimi e potrai vedere che cosa è diventato.</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Tambourine</t>
+          <t>Cooler</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>vai da</t>
-        </is>
-      </c>
-      <c r="F28" t="inlineStr">
-        <is>
-          <t>Piccolo Daimao</t>
-        </is>
-      </c>
-      <c r="G28" t="inlineStr">
-        <is>
-          <t>sì</t>
+          <t>combattimento</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>1v1</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>trasformazione</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
@@ -1395,29 +1342,39 @@
       <c r="L28" t="n">
         <v>400</v>
       </c>
+      <c r="N28" t="inlineStr">
+        <is>
+          <t>Metal Cooler</t>
+        </is>
+      </c>
       <c r="O28" t="n">
         <v>1</v>
       </c>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Devo fare rapporto al Grande Mago Piccolo. | Vai da {obiettivo} e torna: poi verrò con te.</t>
+          <t>Mio fratello non era alla mia altezza. | Costringimi a trasformarmi, se ci riesci!</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Krilin</t>
+          <t>Cooler</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>batti</t>
-        </is>
-      </c>
-      <c r="F29" t="inlineStr">
-        <is>
-          <t>Tambourine</t>
+          <t>combattimento</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>1v1</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>trasformazione</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
@@ -1433,19 +1390,29 @@
       </c>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Al torneo un demone mi ha colto alle spalle... | Batti {obiettivo} e verrò con te.</t>
+          <t>Mio fratello non era alla mia altezza. | Costringimi a trasformarmi, se ci riesci!</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Yamcha</t>
+          <t>Freeza (prima forma)</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>quiz</t>
+          <t>combattimento</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>1v1</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>trasformazione</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
@@ -1461,52 +1428,47 @@
       </c>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Ho studiato tanto, sai? | Rispondi meglio di me e vengo con te.</t>
+          <t>Non hai idea di quante trasformazioni mi restino. | Costringimi a usarne una, se ci riesci!</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>C-8</t>
+          <t>Cell (prima forma)</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>vai da</t>
-        </is>
-      </c>
-      <c r="F31" t="inlineStr">
-        <is>
-          <t>Son Goku (bambino)</t>
-        </is>
-      </c>
-      <c r="G31" t="inlineStr">
-        <is>
-          <t>sì</t>
-        </is>
-      </c>
-      <c r="J31" t="inlineStr">
-        <is>
-          <t>sì</t>
+          <t>combattimento</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>trasformazione</t>
         </is>
       </c>
       <c r="L31" t="n">
-        <v>400</v>
+        <v>1200</v>
+      </c>
+      <c r="N31" t="inlineStr">
+        <is>
+          <t>Cell (perfetto, massima potenza)</t>
+        </is>
       </c>
       <c r="O31" t="n">
         <v>1</v>
       </c>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Goku mi ha salvato dall'esercito del Red Ribbon. | Portagli i miei saluti: vai da {obiettivo} e torna, poi verrò con te.</t>
+          <t>Mi manca poco per diventare perfetto... | Costringimi a trasformarmi: la strada si aprirà e avrai {monete} monete.</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Muten Roshi (massima potenza)</t>
+          <t>Cell (prima forma)</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -1516,7 +1478,7 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>vincere</t>
+          <t>trasformazione</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
@@ -1532,24 +1494,24 @@
       </c>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Anche un vecchio maestro ha ancora qualche asso nella manica. | Battimi e verrò con te.</t>
+          <t>Mi manca poco per diventare perfetto... | Costringimi a trasformarmi e capirai il tuo errore.</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Garlic Jr.</t>
+          <t>Son Goku (bambino)</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>combattimento</t>
-        </is>
-      </c>
-      <c r="D33" t="inlineStr">
-        <is>
-          <t>trasformazione</t>
+          <t>batti</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>Tao Pai Pai</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
@@ -1565,24 +1527,29 @@
       </c>
       <c r="P33" t="inlineStr">
         <is>
-          <t>Con le sfere del drago sono diventato immortale. | Costringimi a trasformarmi e combatterò per te.</t>
+          <t>Tao Pai Pai ha ucciso il papà di Upa. | Batti {obiettivo} e verrò con te.</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Son Goku (inizio)</t>
+          <t>Tao Pai Pai (cyborg)</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>batti</t>
-        </is>
-      </c>
-      <c r="F34" t="inlineStr">
-        <is>
-          <t>Raditz</t>
+          <t>combattimento</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>1v1</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>vincere</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
@@ -1598,14 +1565,14 @@
       </c>
       <c r="P34" t="inlineStr">
         <is>
-          <t>Raditz dice di essere mio fratello e ha rapito Gohan! | Batti {obiettivo} e verrò con te.</t>
+          <t>Il mio corpo da cyborg è inarrestabile! | Battimi, se ci riesci, e lavorerò per te.</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Piccolo (inizio)</t>
+          <t>Tenshinhan</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -1615,7 +1582,7 @@
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Raditz</t>
+          <t>Tao Pai Pai</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
@@ -1627,28 +1594,38 @@
         <v>400</v>
       </c>
       <c r="O35" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="P35" t="inlineStr">
         <is>
-          <t>Ho un conto in sospeso con {obiettivo}. | Battilo e combatterò al tuo fianco.</t>
+          <t>Tao Pai Pai era il mio maestro: ora è solo un assassino. | Batti {obiettivo} e verrò con te.</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Raditz</t>
+          <t>Piccolo Daimao</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>porta</t>
-        </is>
-      </c>
-      <c r="F36" t="inlineStr">
-        <is>
-          <t>Son Gohan (bambino)</t>
+          <t>combattimento</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>2v2</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>vincere</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>Piccolo Daimao | Tambourine</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
@@ -1664,29 +1641,34 @@
       </c>
       <c r="P36" t="inlineStr">
         <is>
-          <t>Kakaroth non vuole unirsi a me? Prenderò suo figlio. | Portami {obiettivo} e verrò con te.</t>
+          <t>Tambourine, sbarazzati di loro! | Battete me e Tambourine, e sarò vostro.</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Son Gohan (bambino)</t>
+          <t>Tambourine</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>vai da</t>
-        </is>
-      </c>
-      <c r="F37" t="inlineStr">
-        <is>
-          <t>Piccolo (inizio)</t>
-        </is>
-      </c>
-      <c r="G37" t="inlineStr">
-        <is>
-          <t>sì</t>
+          <t>combattimento</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>2v2</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>vincere</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>Tambourine | Piccolo Daimao</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
@@ -1702,34 +1684,24 @@
       </c>
       <c r="P37" t="inlineStr">
         <is>
-          <t>Il signor Piccolo mi starà aspettando. | Accompagnami da {obiettivo}, poi torniamo qui e verrò con te.</t>
+          <t>Il Gran Re Piccolo mi ha mandato a cercarti. | Battete me e il mio re, e vi seguirò.</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Nappa</t>
+          <t>Krilin</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>combattimento</t>
-        </is>
-      </c>
-      <c r="C38" t="inlineStr">
-        <is>
-          <t>2v2</t>
-        </is>
-      </c>
-      <c r="D38" t="inlineStr">
-        <is>
-          <t>vincere</t>
-        </is>
-      </c>
-      <c r="E38" t="inlineStr">
-        <is>
-          <t>Nappa | Saibaiman</t>
+          <t>batti</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>Tambourine</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
@@ -1745,24 +1717,19 @@
       </c>
       <c r="P38" t="inlineStr">
         <is>
-          <t>Saibaiman, uscite dal terreno! | Battete me e il mio Saibaiman, e vi seguirò.</t>
+          <t>Al torneo un demone mi ha colto alle spalle... | Batti {obiettivo} e verrò con te.</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Vegeta (scouter)</t>
+          <t>Yamcha</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>combattimento</t>
-        </is>
-      </c>
-      <c r="D39" t="inlineStr">
-        <is>
-          <t>trasformazione</t>
+          <t>quiz</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
@@ -1778,24 +1745,24 @@
       </c>
       <c r="P39" t="inlineStr">
         <is>
-          <t>Il principe dei Saiyan non perde contro nessuno. | Costringimi a trasformarmi e ti seguirò.</t>
+          <t>Ho studiato tanto, sai? | Rispondi meglio di me e vengo con te.</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Vegeta (scouter)</t>
+          <t>Muten Roshi (massima potenza)</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>batti</t>
-        </is>
-      </c>
-      <c r="F40" t="inlineStr">
-        <is>
-          <t>Kyui</t>
+          <t>combattimento</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>vincere</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
@@ -1811,24 +1778,24 @@
       </c>
       <c r="P40" t="inlineStr">
         <is>
-          <t>Kyui si crede alla mia altezza. Che illuso. | Batti {obiettivo} e verrò con te.</t>
+          <t>Anche un vecchio maestro ha ancora qualche asso nella manica. | Battimi e verrò con te.</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Re Vegeta</t>
+          <t>Garlic Jr.</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>batti</t>
-        </is>
-      </c>
-      <c r="F41" t="inlineStr">
-        <is>
-          <t>Freeza (prima forma)</t>
+          <t>combattimento</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>trasformazione</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
@@ -1844,14 +1811,14 @@
       </c>
       <c r="P41" t="inlineStr">
         <is>
-          <t>Freeza tiene in pugno il popolo dei Saiyan. | Batti {obiettivo} e il re dei Saiyan combatterà per te.</t>
+          <t>Con le sfere del drago sono diventato immortale. | Costringimi a trasformarmi e combatterò per te.</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Bardock</t>
+          <t>Son Goku (inizio)</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -1861,7 +1828,7 @@
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Freeza (prima forma)</t>
+          <t>Raditz</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
@@ -1877,14 +1844,14 @@
       </c>
       <c r="P42" t="inlineStr">
         <is>
-          <t>Freeza vuole distruggere il mio pianeta. | Batti {obiettivo} e avrai la mia forza.</t>
+          <t>Raditz dice di essere mio fratello e ha rapito Gohan! | Batti {obiettivo} e verrò con te.</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Selypa</t>
+          <t>Piccolo (inizio)</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -1894,7 +1861,7 @@
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Dodoria</t>
+          <t>Raditz</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
@@ -1910,23 +1877,30 @@
       </c>
       <c r="P43" t="inlineStr">
         <is>
-          <t>Gli uomini di Dodoria hanno sterminato la nostra squadra. | Batti {obiettivo} e verrò con te.</t>
+          <t>Ho un conto in sospeso con {obiettivo}. | Battilo e combatterò al tuo fianco.</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Son Goku (metà)</t>
+          <t>Raditz</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>salta turni</t>
-        </is>
-      </c>
-      <c r="H44" t="n">
-        <v>1</v>
+          <t>combattimento</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>1v1</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>vincere</t>
+        </is>
       </c>
       <c r="J44" t="inlineStr">
         <is>
@@ -1934,21 +1908,21 @@
         </is>
       </c>
       <c r="L44" t="n">
-        <v>900</v>
+        <v>400</v>
       </c>
       <c r="O44" t="n">
         <v>1</v>
       </c>
       <c r="P44" t="inlineStr">
         <is>
-          <t>Sto andando su Nameck: in astronave mi alleno a cento volte la gravità. | Allenati con me per {n} turno e verrò con te.</t>
+          <t>Kakaroth si è rammollito su questo pianeta. | Battimi, se ne sei capace, e verrò con te.</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Son Goku (metà)</t>
+          <t>Son Gohan (bambino)</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -1958,7 +1932,7 @@
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Ginyu</t>
+          <t>Raditz</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
@@ -1974,24 +1948,34 @@
       </c>
       <c r="P45" t="inlineStr">
         <is>
-          <t>La Squadra Ginyu sta attaccando i miei amici. | Batti {obiettivo} e verrò con te.</t>
+          <t>Papà è in pericolo! | Batti {obiettivo} e verrò con te.</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Son Goku (metà) SSJ</t>
+          <t>Nappa</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>batti</t>
-        </is>
-      </c>
-      <c r="F46" t="inlineStr">
-        <is>
-          <t>Freeza (forma finale)</t>
+          <t>combattimento</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>2v2</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>vincere</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>Nappa | Saibaiman</t>
         </is>
       </c>
       <c r="J46" t="inlineStr">
@@ -2007,24 +1991,24 @@
       </c>
       <c r="P46" t="inlineStr">
         <is>
-          <t>Freeza ha ucciso Krilin: per questo sono diventato Super Saiyan. | Batti {obiettivo} e combatterò al tuo fianco.</t>
+          <t>Saibaiman, uscite dal terreno! | Battete me e il mio Saibaiman, e vi seguirò.</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Nail</t>
+          <t>Vegeta (scouter)</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>batti</t>
-        </is>
-      </c>
-      <c r="F47" t="inlineStr">
-        <is>
-          <t>Zarbon</t>
+          <t>combattimento</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>trasformazione</t>
         </is>
       </c>
       <c r="J47" t="inlineStr">
@@ -2040,29 +2024,24 @@
       </c>
       <c r="P47" t="inlineStr">
         <is>
-          <t>Il pianeta Nameck è in pericolo. | Batti {obiettivo} e combatterò per te.</t>
+          <t>Il principe dei Saiyan non perde contro nessuno. | Costringimi a trasformarmi e ti seguirò.</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Zarbon</t>
+          <t>Re Vegeta</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>combattimento</t>
-        </is>
-      </c>
-      <c r="C48" t="inlineStr">
-        <is>
-          <t>1v1</t>
-        </is>
-      </c>
-      <c r="D48" t="inlineStr">
-        <is>
-          <t>trasformazione</t>
+          <t>batti</t>
+        </is>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>Freeza (prima forma)</t>
         </is>
       </c>
       <c r="J48" t="inlineStr">
@@ -2078,14 +2057,14 @@
       </c>
       <c r="P48" t="inlineStr">
         <is>
-          <t>Non costringermi a mostrarti il mio vero aspetto! | Se ci riesci, verrò con te.</t>
+          <t>Freeza tiene in pugno il popolo dei Saiyan. | Batti {obiettivo} e il re dei Saiyan combatterà per te.</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Zarbon (trasformato)</t>
+          <t>Bardock</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -2095,7 +2074,7 @@
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Vegeta (scouter)</t>
+          <t>Freeza (prima forma)</t>
         </is>
       </c>
       <c r="J49" t="inlineStr">
@@ -2111,26 +2090,26 @@
       </c>
       <c r="P49" t="inlineStr">
         <is>
-          <t>Quella scimmia di Vegeta si è presa gioco di me. | Batti {obiettivo} e combatterò per te.</t>
+          <t>Freeza vuole distruggere il mio pianeta. | Batti {obiettivo} e avrai la mia forza.</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
+          <t>Selypa</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>batti</t>
+        </is>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
           <t>Dodoria</t>
         </is>
       </c>
-      <c r="B50" t="inlineStr">
-        <is>
-          <t>batti</t>
-        </is>
-      </c>
-      <c r="F50" t="inlineStr">
-        <is>
-          <t>Bardock</t>
-        </is>
-      </c>
       <c r="J50" t="inlineStr">
         <is>
           <t>sì</t>
@@ -2144,35 +2123,23 @@
       </c>
       <c r="P50" t="inlineStr">
         <is>
-          <t>Un Saiyan è sopravvissuto alla mia squadra. | Batti {obiettivo} e verrò con te.</t>
+          <t>Gli uomini di Dodoria hanno sterminato la nostra squadra. | Batti {obiettivo} e verrò con te.</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Ginyu</t>
+          <t>Son Goku (metà)</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>combattimento</t>
-        </is>
-      </c>
-      <c r="C51" t="inlineStr">
-        <is>
-          <t>2v2</t>
-        </is>
-      </c>
-      <c r="D51" t="inlineStr">
-        <is>
-          <t>vincere</t>
-        </is>
-      </c>
-      <c r="E51" t="inlineStr">
-        <is>
-          <t>Recoome | Guldo</t>
-        </is>
+          <t>salta turni</t>
+        </is>
+      </c>
+      <c r="H51" t="n">
+        <v>1</v>
       </c>
       <c r="J51" t="inlineStr">
         <is>
@@ -2180,21 +2147,21 @@
         </is>
       </c>
       <c r="L51" t="n">
-        <v>400</v>
+        <v>900</v>
       </c>
       <c r="O51" t="n">
         <v>1</v>
       </c>
       <c r="P51" t="inlineStr">
         <is>
-          <t>Squadra Ginyu, in posizione! | Battete Recoome e Guldo e sarò dei vostri.</t>
+          <t>Sto andando su Nameck: in astronave mi alleno a cento volte la gravità. | Allenati con me per {n} turno e verrò con te.</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Recoome</t>
+          <t>Son Goku (metà)</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -2204,7 +2171,7 @@
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Vegeta (scouter)</t>
+          <t>Ginyu</t>
         </is>
       </c>
       <c r="J52" t="inlineStr">
@@ -2220,23 +2187,25 @@
       </c>
       <c r="P52" t="inlineStr">
         <is>
-          <t>Il principe dei Saiyan? L'ho già fatto piangere una volta. | Batti {obiettivo} e verrò con te.</t>
+          <t>La Squadra Ginyu sta attaccando i miei amici. | Batti {obiettivo} e verrò con te.</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Guldo</t>
+          <t>Son Goku (metà) SSJ</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>salta turni</t>
-        </is>
-      </c>
-      <c r="H53" t="n">
-        <v>1</v>
+          <t>batti</t>
+        </is>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>Freeza (forma finale)</t>
+        </is>
       </c>
       <c r="J53" t="inlineStr">
         <is>
@@ -2244,41 +2213,31 @@
         </is>
       </c>
       <c r="L53" t="n">
-        <v>900</v>
+        <v>400</v>
       </c>
       <c r="O53" t="n">
         <v>1</v>
       </c>
       <c r="P53" t="inlineStr">
         <is>
-          <t>Ho fermato il tempo! | Resta immobile per {n} turno, poi verrò con te.</t>
+          <t>Freeza ha ucciso Krilin: per questo sono diventato Super Saiyan. | Batti {obiettivo} e combatterò al tuo fianco.</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Butter</t>
+          <t>Nail</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>combattimento</t>
-        </is>
-      </c>
-      <c r="C54" t="inlineStr">
-        <is>
-          <t>2v2</t>
-        </is>
-      </c>
-      <c r="D54" t="inlineStr">
-        <is>
-          <t>vincere</t>
-        </is>
-      </c>
-      <c r="E54" t="inlineStr">
-        <is>
-          <t>Butter | Jeeth</t>
+          <t>batti</t>
+        </is>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>Zarbon</t>
         </is>
       </c>
       <c r="J54" t="inlineStr">
@@ -2294,14 +2253,14 @@
       </c>
       <c r="P54" t="inlineStr">
         <is>
-          <t>Sono il guerriero più veloce dell'universo! | Battete me e Jeeth, e verrò con voi.</t>
+          <t>Il pianeta Nameck è in pericolo. | Batti {obiettivo} e combatterò per te.</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Jeeth</t>
+          <t>Zarbon</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -2311,17 +2270,12 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>2v2</t>
+          <t>1v1</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>vincere</t>
-        </is>
-      </c>
-      <c r="E55" t="inlineStr">
-        <is>
-          <t>Jeeth | Butter</t>
+          <t>trasformazione</t>
         </is>
       </c>
       <c r="J55" t="inlineStr">
@@ -2337,14 +2291,14 @@
       </c>
       <c r="P55" t="inlineStr">
         <is>
-          <t>Io e Butter colpiamo sempre in coppia. | Battete tutti e due e verrò con voi.</t>
+          <t>Non costringermi a mostrarti il mio vero aspetto! | Se ci riesci, verrò con te.</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Freeza (seconda forma)</t>
+          <t>Zarbon (trasformato)</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -2352,9 +2306,14 @@
           <t>combattimento</t>
         </is>
       </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>1v1</t>
+        </is>
+      </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>trasformazione</t>
+          <t>vincere</t>
         </is>
       </c>
       <c r="J56" t="inlineStr">
@@ -2370,14 +2329,14 @@
       </c>
       <c r="P56" t="inlineStr">
         <is>
-          <t>La mia potenza supera il milione. | Costringimi a trasformarmi di nuovo e verrò con te.</t>
+          <t>Ora vedrai il mio vero aspetto! | Battimi e verrò con te.</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Freeza (terza forma)</t>
+          <t>Dodoria</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -2385,9 +2344,19 @@
           <t>combattimento</t>
         </is>
       </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>2v2</t>
+        </is>
+      </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>trasformazione</t>
+          <t>vincere</t>
+        </is>
+      </c>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t>Dodoria | Zarbon</t>
         </is>
       </c>
       <c r="J57" t="inlineStr">
@@ -2403,14 +2372,14 @@
       </c>
       <c r="P57" t="inlineStr">
         <is>
-          <t>Questa forma non piace a nessuno, nemmeno a me. | Costringimi alla forma finale e verrò con te.</t>
+          <t>Zarbon, questi qui li sistemo io! | Battete me e Zarbon, e vi seguirò.</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Freeza (forma finale)</t>
+          <t>Ginyu</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -2418,9 +2387,19 @@
           <t>combattimento</t>
         </is>
       </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>2v2</t>
+        </is>
+      </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>trasformazione</t>
+          <t>vincere</t>
+        </is>
+      </c>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t>Recoome | Guldo</t>
         </is>
       </c>
       <c r="J58" t="inlineStr">
@@ -2436,29 +2415,29 @@
       </c>
       <c r="P58" t="inlineStr">
         <is>
-          <t>Finora ho usato solo una parte della mia forza. | Costringimi alla massima potenza e Freeza combatterà per te.</t>
+          <t>Squadra Ginyu, in posizione! | Battete Recoome e Guldo e sarò dei vostri.</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Trunks (spada)</t>
+          <t>Recoome</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>vai da</t>
-        </is>
-      </c>
-      <c r="F59" t="inlineStr">
-        <is>
-          <t>Son Goku (metà) SSJ</t>
-        </is>
-      </c>
-      <c r="G59" t="inlineStr">
-        <is>
-          <t>sì</t>
+          <t>combattimento</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>1v1</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>vincere</t>
         </is>
       </c>
       <c r="J59" t="inlineStr">
@@ -2474,25 +2453,23 @@
       </c>
       <c r="P59" t="inlineStr">
         <is>
-          <t>Vengo dal futuro con un avvertimento per Son Goku. | Vai da {obiettivo} e torna: poi combatterò con te.</t>
+          <t>Recoome Ultra Fighting Bomber! | Battimi e passo dalla tua parte.</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Trunks (spada) SSJ</t>
+          <t>Guldo</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>batti</t>
-        </is>
-      </c>
-      <c r="F60" t="inlineStr">
-        <is>
-          <t>Mecha Freeza</t>
-        </is>
+          <t>salta turni</t>
+        </is>
+      </c>
+      <c r="H60" t="n">
+        <v>1</v>
       </c>
       <c r="J60" t="inlineStr">
         <is>
@@ -2500,31 +2477,41 @@
         </is>
       </c>
       <c r="L60" t="n">
-        <v>400</v>
+        <v>900</v>
       </c>
       <c r="O60" t="n">
         <v>1</v>
       </c>
       <c r="P60" t="inlineStr">
         <is>
-          <t>Freeza è tornato, ricostruito come una macchina. | Batti {obiettivo} e la mia spada sarà tua.</t>
+          <t>Ho fermato il tempo! | Resta immobile per {n} turno, poi verrò con te.</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Mecha Freeza</t>
+          <t>Butter</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>porta</t>
-        </is>
-      </c>
-      <c r="F61" t="inlineStr">
-        <is>
-          <t>Re Cold</t>
+          <t>combattimento</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>2v2</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>vincere</t>
+        </is>
+      </c>
+      <c r="E61" t="inlineStr">
+        <is>
+          <t>Butter | Jeeth</t>
         </is>
       </c>
       <c r="J61" t="inlineStr">
@@ -2540,24 +2527,34 @@
       </c>
       <c r="P61" t="inlineStr">
         <is>
-          <t>Mio padre mi ha ricostruito: ora voglio vendetta. | Portami {obiettivo} e verrò con te.</t>
+          <t>Sono il guerriero più veloce dell'universo! | Battete me e Jeeth, e verrò con voi.</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Trunks</t>
+          <t>Butter</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>porta</t>
-        </is>
-      </c>
-      <c r="F62" t="inlineStr">
-        <is>
-          <t>Vegeta</t>
+          <t>combattimento</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>2v2</t>
+        </is>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>vincere</t>
+        </is>
+      </c>
+      <c r="E62" t="inlineStr">
+        <is>
+          <t>Butter | Jeeth</t>
         </is>
       </c>
       <c r="J62" t="inlineStr">
@@ -2568,29 +2565,44 @@
       <c r="L62" t="n">
         <v>400</v>
       </c>
+      <c r="N62" t="inlineStr">
+        <is>
+          <t>Freeza (forma finale)</t>
+        </is>
+      </c>
       <c r="O62" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="P62" t="inlineStr">
         <is>
-          <t>Nel mio futuro non ho mai conosciuto mio padre. | Portami {obiettivo} e verrò con te.</t>
+          <t>Il grande Freeza non vuole essere disturbato! | Battete me e Jeeth, e la strada per Freeza sarà aperta.</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Trunks SSJ</t>
+          <t>Jeeth</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>batti</t>
-        </is>
-      </c>
-      <c r="F63" t="inlineStr">
-        <is>
-          <t>Cell (prima forma)</t>
+          <t>combattimento</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>2v2</t>
+        </is>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>vincere</t>
+        </is>
+      </c>
+      <c r="E63" t="inlineStr">
+        <is>
+          <t>Jeeth | Butter</t>
         </is>
       </c>
       <c r="J63" t="inlineStr">
@@ -2606,24 +2618,24 @@
       </c>
       <c r="P63" t="inlineStr">
         <is>
-          <t>Cell viene dal mio futuro: là ha già vinto. | Batti {obiettivo} prima che diventi perfetto, e verrò con te.</t>
+          <t>Io e Butter colpiamo sempre in coppia. | Battete tutti e due e verrò con voi.</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Super Trunks</t>
+          <t>Freeza (seconda forma)</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>batti</t>
-        </is>
-      </c>
-      <c r="F64" t="inlineStr">
-        <is>
-          <t>Cell (forma perfetta)</t>
+          <t>combattimento</t>
+        </is>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>trasformazione</t>
         </is>
       </c>
       <c r="J64" t="inlineStr">
@@ -2639,23 +2651,25 @@
       </c>
       <c r="P64" t="inlineStr">
         <is>
-          <t>Ho più muscoli di Cell, ma sono troppo lento. | Batti {obiettivo} e verrò con te.</t>
+          <t>La mia potenza supera il milione. | Costringimi a trasformarmi di nuovo e verrò con te.</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Vegeta</t>
+          <t>Freeza (terza forma)</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>salta turni</t>
-        </is>
-      </c>
-      <c r="H65" t="n">
-        <v>1</v>
+          <t>combattimento</t>
+        </is>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>trasformazione</t>
+        </is>
       </c>
       <c r="J65" t="inlineStr">
         <is>
@@ -2663,31 +2677,41 @@
         </is>
       </c>
       <c r="L65" t="n">
-        <v>900</v>
+        <v>400</v>
       </c>
       <c r="O65" t="n">
         <v>1</v>
       </c>
       <c r="P65" t="inlineStr">
         <is>
-          <t>Mi alleno nella stanza della gravità di Bulma. | Allenati con me per {n} turno e verrò con te.</t>
+          <t>Questa forma non piace a nessuno, nemmeno a me. | Costringimi alla forma finale e verrò con te.</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Vegeta SSJ</t>
+          <t>Freeza (forma finale)</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>batti</t>
-        </is>
-      </c>
-      <c r="F66" t="inlineStr">
-        <is>
-          <t>C-19</t>
+          <t>combattimento</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>2v2</t>
+        </is>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>vincere</t>
+        </is>
+      </c>
+      <c r="E66" t="inlineStr">
+        <is>
+          <t>Freeza (forma finale) | Re Cold</t>
         </is>
       </c>
       <c r="J66" t="inlineStr">
@@ -2703,24 +2727,24 @@
       </c>
       <c r="P66" t="inlineStr">
         <is>
-          <t>Sono diventato Super Saiyan anch'io. | Dimostrami che sei alla mia altezza: batti {obiettivo}.</t>
+          <t>Papà, guarda come tratto questi insetti. | Battete me e mio padre, e vi servirò.</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Super Vegeta</t>
+          <t>Trunks (spada)</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>batti</t>
+          <t>porta</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Cell (forma perfetta)</t>
+          <t>Son Goku (metà)</t>
         </is>
       </c>
       <c r="J67" t="inlineStr">
@@ -2736,23 +2760,25 @@
       </c>
       <c r="P67" t="inlineStr">
         <is>
-          <t>Ho lasciato che Cell diventasse perfetto, per batterlo al suo meglio. | Batti {obiettivo} e verrò con te.</t>
+          <t>Vengo dal futuro: devo parlare con Son Goku. | Portami {obiettivo} e verrò con te.</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Son Gohan (ragazzo)</t>
+          <t>Trunks (spada) SSJ</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>salta turni</t>
-        </is>
-      </c>
-      <c r="H68" t="n">
-        <v>1</v>
+          <t>batti</t>
+        </is>
+      </c>
+      <c r="F68" t="inlineStr">
+        <is>
+          <t>Mecha Freeza</t>
+        </is>
       </c>
       <c r="J68" t="inlineStr">
         <is>
@@ -2760,31 +2786,41 @@
         </is>
       </c>
       <c r="L68" t="n">
-        <v>900</v>
+        <v>400</v>
       </c>
       <c r="O68" t="n">
         <v>1</v>
       </c>
       <c r="P68" t="inlineStr">
         <is>
-          <t>Papà mi allena nella Stanza dello Spirito e del Tempo. | Entra con noi per {n} turno e poi verrò con te.</t>
+          <t>Freeza è tornato, ricostruito come una macchina. | Batti {obiettivo} e la mia spada sarà tua.</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Son Gohan (ragazzo) SSJ</t>
+          <t>Mecha Freeza</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>batti</t>
-        </is>
-      </c>
-      <c r="F69" t="inlineStr">
-        <is>
-          <t>Cell Jr.</t>
+          <t>combattimento</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>2v2</t>
+        </is>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>vincere</t>
+        </is>
+      </c>
+      <c r="E69" t="inlineStr">
+        <is>
+          <t>Mecha Freeza | Re Cold</t>
         </is>
       </c>
       <c r="J69" t="inlineStr">
@@ -2800,24 +2836,34 @@
       </c>
       <c r="P69" t="inlineStr">
         <is>
-          <t>Cell ha liberato i suoi figli. | Batti {obiettivo} e combatterò al tuo fianco.</t>
+          <t>Mio padre mi ha ricostruito: ora voglio vendetta. | Battete me e mio padre, e vi seguirò.</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Son Gohan (ragazzo) SSJ2</t>
+          <t>Re Cold</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>batti</t>
-        </is>
-      </c>
-      <c r="F70" t="inlineStr">
-        <is>
-          <t>Cell (forma perfetta)</t>
+          <t>combattimento</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>2v2</t>
+        </is>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>vincere</t>
+        </is>
+      </c>
+      <c r="E70" t="inlineStr">
+        <is>
+          <t>Re Cold | Mecha Freeza</t>
         </is>
       </c>
       <c r="J70" t="inlineStr">
@@ -2833,24 +2879,24 @@
       </c>
       <c r="P70" t="inlineStr">
         <is>
-          <t>Papà dice che tocca a me. | Batti {obiettivo} e combatterò per te.</t>
+          <t>Mio figlio è tornato più forte di prima. | Battete me e Freeza, e vi seguirò.</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Piccolo (fine)</t>
+          <t>Trunks</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>batti</t>
+          <t>porta</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>C-17</t>
+          <t>Vegeta</t>
         </is>
       </c>
       <c r="J71" t="inlineStr">
@@ -2866,24 +2912,24 @@
       </c>
       <c r="P71" t="inlineStr">
         <is>
-          <t>Mi sono fuso con Kami per affrontare i cyborg. | Batti {obiettivo} e combatterò al tuo fianco.</t>
+          <t>Nel mio futuro non ho mai conosciuto mio padre. | Portami {obiettivo} e verrò con te.</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>C-17</t>
+          <t>Trunks SSJ</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>porta</t>
+          <t>batti</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>C-16</t>
+          <t>Cell (prima forma)</t>
         </is>
       </c>
       <c r="J72" t="inlineStr">
@@ -2899,24 +2945,24 @@
       </c>
       <c r="P72" t="inlineStr">
         <is>
-          <t>Abbiamo svegliato C-16: è uno strano tipo, ma è dei nostri. | Portami {obiettivo} e verrò con te.</t>
+          <t>Cell viene dal mio futuro: là ha già vinto. | Batti {obiettivo} prima che diventi perfetto, e verrò con te.</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>C-18</t>
+          <t>Super Trunks</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>porta</t>
+          <t>batti</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Krilin</t>
+          <t>Cell (forma perfetta)</t>
         </is>
       </c>
       <c r="J73" t="inlineStr">
@@ -2932,25 +2978,23 @@
       </c>
       <c r="P73" t="inlineStr">
         <is>
-          <t>Quel piccoletto pelato... non riesco a togliermelo dalla testa. | Portami {obiettivo} e verrò con te.</t>
+          <t>Ho più muscoli di Cell, ma sono troppo lento. | Batti {obiettivo} e verrò con te.</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>C-18</t>
+          <t>Vegeta</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>porta</t>
-        </is>
-      </c>
-      <c r="F74" t="inlineStr">
-        <is>
-          <t>C-17</t>
-        </is>
+          <t>salta turni</t>
+        </is>
+      </c>
+      <c r="H74" t="n">
+        <v>1</v>
       </c>
       <c r="J74" t="inlineStr">
         <is>
@@ -2958,36 +3002,31 @@
         </is>
       </c>
       <c r="L74" t="n">
-        <v>400</v>
+        <v>900</v>
       </c>
       <c r="O74" t="n">
         <v>1</v>
       </c>
       <c r="P74" t="inlineStr">
         <is>
-          <t>Io e mio fratello non ci separiamo. | Portami {obiettivo} e combatterò per te.</t>
+          <t>Mi alleno nella stanza della gravità di Bulma. | Allenati con me per {n} turno e verrò con te.</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>C-16</t>
+          <t>Vegeta SSJ</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>vai da</t>
+          <t>batti</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Son Gohan (ragazzo)</t>
-        </is>
-      </c>
-      <c r="G75" t="inlineStr">
-        <is>
-          <t>sì</t>
+          <t>C-19</t>
         </is>
       </c>
       <c r="J75" t="inlineStr">
@@ -3003,14 +3042,14 @@
       </c>
       <c r="P75" t="inlineStr">
         <is>
-          <t>Gli uccelli e gli animali di questo pianeta vanno protetti. | Porta il mio messaggio a {obiettivo} e torna: poi combatterò con te.</t>
+          <t>Sono diventato Super Saiyan anch'io. | Dimostrami che sei alla mia altezza: batti {obiettivo}.</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>C-19</t>
+          <t>Super Vegeta</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -3020,7 +3059,7 @@
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Son Goku (metà) SSJ</t>
+          <t>Cell (forma perfetta)</t>
         </is>
       </c>
       <c r="J76" t="inlineStr">
@@ -3036,25 +3075,23 @@
       </c>
       <c r="P76" t="inlineStr">
         <is>
-          <t>Il dottor Gero vuole Son Goku. Io voglio la sua energia. | Batti {obiettivo} e verrò con te.</t>
+          <t>Ho lasciato che Cell diventasse perfetto, per batterlo al suo meglio. | Batti {obiettivo} e verrò con te.</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>Dr. Gero (C-20)</t>
+          <t>Son Gohan (ragazzo)</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>batti</t>
-        </is>
-      </c>
-      <c r="F77" t="inlineStr">
-        <is>
-          <t>Son Goku (metà)</t>
-        </is>
+          <t>salta turni</t>
+        </is>
+      </c>
+      <c r="H77" t="n">
+        <v>1</v>
       </c>
       <c r="J77" t="inlineStr">
         <is>
@@ -3062,31 +3099,31 @@
         </is>
       </c>
       <c r="L77" t="n">
-        <v>400</v>
+        <v>900</v>
       </c>
       <c r="O77" t="n">
         <v>1</v>
       </c>
       <c r="P77" t="inlineStr">
         <is>
-          <t>Son Goku ha distrutto il mio esercito del Red Ribbon. | Batti {obiettivo} e i miei cyborg saranno tuoi.</t>
+          <t>Papà mi allena nella Stanza dello Spirito e del Tempo. | Entra con noi per {n} turno e poi verrò con te.</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>Cell (seconda forma)</t>
+          <t>Son Gohan (ragazzo) SSJ</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>combattimento</t>
-        </is>
-      </c>
-      <c r="D78" t="inlineStr">
-        <is>
-          <t>trasformazione</t>
+          <t>batti</t>
+        </is>
+      </c>
+      <c r="F78" t="inlineStr">
+        <is>
+          <t>Cell (forma perfetta)</t>
         </is>
       </c>
       <c r="J78" t="inlineStr">
@@ -3102,36 +3139,26 @@
       </c>
       <c r="P78" t="inlineStr">
         <is>
-          <t>Ho assorbito C-17. Me ne manca solo una. | Costringimi a trasformarmi e verrò con te.</t>
+          <t>I Cell Jr. non mi fanno paura. | Batti {obiettivo} e verrò con te.</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
+          <t>Son Gohan (ragazzo) SSJ2</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>batti</t>
+        </is>
+      </c>
+      <c r="F79" t="inlineStr">
+        <is>
           <t>Cell (forma perfetta)</t>
         </is>
       </c>
-      <c r="B79" t="inlineStr">
-        <is>
-          <t>combattimento</t>
-        </is>
-      </c>
-      <c r="C79" t="inlineStr">
-        <is>
-          <t>2v2</t>
-        </is>
-      </c>
-      <c r="D79" t="inlineStr">
-        <is>
-          <t>vincere</t>
-        </is>
-      </c>
-      <c r="E79" t="inlineStr">
-        <is>
-          <t>Cell (forma perfetta) | Cell Jr.</t>
-        </is>
-      </c>
       <c r="J79" t="inlineStr">
         <is>
           <t>sì</t>
@@ -3145,24 +3172,24 @@
       </c>
       <c r="P79" t="inlineStr">
         <is>
-          <t>Ti presento mio figlio. | Battete noi due, e verrò con voi.</t>
+          <t>Papà dice che tocca a me. | Batti {obiettivo} e combatterò per te.</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>Son Gohan (futuro)</t>
+          <t>Piccolo (fine)</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>porta</t>
+          <t>batti</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Trunks (spada)</t>
+          <t>C-17</t>
         </is>
       </c>
       <c r="J80" t="inlineStr">
@@ -3178,24 +3205,34 @@
       </c>
       <c r="P80" t="inlineStr">
         <is>
-          <t>Nel mio futuro i cyborg hanno distrutto tutto: mi resta solo Trunks. | Portami {obiettivo} e combatteremo insieme.</t>
+          <t>Mi sono fuso con Kami per affrontare i cyborg. | Batti {obiettivo} e combatterò al tuo fianco.</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>Son Gohan (futuro) SSJ</t>
+          <t>C-17</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>batti</t>
-        </is>
-      </c>
-      <c r="F81" t="inlineStr">
-        <is>
-          <t>C-18</t>
+          <t>combattimento</t>
+        </is>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>2v2</t>
+        </is>
+      </c>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t>vincere</t>
+        </is>
+      </c>
+      <c r="E81" t="inlineStr">
+        <is>
+          <t>C-17 | C-18</t>
         </is>
       </c>
       <c r="J81" t="inlineStr">
@@ -3211,24 +3248,34 @@
       </c>
       <c r="P81" t="inlineStr">
         <is>
-          <t>C-17 e C-18 seminano il terrore nel mio tempo. | Batti {obiettivo} e verrò con te.</t>
+          <t>Io e mia sorella non obbediamo a nessuno. | Battete me e C-18, e vi seguirò.</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>Cooler (forma finale)</t>
+          <t>C-17</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>batti</t>
-        </is>
-      </c>
-      <c r="F82" t="inlineStr">
-        <is>
-          <t>Son Goku (metà) SSJ</t>
+          <t>combattimento</t>
+        </is>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>2v2</t>
+        </is>
+      </c>
+      <c r="D82" t="inlineStr">
+        <is>
+          <t>vincere</t>
+        </is>
+      </c>
+      <c r="E82" t="inlineStr">
+        <is>
+          <t>C-17 | C-18</t>
         </is>
       </c>
       <c r="J82" t="inlineStr">
@@ -3239,29 +3286,44 @@
       <c r="L82" t="n">
         <v>400</v>
       </c>
+      <c r="N82" t="inlineStr">
+        <is>
+          <t>Cell (prima forma)</t>
+        </is>
+      </c>
       <c r="O82" t="n">
         <v>1</v>
       </c>
       <c r="P82" t="inlineStr">
         <is>
-          <t>Il Saiyan che ha battuto mio fratello deve pagare. | Batti {obiettivo} e verrò con te.</t>
+          <t>Cell ci sta cercando, ma noi non abbiamo paura. | Battete me e C-18, e la strada per Cell sarà aperta.</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>C-13</t>
+          <t>C-18</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>batti</t>
-        </is>
-      </c>
-      <c r="F83" t="inlineStr">
-        <is>
-          <t>Son Goku (metà) SSJ</t>
+          <t>combattimento</t>
+        </is>
+      </c>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>2v2</t>
+        </is>
+      </c>
+      <c r="D83" t="inlineStr">
+        <is>
+          <t>vincere</t>
+        </is>
+      </c>
+      <c r="E83" t="inlineStr">
+        <is>
+          <t>C-18 | C-17</t>
         </is>
       </c>
       <c r="J83" t="inlineStr">
@@ -3277,24 +3339,34 @@
       </c>
       <c r="P83" t="inlineStr">
         <is>
-          <t>Il dottor Gero mi ha costruito per un solo scopo. | Batti {obiettivo} e combatterò per te.</t>
+          <t>Mio fratello e io ci annoiamo. | Battete tutti e due e verrò con voi.</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>Turles</t>
+          <t>C-16</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>batti</t>
-        </is>
-      </c>
-      <c r="F84" t="inlineStr">
-        <is>
-          <t>Son Goku (metà)</t>
+          <t>combattimento</t>
+        </is>
+      </c>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>3v3</t>
+        </is>
+      </c>
+      <c r="D84" t="inlineStr">
+        <is>
+          <t>vincere</t>
+        </is>
+      </c>
+      <c r="E84" t="inlineStr">
+        <is>
+          <t>C-16 | C-17 | C-18</t>
         </is>
       </c>
       <c r="J84" t="inlineStr">
@@ -3310,14 +3382,14 @@
       </c>
       <c r="P84" t="inlineStr">
         <is>
-          <t>Kakaroth e io sembriamo gemelli, ma il cattivo sono io. | Batti {obiettivo} e verrò con te.</t>
+          <t>Non voglio combattere... ma C-17 e C-18 non mi lasciano scelta. | Battete tutti e tre e verrò con voi.</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>Slug</t>
+          <t>C-19</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -3325,9 +3397,19 @@
           <t>combattimento</t>
         </is>
       </c>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>2v2</t>
+        </is>
+      </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>trasformazione</t>
+          <t>vincere</t>
+        </is>
+      </c>
+      <c r="E85" t="inlineStr">
+        <is>
+          <t>C-19 | Dr. Gero (C-20)</t>
         </is>
       </c>
       <c r="J85" t="inlineStr">
@@ -3343,14 +3425,14 @@
       </c>
       <c r="P85" t="inlineStr">
         <is>
-          <t>Il mio vero potere ha dimensioni enormi. | Costringimi a diventare gigante e verrò con te.</t>
+          <t>Assorbirò la vostra energia. | Battete me e il dottor Gero, e vi seguirò.</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>Broli</t>
+          <t>Dr. Gero (C-20)</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -3358,9 +3440,19 @@
           <t>combattimento</t>
         </is>
       </c>
+      <c r="C86" t="inlineStr">
+        <is>
+          <t>2v2</t>
+        </is>
+      </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>trasformazione</t>
+          <t>vincere</t>
+        </is>
+      </c>
+      <c r="E86" t="inlineStr">
+        <is>
+          <t>Dr. Gero (C-20) | C-19</t>
         </is>
       </c>
       <c r="J86" t="inlineStr">
@@ -3376,24 +3468,24 @@
       </c>
       <c r="P86" t="inlineStr">
         <is>
-          <t>Kakaroth... KAKAROTH! | Se mi fai trasformare, ti seguirò.</t>
+          <t>Ho studiato Son Goku per anni. | Battete me e C-19, e lavorerò per voi.</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>Broli SSJ</t>
+          <t>Cell (seconda forma)</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>batti</t>
-        </is>
-      </c>
-      <c r="F87" t="inlineStr">
-        <is>
-          <t>Son Gohan (ragazzo) SSJ</t>
+          <t>combattimento</t>
+        </is>
+      </c>
+      <c r="D87" t="inlineStr">
+        <is>
+          <t>trasformazione</t>
         </is>
       </c>
       <c r="J87" t="inlineStr">
@@ -3409,24 +3501,34 @@
       </c>
       <c r="P87" t="inlineStr">
         <is>
-          <t>Quel moccioso di Kakaroth mi ha già sfidato una volta. | Batti {obiettivo} e verrò con te.</t>
+          <t>Ho assorbito C-17. Me ne manca solo una. | Costringimi a trasformarmi e verrò con te.</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>Zangya</t>
+          <t>Cell (forma perfetta)</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>batti</t>
-        </is>
-      </c>
-      <c r="F88" t="inlineStr">
-        <is>
-          <t>Son Gohan (ragazzo)</t>
+          <t>combattimento</t>
+        </is>
+      </c>
+      <c r="C88" t="inlineStr">
+        <is>
+          <t>2v2</t>
+        </is>
+      </c>
+      <c r="D88" t="inlineStr">
+        <is>
+          <t>vincere</t>
+        </is>
+      </c>
+      <c r="E88" t="inlineStr">
+        <is>
+          <t>Cell (forma perfetta) | Cell Jr.</t>
         </is>
       </c>
       <c r="J88" t="inlineStr">
@@ -3442,14 +3544,14 @@
       </c>
       <c r="P88" t="inlineStr">
         <is>
-          <t>Bojack mi ha mandato a sfidare il ragazzo che ha battuto Cell. | Batti {obiettivo} e verrò con te.</t>
+          <t>Ti presento mio figlio. | Battete noi due, e verrò con voi.</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>Bojack</t>
+          <t>Son Gohan (futuro)</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -3459,7 +3561,7 @@
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Zangya</t>
+          <t>Trunks (spada)</t>
         </is>
       </c>
       <c r="J89" t="inlineStr">
@@ -3475,14 +3577,14 @@
       </c>
       <c r="P89" t="inlineStr">
         <is>
-          <t>La mia squadra non lascia indietro nessuno. | Portami {obiettivo} e combatterò per te.</t>
+          <t>Nel mio futuro i cyborg hanno distrutto tutto: mi resta solo Trunks. | Portami {obiettivo} e combatteremo insieme.</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>Bojack (massima potenza)</t>
+          <t>Son Gohan (futuro) SSJ</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -3492,7 +3594,7 @@
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Son Gohan (ragazzo) SSJ2</t>
+          <t>C-18</t>
         </is>
       </c>
       <c r="J90" t="inlineStr">
@@ -3508,14 +3610,14 @@
       </c>
       <c r="P90" t="inlineStr">
         <is>
-          <t>Solo il ragazzo di Cell mi ha messo in difficoltà. | Batti {obiettivo} e verrò con te.</t>
+          <t>C-17 e C-18 seminano il terrore nel mio tempo. | Batti {obiettivo} e verrò con te.</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>Janemba</t>
+          <t>Cooler (forma finale)</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
@@ -3523,9 +3625,14 @@
           <t>combattimento</t>
         </is>
       </c>
+      <c r="C91" t="inlineStr">
+        <is>
+          <t>1v1</t>
+        </is>
+      </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>trasformazione</t>
+          <t>vincere</t>
         </is>
       </c>
       <c r="J91" t="inlineStr">
@@ -3541,24 +3648,24 @@
       </c>
       <c r="P91" t="inlineStr">
         <is>
-          <t>Il mondo dei morti è sottosopra per colpa mia! | Costringimi a trasformarmi e verrò con te.</t>
+          <t>Ora conoscerai la mia forma finale! | Battimi e verrò con te.</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>Paikuhan</t>
+          <t>C-13</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>batti</t>
-        </is>
-      </c>
-      <c r="F92" t="inlineStr">
-        <is>
-          <t>Janemba</t>
+          <t>combattimento</t>
+        </is>
+      </c>
+      <c r="D92" t="inlineStr">
+        <is>
+          <t>trasformazione</t>
         </is>
       </c>
       <c r="J92" t="inlineStr">
@@ -3574,24 +3681,24 @@
       </c>
       <c r="P92" t="inlineStr">
         <is>
-          <t>Nell'aldilà nessuno riesce a fermare Janemba. | Batti {obiettivo} e combatterò con te.</t>
+          <t>Il dottor Gero mi ha programmato per una cosa sola. | Costringimi a trasformarmi e ti seguirò.</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>Super Gogeta</t>
+          <t>Turles</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>batti</t>
-        </is>
-      </c>
-      <c r="F93" t="inlineStr">
-        <is>
-          <t>Super Janemba</t>
+          <t>combattimento</t>
+        </is>
+      </c>
+      <c r="D93" t="inlineStr">
+        <is>
+          <t>trasformazione</t>
         </is>
       </c>
       <c r="J93" t="inlineStr">
@@ -3607,24 +3714,24 @@
       </c>
       <c r="P93" t="inlineStr">
         <is>
-          <t>Goku e Vegeta, fusi per salvare l'aldilà. | Batti {obiettivo} e combatterò con te.</t>
+          <t>L'albero della potenza mi rende invincibile! | Costringimi a trasformarmi e ti seguirò.</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>Tapion</t>
+          <t>Slug</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>batti</t>
-        </is>
-      </c>
-      <c r="F94" t="inlineStr">
-        <is>
-          <t>Hildegarn</t>
+          <t>combattimento</t>
+        </is>
+      </c>
+      <c r="D94" t="inlineStr">
+        <is>
+          <t>trasformazione</t>
         </is>
       </c>
       <c r="J94" t="inlineStr">
@@ -3640,14 +3747,14 @@
       </c>
       <c r="P94" t="inlineStr">
         <is>
-          <t>Il demone Hildegarn sta per risvegliarsi. | Batti {obiettivo} e il mio flauto suonerà per te.</t>
+          <t>Il mio vero potere ha dimensioni enormi. | Costringimi a diventare gigante e verrò con te.</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>Hildegarn</t>
+          <t>Broli</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
@@ -3655,14 +3762,9 @@
           <t>combattimento</t>
         </is>
       </c>
-      <c r="C95" t="inlineStr">
-        <is>
-          <t>3v3</t>
-        </is>
-      </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>vincere</t>
+          <t>trasformazione</t>
         </is>
       </c>
       <c r="J95" t="inlineStr">
@@ -3678,14 +3780,14 @@
       </c>
       <c r="P95" t="inlineStr">
         <is>
-          <t>GROOOAAAR! | Battilo con tre guerrieri e il demone sarà tuo.</t>
+          <t>Kakaroth... KAKAROTH! | Se mi fai trasformare, ti seguirò.</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>Arale</t>
+          <t>Broli SSJ</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
@@ -3695,7 +3797,7 @@
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>vincere</t>
+          <t>trasformazione</t>
         </is>
       </c>
       <c r="J96" t="inlineStr">
@@ -3711,29 +3813,29 @@
       </c>
       <c r="P96" t="inlineStr">
         <is>
-          <t>Ncha! Giochiamo a fare la lotta? | Battimi e vengo con te!</t>
+          <t>Kakaroth... KAKAROTH! | Costringimi a trasformarmi e verrò con te.</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>Son Goku (fine)</t>
+          <t>Zangya</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>vai da</t>
-        </is>
-      </c>
-      <c r="F97" t="inlineStr">
-        <is>
-          <t>Son Goten</t>
-        </is>
-      </c>
-      <c r="G97" t="inlineStr">
-        <is>
-          <t>sì</t>
+          <t>combattimento</t>
+        </is>
+      </c>
+      <c r="C97" t="inlineStr">
+        <is>
+          <t>1v1</t>
+        </is>
+      </c>
+      <c r="D97" t="inlineStr">
+        <is>
+          <t>vincere</t>
         </is>
       </c>
       <c r="J97" t="inlineStr">
@@ -3749,24 +3851,34 @@
       </c>
       <c r="P97" t="inlineStr">
         <is>
-          <t>Ho un giorno solo sulla Terra e non ho mai visto mio figlio Goten. | Vai da {obiettivo} e torna: poi verrò con te.</t>
+          <t>Bojack ci ha liberati: ora la Terra è nostra. | Battimi e ti seguirò.</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>Son Goku (fine) SSJ</t>
+          <t>Bojack</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>batti</t>
-        </is>
-      </c>
-      <c r="F98" t="inlineStr">
-        <is>
-          <t>Majin Vegeta</t>
+          <t>combattimento</t>
+        </is>
+      </c>
+      <c r="C98" t="inlineStr">
+        <is>
+          <t>2v2</t>
+        </is>
+      </c>
+      <c r="D98" t="inlineStr">
+        <is>
+          <t>vincere</t>
+        </is>
+      </c>
+      <c r="E98" t="inlineStr">
+        <is>
+          <t>Bojack | Zangya</t>
         </is>
       </c>
       <c r="J98" t="inlineStr">
@@ -3782,57 +3894,67 @@
       </c>
       <c r="P98" t="inlineStr">
         <is>
-          <t>Vegeta si è fatto controllare da Bobbidi pur di combattere con me. | Batti {obiettivo} e verrò con te.</t>
+          <t>Il mio gruppo è libero, finalmente. | Battete me e Zangya, e verrò con voi.</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>Son Goku (fine) SSJ3</t>
+          <t>Bojack</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>batti</t>
-        </is>
-      </c>
-      <c r="F99" t="inlineStr">
-        <is>
-          <t>Majin Buu (puro)</t>
-        </is>
-      </c>
-      <c r="J99" t="inlineStr">
-        <is>
-          <t>sì</t>
+          <t>combattimento</t>
+        </is>
+      </c>
+      <c r="C99" t="inlineStr">
+        <is>
+          <t>1v1</t>
+        </is>
+      </c>
+      <c r="D99" t="inlineStr">
+        <is>
+          <t>trasformazione</t>
         </is>
       </c>
       <c r="L99" t="n">
-        <v>400</v>
+        <v>1200</v>
+      </c>
+      <c r="N99" t="inlineStr">
+        <is>
+          <t>Bojack (massima potenza)</t>
+        </is>
       </c>
       <c r="O99" t="n">
         <v>1</v>
       </c>
       <c r="P99" t="inlineStr">
         <is>
-          <t>Majin Bu è tornato alla sua forma originale: la più pericolosa. | Batti {obiettivo} e verrò con te.</t>
+          <t>Il mio vero potere ti spazzerà via. | Costringimi a trasformarmi: ti lascerò passare e avrai {monete} monete.</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>Majin Vegeta</t>
+          <t>Bojack (massima potenza)</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>batti</t>
-        </is>
-      </c>
-      <c r="F100" t="inlineStr">
-        <is>
-          <t>Son Goku (fine) SSJ2</t>
+          <t>combattimento</t>
+        </is>
+      </c>
+      <c r="C100" t="inlineStr">
+        <is>
+          <t>1v1</t>
+        </is>
+      </c>
+      <c r="D100" t="inlineStr">
+        <is>
+          <t>vincere</t>
         </is>
       </c>
       <c r="J100" t="inlineStr">
@@ -3848,24 +3970,24 @@
       </c>
       <c r="P100" t="inlineStr">
         <is>
-          <t>La mia sfida con Kakaroth non è mai finita. | Batti {obiettivo} e verrò con te.</t>
+          <t>Ora vedrai il mio vero potere! | Battimi e ti seguirò.</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>Vegeta (seconda forma)</t>
+          <t>Janemba</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>porta</t>
-        </is>
-      </c>
-      <c r="F101" t="inlineStr">
-        <is>
-          <t>Trunks (bambino)</t>
+          <t>combattimento</t>
+        </is>
+      </c>
+      <c r="D101" t="inlineStr">
+        <is>
+          <t>trasformazione</t>
         </is>
       </c>
       <c r="J101" t="inlineStr">
@@ -3881,62 +4003,57 @@
       </c>
       <c r="P101" t="inlineStr">
         <is>
-          <t>Trunks deve diventare più forte: lo alleno io. | Portami {obiettivo} e verrò con te.</t>
+          <t>Il mondo dei morti è sottosopra per colpa mia! | Costringimi a trasformarmi e verrò con te.</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>Trunks (bambino)</t>
+          <t>Janemba</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>vai da</t>
-        </is>
-      </c>
-      <c r="F102" t="inlineStr">
-        <is>
-          <t>Vegeta (seconda forma)</t>
-        </is>
-      </c>
-      <c r="G102" t="inlineStr">
-        <is>
-          <t>sì</t>
-        </is>
-      </c>
-      <c r="J102" t="inlineStr">
-        <is>
-          <t>sì</t>
+          <t>combattimento</t>
+        </is>
+      </c>
+      <c r="D102" t="inlineStr">
+        <is>
+          <t>trasformazione</t>
         </is>
       </c>
       <c r="L102" t="n">
-        <v>400</v>
+        <v>1200</v>
+      </c>
+      <c r="N102" t="inlineStr">
+        <is>
+          <t>Super Janemba</t>
+        </is>
       </c>
       <c r="O102" t="n">
         <v>1</v>
       </c>
       <c r="P102" t="inlineStr">
         <is>
-          <t>Papà mi ha promesso il parco giochi se lo batto. | Vai da {obiettivo} e torna: poi vengo con te.</t>
+          <t>L'inferno si sta riversando sulla Terra... | Costringimi a trasformarmi: ti lascerò passare e avrai {monete} monete.</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>Son Goten</t>
+          <t>Paikuhan</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>porta</t>
+          <t>batti</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Trunks (bambino)</t>
+          <t>Janemba</t>
         </is>
       </c>
       <c r="J103" t="inlineStr">
@@ -3952,24 +4069,24 @@
       </c>
       <c r="P103" t="inlineStr">
         <is>
-          <t>Senza Trunks non vengo da nessuna parte! | Portami {obiettivo} e veniamo tutti e due.</t>
+          <t>Nell'aldilà nessuno riesce a fermare Janemba. | Batti {obiettivo} e combatterò con te.</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>Son Goten SSJ</t>
+          <t>Super Gogeta</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>porta</t>
+          <t>batti</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Trunks (bambino) SSJ</t>
+          <t>Super Janemba</t>
         </is>
       </c>
       <c r="J104" t="inlineStr">
@@ -3985,29 +4102,24 @@
       </c>
       <c r="P104" t="inlineStr">
         <is>
-          <t>Io e Trunks abbiamo imparato la danza della fusione! | Portami {obiettivo} e la proviamo subito.</t>
+          <t>Goku e Vegeta, fusi per salvare l'aldilà. | Batti {obiettivo} e combatterò con te.</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>Son Gohan</t>
+          <t>Tapion</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>vai da</t>
+          <t>batti</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Videl</t>
-        </is>
-      </c>
-      <c r="G105" t="inlineStr">
-        <is>
-          <t>sì</t>
+          <t>Hildegarn</t>
         </is>
       </c>
       <c r="J105" t="inlineStr">
@@ -4023,24 +4135,29 @@
       </c>
       <c r="P105" t="inlineStr">
         <is>
-          <t>Ho promesso a Videl che le avrei insegnato a volare. | Vai da {obiettivo} e torna: poi verrò con te.</t>
+          <t>Il demone Hildegarn sta per risvegliarsi. | Batti {obiettivo} e il mio flauto suonerà per te.</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>Son Gohan SSJ</t>
+          <t>Tapion</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>batti</t>
-        </is>
-      </c>
-      <c r="F106" t="inlineStr">
-        <is>
-          <t>Dabura</t>
+          <t>combattimento</t>
+        </is>
+      </c>
+      <c r="C106" t="inlineStr">
+        <is>
+          <t>1v1</t>
+        </is>
+      </c>
+      <c r="D106" t="inlineStr">
+        <is>
+          <t>vincere</t>
         </is>
       </c>
       <c r="J106" t="inlineStr">
@@ -4051,29 +4168,39 @@
       <c r="L106" t="n">
         <v>400</v>
       </c>
+      <c r="N106" t="inlineStr">
+        <is>
+          <t>Hildegarn</t>
+        </is>
+      </c>
       <c r="O106" t="n">
         <v>1</v>
       </c>
       <c r="P106" t="inlineStr">
         <is>
-          <t>Dabura ha pietrificato Piccolo e Krilin. | Batti {obiettivo} e combatterò al tuo fianco.</t>
+          <t>È troppo pericoloso: se non riuscite a battere me, non avete speranze con lui. | Battimi e ti lascerò passare.</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>Son Gohan (Ultimate)</t>
+          <t>Hildegarn</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>batti</t>
-        </is>
-      </c>
-      <c r="F107" t="inlineStr">
-        <is>
-          <t>Super Buu</t>
+          <t>combattimento</t>
+        </is>
+      </c>
+      <c r="C107" t="inlineStr">
+        <is>
+          <t>3v3</t>
+        </is>
+      </c>
+      <c r="D107" t="inlineStr">
+        <is>
+          <t>vincere</t>
         </is>
       </c>
       <c r="J107" t="inlineStr">
@@ -4089,19 +4216,24 @@
       </c>
       <c r="P107" t="inlineStr">
         <is>
-          <t>Il Vecchio Kaioshin ha risvegliato tutto il mio potere. | Batti {obiettivo} e verrò con te.</t>
+          <t>GROOOAAAR! | Battilo con tre guerrieri e il demone sarà tuo.</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>Great Saiyaman</t>
+          <t>Arale</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>quiz</t>
+          <t>combattimento</t>
+        </is>
+      </c>
+      <c r="D108" t="inlineStr">
+        <is>
+          <t>vincere</t>
         </is>
       </c>
       <c r="J108" t="inlineStr">
@@ -4117,19 +4249,24 @@
       </c>
       <c r="P108" t="inlineStr">
         <is>
-          <t>La giustizia trionfa sempre! Io sono Great Saiyaman! | Rispondi giusto e combatterò al tuo fianco.</t>
+          <t>Ncha! Giochiamo a fare la lotta? | Battimi e vengo con te!</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>Great Saiyaman 2-go</t>
+          <t>Son Goku (fine)</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>quiz</t>
+          <t>porta</t>
+        </is>
+      </c>
+      <c r="F109" t="inlineStr">
+        <is>
+          <t>Son Goten</t>
         </is>
       </c>
       <c r="J109" t="inlineStr">
@@ -4145,29 +4282,24 @@
       </c>
       <c r="P109" t="inlineStr">
         <is>
-          <t>Anch'io combatto per la giustizia! | Rispondi giusto e verrò con te.</t>
+          <t>Non ho ancora conosciuto il mio secondo figlio! | Portami {obiettivo} e verrò con te.</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>Videl</t>
+          <t>Son Goku (fine) SSJ</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>vai da</t>
+          <t>batti</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Great Saiyaman</t>
-        </is>
-      </c>
-      <c r="G110" t="inlineStr">
-        <is>
-          <t>sì</t>
+          <t>Majin Vegeta</t>
         </is>
       </c>
       <c r="J110" t="inlineStr">
@@ -4183,14 +4315,14 @@
       </c>
       <c r="P110" t="inlineStr">
         <is>
-          <t>Chi si nasconde dietro Great Saiyaman? | Vai da {obiettivo} e torna a dirmelo: poi verrò con te.</t>
+          <t>Vegeta si è fatto controllare da Bobbidi pur di combattere con me. | Batti {obiettivo} e verrò con te.</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>Spopovitch</t>
+          <t>Son Goku (fine) SSJ3</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
@@ -4200,7 +4332,7 @@
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Videl</t>
+          <t>Majin Buu (puro)</t>
         </is>
       </c>
       <c r="J111" t="inlineStr">
@@ -4216,29 +4348,29 @@
       </c>
       <c r="P111" t="inlineStr">
         <is>
-          <t>Bobbidi mi ha dato una forza enorme. | Batti {obiettivo} e verrò con te.</t>
+          <t>Majin Bu è tornato alla sua forma originale: la più pericolosa. | Batti {obiettivo} e verrò con te.</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>Kaioshin</t>
+          <t>Majin Vegeta</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>vai da</t>
-        </is>
-      </c>
-      <c r="F112" t="inlineStr">
-        <is>
-          <t>Son Gohan</t>
-        </is>
-      </c>
-      <c r="G112" t="inlineStr">
-        <is>
-          <t>sì</t>
+          <t>combattimento</t>
+        </is>
+      </c>
+      <c r="C112" t="inlineStr">
+        <is>
+          <t>1v1</t>
+        </is>
+      </c>
+      <c r="D112" t="inlineStr">
+        <is>
+          <t>vincere</t>
         </is>
       </c>
       <c r="J112" t="inlineStr">
@@ -4254,24 +4386,24 @@
       </c>
       <c r="P112" t="inlineStr">
         <is>
-          <t>Il potere nascosto di Gohan va risvegliato. | Vai da {obiettivo} e torna a dirmi che è pronto: poi verrò con te.</t>
+          <t>Bobbidi mi ha dato ciò che volevo: il potere! | Battimi, se ci riesci, e verrò con te.</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>Kibitoshin</t>
+          <t>Vegeta (seconda forma)</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>batti</t>
+          <t>porta</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Dabura</t>
+          <t>Trunks (bambino)</t>
         </is>
       </c>
       <c r="J113" t="inlineStr">
@@ -4287,25 +4419,23 @@
       </c>
       <c r="P113" t="inlineStr">
         <is>
-          <t>Dabura serve Bobbidi: va fermato. | Batti {obiettivo} e ti aiuterò.</t>
+          <t>Trunks deve diventare più forte: lo alleno io. | Portami {obiettivo} e verrò con te.</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>Majin Buu (buono)</t>
+          <t>Trunks (bambino)</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>porta</t>
-        </is>
-      </c>
-      <c r="F114" t="inlineStr">
-        <is>
-          <t>Uub</t>
-        </is>
+          <t>attendi</t>
+        </is>
+      </c>
+      <c r="H114" t="n">
+        <v>2</v>
       </c>
       <c r="J114" t="inlineStr">
         <is>
@@ -4313,31 +4443,31 @@
         </is>
       </c>
       <c r="L114" t="n">
-        <v>400</v>
+        <v>1400</v>
       </c>
       <c r="O114" t="n">
         <v>1</v>
       </c>
       <c r="P114" t="inlineStr">
         <is>
-          <t>Bu sente che quel bambino, Uub, è come lui. | Portami {obiettivo} e Bu verrà con te.</t>
+          <t>Sto finendo l'allenamento nella stanza gravitazionale. | Ripassa tra {n} turni e verrò con te.</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>Super Buu</t>
+          <t>Son Goten</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>batti</t>
+          <t>porta</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Gotenks SSJ3</t>
+          <t>Trunks (bambino)</t>
         </is>
       </c>
       <c r="J115" t="inlineStr">
@@ -4353,24 +4483,24 @@
       </c>
       <c r="P115" t="inlineStr">
         <is>
-          <t>Quei due bambini fusi mi hanno fatto arrabbiare. | Batti {obiettivo} e Bu verrà con te.</t>
+          <t>Senza Trunks non vengo da nessuna parte! | Portami {obiettivo} e veniamo tutti e due.</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>Super Buu (Gotenks assorbito)</t>
+          <t>Son Goten SSJ</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>batti</t>
+          <t>porta</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Son Gohan (Ultimate)</t>
+          <t>Trunks (bambino) SSJ</t>
         </is>
       </c>
       <c r="J116" t="inlineStr">
@@ -4386,24 +4516,24 @@
       </c>
       <c r="P116" t="inlineStr">
         <is>
-          <t>Ora ho la forza di Gotenks e di Piccolo. | Batti {obiettivo} e verrò con te.</t>
+          <t>Io e Trunks abbiamo imparato la danza della fusione! | Portami {obiettivo} e la proviamo subito.</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>Vegetto</t>
+          <t>Son Gohan</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>batti</t>
+          <t>porta</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Super Buu (Son Gohan assorbito)</t>
+          <t>Videl</t>
         </is>
       </c>
       <c r="J117" t="inlineStr">
@@ -4419,24 +4549,24 @@
       </c>
       <c r="P117" t="inlineStr">
         <is>
-          <t>Io sono Vegetto: Goku e Vegeta in un solo guerriero. | Batti {obiettivo} e combatterò con te.</t>
+          <t>Videl vuole imparare a volare... | Portami {obiettivo} e verrò con te.</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>Uub</t>
+          <t>Son Gohan SSJ</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>combattimento</t>
-        </is>
-      </c>
-      <c r="D118" t="inlineStr">
-        <is>
-          <t>vincere</t>
+          <t>batti</t>
+        </is>
+      </c>
+      <c r="F118" t="inlineStr">
+        <is>
+          <t>Dabura</t>
         </is>
       </c>
       <c r="J118" t="inlineStr">
@@ -4452,29 +4582,24 @@
       </c>
       <c r="P118" t="inlineStr">
         <is>
-          <t>Il signor Goku mi ha detto di allenarmi. | Battimi e vengo con te!</t>
+          <t>Dabura ha pietrificato Piccolo e Krilin. | Batti {obiettivo} e combatterò al tuo fianco.</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>Uub</t>
+          <t>Son Gohan (Ultimate)</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>vai da</t>
+          <t>batti</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Son Goku (fine)</t>
-        </is>
-      </c>
-      <c r="G119" t="inlineStr">
-        <is>
-          <t>sì</t>
+          <t>Super Buu</t>
         </is>
       </c>
       <c r="J119" t="inlineStr">
@@ -4490,24 +4615,19 @@
       </c>
       <c r="P119" t="inlineStr">
         <is>
-          <t>Il signor Goku ha promesso di allenarmi. | Vai da {obiettivo} e torna: poi partiamo insieme.</t>
+          <t>Il Vecchio Kaioshin ha risvegliato tutto il mio potere. | Batti {obiettivo} e verrò con te.</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>Pan</t>
+          <t>Great Saiyaman</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>porta</t>
-        </is>
-      </c>
-      <c r="F120" t="inlineStr">
-        <is>
-          <t>Son Goku (GT)</t>
+          <t>quiz</t>
         </is>
       </c>
       <c r="J120" t="inlineStr">
@@ -4523,29 +4643,19 @@
       </c>
       <c r="P120" t="inlineStr">
         <is>
-          <t>Nonno Goku viene con noi? | Portami {obiettivo} e partiamo!</t>
+          <t>La giustizia trionfa sempre! Io sono Great Saiyaman! | Rispondi giusto e combatterò al tuo fianco.</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>Son Goku (GT)</t>
+          <t>Great Saiyaman 2-go</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>vai da</t>
-        </is>
-      </c>
-      <c r="F121" t="inlineStr">
-        <is>
-          <t>Trunks</t>
-        </is>
-      </c>
-      <c r="G121" t="inlineStr">
-        <is>
-          <t>sì</t>
+          <t>quiz</t>
         </is>
       </c>
       <c r="J121" t="inlineStr">
@@ -4561,14 +4671,14 @@
       </c>
       <c r="P121" t="inlineStr">
         <is>
-          <t>Con le sfere nere sono tornato bambino! | Vai da {obiettivo} e torna: ci serve un'astronave.</t>
+          <t>Anch'io combatto per la giustizia! | Rispondi giusto e verrò con te.</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>Son Goku (GT) SSJ</t>
+          <t>Videl</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
@@ -4578,7 +4688,7 @@
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Baby Vegeta</t>
+          <t>Spopovitch</t>
         </is>
       </c>
       <c r="J122" t="inlineStr">
@@ -4594,24 +4704,29 @@
       </c>
       <c r="P122" t="inlineStr">
         <is>
-          <t>Baby ha preso il corpo di Vegeta. | Batti {obiettivo} e verrò con te.</t>
+          <t>Al torneo Spopovitch mi ha umiliata. | Batti {obiettivo} e verrò con te.</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>Son Goku (GT) SSJ3</t>
+          <t>Spopovitch</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>batti</t>
-        </is>
-      </c>
-      <c r="F123" t="inlineStr">
-        <is>
-          <t>Super Baby 2</t>
+          <t>combattimento</t>
+        </is>
+      </c>
+      <c r="C123" t="inlineStr">
+        <is>
+          <t>1v1</t>
+        </is>
+      </c>
+      <c r="D123" t="inlineStr">
+        <is>
+          <t>vincere</t>
         </is>
       </c>
       <c r="J123" t="inlineStr">
@@ -4627,14 +4742,14 @@
       </c>
       <c r="P123" t="inlineStr">
         <is>
-          <t>Baby controlla tutta la Terra. | Batti {obiettivo} e verrò con te.</t>
+          <t>Bobbidi mi ha dato un potere enorme! | Battimi e verrò con te.</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>Son Goku SSJ4</t>
+          <t>Kaioshin</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
@@ -4644,7 +4759,7 @@
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Baby Oozaru</t>
+          <t>Bobbidi</t>
         </is>
       </c>
       <c r="J124" t="inlineStr">
@@ -4660,24 +4775,24 @@
       </c>
       <c r="P124" t="inlineStr">
         <is>
-          <t>Ho riavuto la coda: ora sono Super Saiyan 4. | Batti {obiettivo} e verrò con te.</t>
+          <t>Bobbidi vuole risvegliare Majin Bu. | Batti {obiettivo} e verrò con te.</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>Vegeta SSJ4</t>
+          <t>Kibitoshin</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>porta</t>
+          <t>batti</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Son Goku SSJ4</t>
+          <t>Dabura</t>
         </is>
       </c>
       <c r="J125" t="inlineStr">
@@ -4693,24 +4808,24 @@
       </c>
       <c r="P125" t="inlineStr">
         <is>
-          <t>Bulma ha trovato il modo di farmi diventare Super Saiyan 4. | Portami {obiettivo}: è ora della fusione.</t>
+          <t>Dabura serve Bobbidi: va fermato. | Batti {obiettivo} e ti aiuterò.</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>Gogeta SSJ4</t>
+          <t>Majin Buu (buono)</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>batti</t>
+          <t>porta</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Super Ii Shenron</t>
+          <t>Uub</t>
         </is>
       </c>
       <c r="J126" t="inlineStr">
@@ -4726,24 +4841,24 @@
       </c>
       <c r="P126" t="inlineStr">
         <is>
-          <t>Il drago più forte è nato dalle sfere del drago. | Batti {obiettivo} e combatterò con te.</t>
+          <t>Bu sente che quel bambino, Uub, è come lui. | Portami {obiettivo} e Bu verrà con te.</t>
         </is>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>Super C-17</t>
+          <t>Super Buu</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>batti</t>
-        </is>
-      </c>
-      <c r="F127" t="inlineStr">
-        <is>
-          <t>Son Goku SSJ4</t>
+          <t>combattimento</t>
+        </is>
+      </c>
+      <c r="D127" t="inlineStr">
+        <is>
+          <t>trasformazione</t>
         </is>
       </c>
       <c r="J127" t="inlineStr">
@@ -4759,24 +4874,24 @@
       </c>
       <c r="P127" t="inlineStr">
         <is>
-          <t>Due C-17 in uno, e un solo bersaglio. | Batti {obiettivo} e verrò con te.</t>
+          <t>Buu ha fame... Buu assorbe! | Costringimi a trasformarmi e verrò con te.</t>
         </is>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>Super Uub</t>
+          <t>Super Buu (Gotenks assorbito)</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>batti</t>
-        </is>
-      </c>
-      <c r="F128" t="inlineStr">
-        <is>
-          <t>Super Baby 2</t>
+          <t>combattimento</t>
+        </is>
+      </c>
+      <c r="D128" t="inlineStr">
+        <is>
+          <t>trasformazione</t>
         </is>
       </c>
       <c r="J128" t="inlineStr">
@@ -4792,38 +4907,439 @@
       </c>
       <c r="P128" t="inlineStr">
         <is>
-          <t>Con Majin Bu dentro di me ho una forza nuova. | Batti {obiettivo} e verrò con te.</t>
+          <t>Gotenks è dentro di me, e voglio di più! | Costringimi a trasformarmi e verrò con te.</t>
         </is>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
+          <t>Vegetto</t>
+        </is>
+      </c>
+      <c r="B129" t="inlineStr">
+        <is>
+          <t>batti</t>
+        </is>
+      </c>
+      <c r="F129" t="inlineStr">
+        <is>
+          <t>Super Buu (Son Gohan assorbito)</t>
+        </is>
+      </c>
+      <c r="J129" t="inlineStr">
+        <is>
+          <t>sì</t>
+        </is>
+      </c>
+      <c r="L129" t="n">
+        <v>400</v>
+      </c>
+      <c r="O129" t="n">
+        <v>1</v>
+      </c>
+      <c r="P129" t="inlineStr">
+        <is>
+          <t>Io sono Vegetto: Goku e Vegeta in un solo guerriero. | Batti {obiettivo} e combatterò con te.</t>
+        </is>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" t="inlineStr">
+        <is>
+          <t>Uub</t>
+        </is>
+      </c>
+      <c r="B130" t="inlineStr">
+        <is>
+          <t>combattimento</t>
+        </is>
+      </c>
+      <c r="D130" t="inlineStr">
+        <is>
+          <t>vincere</t>
+        </is>
+      </c>
+      <c r="J130" t="inlineStr">
+        <is>
+          <t>sì</t>
+        </is>
+      </c>
+      <c r="L130" t="n">
+        <v>400</v>
+      </c>
+      <c r="O130" t="n">
+        <v>1</v>
+      </c>
+      <c r="P130" t="inlineStr">
+        <is>
+          <t>Il signor Goku mi ha detto di allenarmi. | Battimi e vengo con te!</t>
+        </is>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" t="inlineStr">
+        <is>
+          <t>Pan</t>
+        </is>
+      </c>
+      <c r="B131" t="inlineStr">
+        <is>
+          <t>porta</t>
+        </is>
+      </c>
+      <c r="F131" t="inlineStr">
+        <is>
+          <t>Son Goku (GT)</t>
+        </is>
+      </c>
+      <c r="J131" t="inlineStr">
+        <is>
+          <t>sì</t>
+        </is>
+      </c>
+      <c r="L131" t="n">
+        <v>400</v>
+      </c>
+      <c r="O131" t="n">
+        <v>1</v>
+      </c>
+      <c r="P131" t="inlineStr">
+        <is>
+          <t>Nonno Goku viene con noi? | Portami {obiettivo} e partiamo!</t>
+        </is>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" t="inlineStr">
+        <is>
+          <t>Son Goku (GT)</t>
+        </is>
+      </c>
+      <c r="B132" t="inlineStr">
+        <is>
+          <t>porta</t>
+        </is>
+      </c>
+      <c r="F132" t="inlineStr">
+        <is>
+          <t>Trunks</t>
+        </is>
+      </c>
+      <c r="J132" t="inlineStr">
+        <is>
+          <t>sì</t>
+        </is>
+      </c>
+      <c r="L132" t="n">
+        <v>400</v>
+      </c>
+      <c r="O132" t="n">
+        <v>1</v>
+      </c>
+      <c r="P132" t="inlineStr">
+        <is>
+          <t>Ci serve qualcuno che sappia pilotare l'astronave. | Portami {obiettivo} e verrò con te.</t>
+        </is>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" t="inlineStr">
+        <is>
+          <t>Son Goku (GT) SSJ</t>
+        </is>
+      </c>
+      <c r="B133" t="inlineStr">
+        <is>
+          <t>batti</t>
+        </is>
+      </c>
+      <c r="F133" t="inlineStr">
+        <is>
+          <t>Baby Vegeta</t>
+        </is>
+      </c>
+      <c r="J133" t="inlineStr">
+        <is>
+          <t>sì</t>
+        </is>
+      </c>
+      <c r="L133" t="n">
+        <v>400</v>
+      </c>
+      <c r="O133" t="n">
+        <v>1</v>
+      </c>
+      <c r="P133" t="inlineStr">
+        <is>
+          <t>Baby ha preso il corpo di Vegeta. | Batti {obiettivo} e verrò con te.</t>
+        </is>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" t="inlineStr">
+        <is>
+          <t>Son Goku (GT) SSJ3</t>
+        </is>
+      </c>
+      <c r="B134" t="inlineStr">
+        <is>
+          <t>batti</t>
+        </is>
+      </c>
+      <c r="F134" t="inlineStr">
+        <is>
+          <t>Super Baby 2</t>
+        </is>
+      </c>
+      <c r="J134" t="inlineStr">
+        <is>
+          <t>sì</t>
+        </is>
+      </c>
+      <c r="L134" t="n">
+        <v>400</v>
+      </c>
+      <c r="O134" t="n">
+        <v>1</v>
+      </c>
+      <c r="P134" t="inlineStr">
+        <is>
+          <t>Baby controlla tutta la Terra. | Batti {obiettivo} e verrò con te.</t>
+        </is>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" t="inlineStr">
+        <is>
+          <t>Son Goku SSJ4</t>
+        </is>
+      </c>
+      <c r="B135" t="inlineStr">
+        <is>
+          <t>batti</t>
+        </is>
+      </c>
+      <c r="F135" t="inlineStr">
+        <is>
+          <t>Baby Oozaru</t>
+        </is>
+      </c>
+      <c r="J135" t="inlineStr">
+        <is>
+          <t>sì</t>
+        </is>
+      </c>
+      <c r="L135" t="n">
+        <v>400</v>
+      </c>
+      <c r="O135" t="n">
+        <v>1</v>
+      </c>
+      <c r="P135" t="inlineStr">
+        <is>
+          <t>Ho riavuto la coda: ora sono Super Saiyan 4. | Batti {obiettivo} e verrò con te.</t>
+        </is>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" t="inlineStr">
+        <is>
+          <t>Vegeta SSJ4</t>
+        </is>
+      </c>
+      <c r="B136" t="inlineStr">
+        <is>
+          <t>porta</t>
+        </is>
+      </c>
+      <c r="F136" t="inlineStr">
+        <is>
+          <t>Son Goku SSJ4</t>
+        </is>
+      </c>
+      <c r="J136" t="inlineStr">
+        <is>
+          <t>sì</t>
+        </is>
+      </c>
+      <c r="L136" t="n">
+        <v>400</v>
+      </c>
+      <c r="O136" t="n">
+        <v>1</v>
+      </c>
+      <c r="P136" t="inlineStr">
+        <is>
+          <t>Bulma ha trovato il modo di farmi diventare Super Saiyan 4. | Portami {obiettivo}: è ora della fusione.</t>
+        </is>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" t="inlineStr">
+        <is>
+          <t>Gogeta SSJ4</t>
+        </is>
+      </c>
+      <c r="B137" t="inlineStr">
+        <is>
+          <t>batti</t>
+        </is>
+      </c>
+      <c r="F137" t="inlineStr">
+        <is>
+          <t>Super Ii Shenron</t>
+        </is>
+      </c>
+      <c r="J137" t="inlineStr">
+        <is>
+          <t>sì</t>
+        </is>
+      </c>
+      <c r="L137" t="n">
+        <v>400</v>
+      </c>
+      <c r="O137" t="n">
+        <v>1</v>
+      </c>
+      <c r="P137" t="inlineStr">
+        <is>
+          <t>Il drago più forte è nato dalle sfere del drago. | Batti {obiettivo} e combatterò con te.</t>
+        </is>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" t="inlineStr">
+        <is>
+          <t>Super C-17</t>
+        </is>
+      </c>
+      <c r="B138" t="inlineStr">
+        <is>
+          <t>combattimento</t>
+        </is>
+      </c>
+      <c r="C138" t="inlineStr">
+        <is>
+          <t>1v1</t>
+        </is>
+      </c>
+      <c r="D138" t="inlineStr">
+        <is>
+          <t>vincere</t>
+        </is>
+      </c>
+      <c r="J138" t="inlineStr">
+        <is>
+          <t>sì</t>
+        </is>
+      </c>
+      <c r="L138" t="n">
+        <v>400</v>
+      </c>
+      <c r="O138" t="n">
+        <v>1</v>
+      </c>
+      <c r="P138" t="inlineStr">
+        <is>
+          <t>Due C-17 in uno: nessuno può fermarmi. | Battimi e verrò con te.</t>
+        </is>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" t="inlineStr">
+        <is>
+          <t>Baby Vegeta</t>
+        </is>
+      </c>
+      <c r="B139" t="inlineStr">
+        <is>
+          <t>combattimento</t>
+        </is>
+      </c>
+      <c r="D139" t="inlineStr">
+        <is>
+          <t>trasformazione</t>
+        </is>
+      </c>
+      <c r="J139" t="inlineStr">
+        <is>
+          <t>sì</t>
+        </is>
+      </c>
+      <c r="L139" t="n">
+        <v>400</v>
+      </c>
+      <c r="O139" t="n">
+        <v>1</v>
+      </c>
+      <c r="P139" t="inlineStr">
+        <is>
+          <t>Mi vendicherò dei Saiyan! | Costringimi a trasformarmi e ti seguirò.</t>
+        </is>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" t="inlineStr">
+        <is>
+          <t>Super Uub</t>
+        </is>
+      </c>
+      <c r="B140" t="inlineStr">
+        <is>
+          <t>batti</t>
+        </is>
+      </c>
+      <c r="F140" t="inlineStr">
+        <is>
+          <t>Super Baby 2</t>
+        </is>
+      </c>
+      <c r="J140" t="inlineStr">
+        <is>
+          <t>sì</t>
+        </is>
+      </c>
+      <c r="L140" t="n">
+        <v>400</v>
+      </c>
+      <c r="O140" t="n">
+        <v>1</v>
+      </c>
+      <c r="P140" t="inlineStr">
+        <is>
+          <t>Con Majin Bu dentro di me ho una forza nuova. | Batti {obiettivo} e verrò con te.</t>
+        </is>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" t="inlineStr">
+        <is>
           <t>Ii Shenron</t>
         </is>
       </c>
-      <c r="B129" t="inlineStr">
-        <is>
-          <t>combattimento</t>
-        </is>
-      </c>
-      <c r="D129" t="inlineStr">
+      <c r="B141" t="inlineStr">
+        <is>
+          <t>combattimento</t>
+        </is>
+      </c>
+      <c r="D141" t="inlineStr">
         <is>
           <t>trasformazione</t>
         </is>
       </c>
-      <c r="J129" t="inlineStr">
-        <is>
-          <t>sì</t>
-        </is>
-      </c>
-      <c r="L129" t="n">
-        <v>400</v>
-      </c>
-      <c r="O129" t="n">
-        <v>1</v>
-      </c>
-      <c r="P129" t="inlineStr">
+      <c r="J141" t="inlineStr">
+        <is>
+          <t>sì</t>
+        </is>
+      </c>
+      <c r="L141" t="n">
+        <v>400</v>
+      </c>
+      <c r="O141" t="n">
+        <v>1</v>
+      </c>
+      <c r="P141" t="inlineStr">
         <is>
           <t>Dentro di me ci sono tutte e sette le sfere del drago. | Costringimi a usarle e verrò con te.</t>
         </is>

--- a/docs/missioni-bt3.xlsx
+++ b/docs/missioni-bt3.xlsx
@@ -419,7 +419,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P141"/>
+  <dimension ref="A1:P160"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -2298,7 +2298,7 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Zarbon (trasformato)</t>
+          <t>Zarbon</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -2308,7 +2308,7 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>1v1</t>
+          <t>2v2</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
@@ -2316,6 +2316,11 @@
           <t>vincere</t>
         </is>
       </c>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>Zarbon | Dodoria</t>
+        </is>
+      </c>
       <c r="J56" t="inlineStr">
         <is>
           <t>sì</t>
@@ -2324,19 +2329,24 @@
       <c r="L56" t="n">
         <v>400</v>
       </c>
+      <c r="N56" t="inlineStr">
+        <is>
+          <t>Freeza (prima forma)</t>
+        </is>
+      </c>
       <c r="O56" t="n">
         <v>1</v>
       </c>
       <c r="P56" t="inlineStr">
         <is>
-          <t>Ora vedrai il mio vero aspetto! | Battimi e verrò con te.</t>
+          <t>Il grande Freeza non riceve visite. | Battete me e Dodoria, e la strada per Freeza sarà aperta.</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Dodoria</t>
+          <t>Zarbon (trasformato)</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -2346,7 +2356,7 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>2v2</t>
+          <t>1v1</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
@@ -2354,11 +2364,6 @@
           <t>vincere</t>
         </is>
       </c>
-      <c r="E57" t="inlineStr">
-        <is>
-          <t>Dodoria | Zarbon</t>
-        </is>
-      </c>
       <c r="J57" t="inlineStr">
         <is>
           <t>sì</t>
@@ -2372,14 +2377,14 @@
       </c>
       <c r="P57" t="inlineStr">
         <is>
-          <t>Zarbon, questi qui li sistemo io! | Battete me e Zarbon, e vi seguirò.</t>
+          <t>Ora vedrai il mio vero aspetto! | Battimi e verrò con te.</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Ginyu</t>
+          <t>Dodoria</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -2399,7 +2404,7 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Recoome | Guldo</t>
+          <t>Dodoria | Zarbon</t>
         </is>
       </c>
       <c r="J58" t="inlineStr">
@@ -2415,14 +2420,14 @@
       </c>
       <c r="P58" t="inlineStr">
         <is>
-          <t>Squadra Ginyu, in posizione! | Battete Recoome e Guldo e sarò dei vostri.</t>
+          <t>Zarbon, questi qui li sistemo io! | Battete me e Zarbon, e vi seguirò.</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Recoome</t>
+          <t>Dodoria</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -2432,7 +2437,7 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>1v1</t>
+          <t>2v2</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
@@ -2440,6 +2445,11 @@
           <t>vincere</t>
         </is>
       </c>
+      <c r="E59" t="inlineStr">
+        <is>
+          <t>Dodoria | Zarbon</t>
+        </is>
+      </c>
       <c r="J59" t="inlineStr">
         <is>
           <t>sì</t>
@@ -2448,28 +2458,45 @@
       <c r="L59" t="n">
         <v>400</v>
       </c>
+      <c r="N59" t="inlineStr">
+        <is>
+          <t>Freeza (prima forma)</t>
+        </is>
+      </c>
       <c r="O59" t="n">
         <v>1</v>
       </c>
       <c r="P59" t="inlineStr">
         <is>
-          <t>Recoome Ultra Fighting Bomber! | Battimi e passo dalla tua parte.</t>
+          <t>Freeza mi ha mandato a sistemarvi! | Battete me e Zarbon, e la strada per Freeza sarà aperta.</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Guldo</t>
+          <t>Ginyu</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>salta turni</t>
-        </is>
-      </c>
-      <c r="H60" t="n">
-        <v>1</v>
+          <t>combattimento</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>2v2</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>vincere</t>
+        </is>
+      </c>
+      <c r="E60" t="inlineStr">
+        <is>
+          <t>Recoome | Guldo</t>
+        </is>
       </c>
       <c r="J60" t="inlineStr">
         <is>
@@ -2477,21 +2504,21 @@
         </is>
       </c>
       <c r="L60" t="n">
-        <v>900</v>
+        <v>400</v>
       </c>
       <c r="O60" t="n">
         <v>1</v>
       </c>
       <c r="P60" t="inlineStr">
         <is>
-          <t>Ho fermato il tempo! | Resta immobile per {n} turno, poi verrò con te.</t>
+          <t>Squadra Ginyu, in posizione! | Battete Recoome e Guldo e sarò dei vostri.</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Butter</t>
+          <t>Ginyu</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -2511,7 +2538,7 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Butter | Jeeth</t>
+          <t>Recoome | Guldo</t>
         </is>
       </c>
       <c r="J61" t="inlineStr">
@@ -2522,19 +2549,24 @@
       <c r="L61" t="n">
         <v>400</v>
       </c>
+      <c r="N61" t="inlineStr">
+        <is>
+          <t>Freeza (forma finale)</t>
+        </is>
+      </c>
       <c r="O61" t="n">
         <v>1</v>
       </c>
       <c r="P61" t="inlineStr">
         <is>
-          <t>Sono il guerriero più veloce dell'universo! | Battete me e Jeeth, e verrò con voi.</t>
+          <t>Il grande Freeza ci ha ordinato di fermarvi! | Battete Recoome e Guldo, e la strada per Freeza sarà aperta.</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Butter</t>
+          <t>Recoome</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -2544,7 +2576,7 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>2v2</t>
+          <t>1v1</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
@@ -2552,11 +2584,6 @@
           <t>vincere</t>
         </is>
       </c>
-      <c r="E62" t="inlineStr">
-        <is>
-          <t>Butter | Jeeth</t>
-        </is>
-      </c>
       <c r="J62" t="inlineStr">
         <is>
           <t>sì</t>
@@ -2565,45 +2592,28 @@
       <c r="L62" t="n">
         <v>400</v>
       </c>
-      <c r="N62" t="inlineStr">
-        <is>
-          <t>Freeza (forma finale)</t>
-        </is>
-      </c>
       <c r="O62" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="P62" t="inlineStr">
         <is>
-          <t>Il grande Freeza non vuole essere disturbato! | Battete me e Jeeth, e la strada per Freeza sarà aperta.</t>
+          <t>Recoome Ultra Fighting Bomber! | Battimi e passo dalla tua parte.</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Jeeth</t>
+          <t>Guldo</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>combattimento</t>
-        </is>
-      </c>
-      <c r="C63" t="inlineStr">
-        <is>
-          <t>2v2</t>
-        </is>
-      </c>
-      <c r="D63" t="inlineStr">
-        <is>
-          <t>vincere</t>
-        </is>
-      </c>
-      <c r="E63" t="inlineStr">
-        <is>
-          <t>Jeeth | Butter</t>
-        </is>
+          <t>salta turni</t>
+        </is>
+      </c>
+      <c r="H63" t="n">
+        <v>1</v>
       </c>
       <c r="J63" t="inlineStr">
         <is>
@@ -2611,21 +2621,21 @@
         </is>
       </c>
       <c r="L63" t="n">
-        <v>400</v>
+        <v>900</v>
       </c>
       <c r="O63" t="n">
         <v>1</v>
       </c>
       <c r="P63" t="inlineStr">
         <is>
-          <t>Io e Butter colpiamo sempre in coppia. | Battete tutti e due e verrò con voi.</t>
+          <t>Ho fermato il tempo! | Resta immobile per {n} turno, poi verrò con te.</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Freeza (seconda forma)</t>
+          <t>Butter</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -2633,9 +2643,19 @@
           <t>combattimento</t>
         </is>
       </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>2v2</t>
+        </is>
+      </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>trasformazione</t>
+          <t>vincere</t>
+        </is>
+      </c>
+      <c r="E64" t="inlineStr">
+        <is>
+          <t>Butter | Jeeth</t>
         </is>
       </c>
       <c r="J64" t="inlineStr">
@@ -2651,14 +2671,14 @@
       </c>
       <c r="P64" t="inlineStr">
         <is>
-          <t>La mia potenza supera il milione. | Costringimi a trasformarmi di nuovo e verrò con te.</t>
+          <t>Sono il guerriero più veloce dell'universo! | Battete me e Jeeth, e verrò con voi.</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Freeza (terza forma)</t>
+          <t>Butter</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -2666,9 +2686,19 @@
           <t>combattimento</t>
         </is>
       </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>2v2</t>
+        </is>
+      </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>trasformazione</t>
+          <t>vincere</t>
+        </is>
+      </c>
+      <c r="E65" t="inlineStr">
+        <is>
+          <t>Butter | Jeeth</t>
         </is>
       </c>
       <c r="J65" t="inlineStr">
@@ -2679,19 +2709,24 @@
       <c r="L65" t="n">
         <v>400</v>
       </c>
+      <c r="N65" t="inlineStr">
+        <is>
+          <t>Freeza (forma finale)</t>
+        </is>
+      </c>
       <c r="O65" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="P65" t="inlineStr">
         <is>
-          <t>Questa forma non piace a nessuno, nemmeno a me. | Costringimi alla forma finale e verrò con te.</t>
+          <t>Il grande Freeza non vuole essere disturbato! | Battete me e Jeeth, e la strada per Freeza sarà aperta.</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Freeza (forma finale)</t>
+          <t>Jeeth</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -2711,7 +2746,7 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Freeza (forma finale) | Re Cold</t>
+          <t>Jeeth | Butter</t>
         </is>
       </c>
       <c r="J66" t="inlineStr">
@@ -2727,24 +2762,34 @@
       </c>
       <c r="P66" t="inlineStr">
         <is>
-          <t>Papà, guarda come tratto questi insetti. | Battete me e mio padre, e vi servirò.</t>
+          <t>Io e Butter colpiamo sempre in coppia. | Battete tutti e due e verrò con voi.</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Trunks (spada)</t>
+          <t>Jeeth</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>porta</t>
-        </is>
-      </c>
-      <c r="F67" t="inlineStr">
-        <is>
-          <t>Son Goku (metà)</t>
+          <t>combattimento</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>2v2</t>
+        </is>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>vincere</t>
+        </is>
+      </c>
+      <c r="E67" t="inlineStr">
+        <is>
+          <t>Jeeth | Butter</t>
         </is>
       </c>
       <c r="J67" t="inlineStr">
@@ -2755,29 +2800,34 @@
       <c r="L67" t="n">
         <v>400</v>
       </c>
+      <c r="N67" t="inlineStr">
+        <is>
+          <t>Freeza (forma finale)</t>
+        </is>
+      </c>
       <c r="O67" t="n">
         <v>1</v>
       </c>
       <c r="P67" t="inlineStr">
         <is>
-          <t>Vengo dal futuro: devo parlare con Son Goku. | Portami {obiettivo} e verrò con te.</t>
+          <t>Il grande Freeza non vuole essere disturbato! | Battete me e Butter, e la strada per Freeza sarà aperta.</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Trunks (spada) SSJ</t>
+          <t>Freeza (seconda forma)</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>batti</t>
-        </is>
-      </c>
-      <c r="F68" t="inlineStr">
-        <is>
-          <t>Mecha Freeza</t>
+          <t>combattimento</t>
+        </is>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>trasformazione</t>
         </is>
       </c>
       <c r="J68" t="inlineStr">
@@ -2793,14 +2843,14 @@
       </c>
       <c r="P68" t="inlineStr">
         <is>
-          <t>Freeza è tornato, ricostruito come una macchina. | Batti {obiettivo} e la mia spada sarà tua.</t>
+          <t>La mia potenza supera il milione. | Costringimi a trasformarmi di nuovo e verrò con te.</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Mecha Freeza</t>
+          <t>Freeza (seconda forma)</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -2808,42 +2858,32 @@
           <t>combattimento</t>
         </is>
       </c>
-      <c r="C69" t="inlineStr">
-        <is>
-          <t>2v2</t>
-        </is>
-      </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>vincere</t>
-        </is>
-      </c>
-      <c r="E69" t="inlineStr">
-        <is>
-          <t>Mecha Freeza | Re Cold</t>
-        </is>
-      </c>
-      <c r="J69" t="inlineStr">
-        <is>
-          <t>sì</t>
+          <t>trasformazione</t>
         </is>
       </c>
       <c r="L69" t="n">
-        <v>400</v>
+        <v>1200</v>
+      </c>
+      <c r="N69" t="inlineStr">
+        <is>
+          <t>Freeza (forma finale)</t>
+        </is>
       </c>
       <c r="O69" t="n">
         <v>1</v>
       </c>
       <c r="P69" t="inlineStr">
         <is>
-          <t>Mio padre mi ha ricostruito: ora voglio vendetta. | Battete me e mio padre, e vi seguirò.</t>
+          <t>Questa è solo la mia seconda forma. | Costringimi a trasformarmi: ti lascerò passare e avrai {monete} monete.</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Re Cold</t>
+          <t>Freeza (terza forma)</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -2851,19 +2891,9 @@
           <t>combattimento</t>
         </is>
       </c>
-      <c r="C70" t="inlineStr">
-        <is>
-          <t>2v2</t>
-        </is>
-      </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>vincere</t>
-        </is>
-      </c>
-      <c r="E70" t="inlineStr">
-        <is>
-          <t>Re Cold | Mecha Freeza</t>
+          <t>trasformazione</t>
         </is>
       </c>
       <c r="J70" t="inlineStr">
@@ -2879,57 +2909,67 @@
       </c>
       <c r="P70" t="inlineStr">
         <is>
-          <t>Mio figlio è tornato più forte di prima. | Battete me e Freeza, e vi seguirò.</t>
+          <t>Questa forma non piace a nessuno, nemmeno a me. | Costringimi alla forma finale e verrò con te.</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Trunks</t>
+          <t>Freeza (terza forma)</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>porta</t>
-        </is>
-      </c>
-      <c r="F71" t="inlineStr">
-        <is>
-          <t>Vegeta</t>
-        </is>
-      </c>
-      <c r="J71" t="inlineStr">
-        <is>
-          <t>sì</t>
+          <t>combattimento</t>
+        </is>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>trasformazione</t>
         </is>
       </c>
       <c r="L71" t="n">
-        <v>400</v>
+        <v>1200</v>
+      </c>
+      <c r="N71" t="inlineStr">
+        <is>
+          <t>Freeza (forma finale)</t>
+        </is>
       </c>
       <c r="O71" t="n">
         <v>1</v>
       </c>
       <c r="P71" t="inlineStr">
         <is>
-          <t>Nel mio futuro non ho mai conosciuto mio padre. | Portami {obiettivo} e verrò con te.</t>
+          <t>Ancora una trasformazione, e sarà la fine per voi. | Costringimi a trasformarmi: ti lascerò passare e avrai {monete} monete.</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Trunks SSJ</t>
+          <t>Freeza (forma finale)</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>batti</t>
-        </is>
-      </c>
-      <c r="F72" t="inlineStr">
-        <is>
-          <t>Cell (prima forma)</t>
+          <t>combattimento</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>2v2</t>
+        </is>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>vincere</t>
+        </is>
+      </c>
+      <c r="E72" t="inlineStr">
+        <is>
+          <t>Freeza (forma finale) | Re Cold</t>
         </is>
       </c>
       <c r="J72" t="inlineStr">
@@ -2945,24 +2985,24 @@
       </c>
       <c r="P72" t="inlineStr">
         <is>
-          <t>Cell viene dal mio futuro: là ha già vinto. | Batti {obiettivo} prima che diventi perfetto, e verrò con te.</t>
+          <t>Papà, guarda come tratto questi insetti. | Battete me e mio padre, e vi servirò.</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Super Trunks</t>
+          <t>Trunks (spada)</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>batti</t>
+          <t>porta</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Cell (forma perfetta)</t>
+          <t>Son Goku (metà)</t>
         </is>
       </c>
       <c r="J73" t="inlineStr">
@@ -2978,23 +3018,25 @@
       </c>
       <c r="P73" t="inlineStr">
         <is>
-          <t>Ho più muscoli di Cell, ma sono troppo lento. | Batti {obiettivo} e verrò con te.</t>
+          <t>Vengo dal futuro: devo parlare con Son Goku. | Portami {obiettivo} e verrò con te.</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Vegeta</t>
+          <t>Trunks (spada) SSJ</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>salta turni</t>
-        </is>
-      </c>
-      <c r="H74" t="n">
-        <v>1</v>
+          <t>batti</t>
+        </is>
+      </c>
+      <c r="F74" t="inlineStr">
+        <is>
+          <t>Mecha Freeza</t>
+        </is>
       </c>
       <c r="J74" t="inlineStr">
         <is>
@@ -3002,31 +3044,41 @@
         </is>
       </c>
       <c r="L74" t="n">
-        <v>900</v>
+        <v>400</v>
       </c>
       <c r="O74" t="n">
         <v>1</v>
       </c>
       <c r="P74" t="inlineStr">
         <is>
-          <t>Mi alleno nella stanza della gravità di Bulma. | Allenati con me per {n} turno e verrò con te.</t>
+          <t>Freeza è tornato, ricostruito come una macchina. | Batti {obiettivo} e la mia spada sarà tua.</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Vegeta SSJ</t>
+          <t>Mecha Freeza</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>batti</t>
-        </is>
-      </c>
-      <c r="F75" t="inlineStr">
-        <is>
-          <t>C-19</t>
+          <t>combattimento</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>2v2</t>
+        </is>
+      </c>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>vincere</t>
+        </is>
+      </c>
+      <c r="E75" t="inlineStr">
+        <is>
+          <t>Mecha Freeza | Re Cold</t>
         </is>
       </c>
       <c r="J75" t="inlineStr">
@@ -3042,24 +3094,34 @@
       </c>
       <c r="P75" t="inlineStr">
         <is>
-          <t>Sono diventato Super Saiyan anch'io. | Dimostrami che sei alla mia altezza: batti {obiettivo}.</t>
+          <t>Mio padre mi ha ricostruito: ora voglio vendetta. | Battete me e mio padre, e vi seguirò.</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>Super Vegeta</t>
+          <t>Re Cold</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>batti</t>
-        </is>
-      </c>
-      <c r="F76" t="inlineStr">
-        <is>
-          <t>Cell (forma perfetta)</t>
+          <t>combattimento</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>2v2</t>
+        </is>
+      </c>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>vincere</t>
+        </is>
+      </c>
+      <c r="E76" t="inlineStr">
+        <is>
+          <t>Re Cold | Mecha Freeza</t>
         </is>
       </c>
       <c r="J76" t="inlineStr">
@@ -3075,23 +3137,25 @@
       </c>
       <c r="P76" t="inlineStr">
         <is>
-          <t>Ho lasciato che Cell diventasse perfetto, per batterlo al suo meglio. | Batti {obiettivo} e verrò con te.</t>
+          <t>Mio figlio è tornato più forte di prima. | Battete me e Freeza, e vi seguirò.</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>Son Gohan (ragazzo)</t>
+          <t>Trunks</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>salta turni</t>
-        </is>
-      </c>
-      <c r="H77" t="n">
-        <v>1</v>
+          <t>porta</t>
+        </is>
+      </c>
+      <c r="F77" t="inlineStr">
+        <is>
+          <t>Vegeta</t>
+        </is>
       </c>
       <c r="J77" t="inlineStr">
         <is>
@@ -3099,21 +3163,21 @@
         </is>
       </c>
       <c r="L77" t="n">
-        <v>900</v>
+        <v>400</v>
       </c>
       <c r="O77" t="n">
         <v>1</v>
       </c>
       <c r="P77" t="inlineStr">
         <is>
-          <t>Papà mi allena nella Stanza dello Spirito e del Tempo. | Entra con noi per {n} turno e poi verrò con te.</t>
+          <t>Nel mio futuro non ho mai conosciuto mio padre. | Portami {obiettivo} e verrò con te.</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>Son Gohan (ragazzo) SSJ</t>
+          <t>Trunks SSJ</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -3123,7 +3187,7 @@
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Cell (forma perfetta)</t>
+          <t>Cell (prima forma)</t>
         </is>
       </c>
       <c r="J78" t="inlineStr">
@@ -3139,14 +3203,14 @@
       </c>
       <c r="P78" t="inlineStr">
         <is>
-          <t>I Cell Jr. non mi fanno paura. | Batti {obiettivo} e verrò con te.</t>
+          <t>Cell viene dal mio futuro: là ha già vinto. | Batti {obiettivo} prima che diventi perfetto, e verrò con te.</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>Son Gohan (ragazzo) SSJ2</t>
+          <t>Super Trunks</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -3172,25 +3236,23 @@
       </c>
       <c r="P79" t="inlineStr">
         <is>
-          <t>Papà dice che tocca a me. | Batti {obiettivo} e combatterò per te.</t>
+          <t>Ho più muscoli di Cell, ma sono troppo lento. | Batti {obiettivo} e verrò con te.</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>Piccolo (fine)</t>
+          <t>Vegeta</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>batti</t>
-        </is>
-      </c>
-      <c r="F80" t="inlineStr">
-        <is>
-          <t>C-17</t>
-        </is>
+          <t>salta turni</t>
+        </is>
+      </c>
+      <c r="H80" t="n">
+        <v>1</v>
       </c>
       <c r="J80" t="inlineStr">
         <is>
@@ -3198,41 +3260,31 @@
         </is>
       </c>
       <c r="L80" t="n">
-        <v>400</v>
+        <v>900</v>
       </c>
       <c r="O80" t="n">
         <v>1</v>
       </c>
       <c r="P80" t="inlineStr">
         <is>
-          <t>Mi sono fuso con Kami per affrontare i cyborg. | Batti {obiettivo} e combatterò al tuo fianco.</t>
+          <t>Mi alleno nella stanza della gravità di Bulma. | Allenati con me per {n} turno e verrò con te.</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>C-17</t>
+          <t>Vegeta SSJ</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>combattimento</t>
-        </is>
-      </c>
-      <c r="C81" t="inlineStr">
-        <is>
-          <t>2v2</t>
-        </is>
-      </c>
-      <c r="D81" t="inlineStr">
-        <is>
-          <t>vincere</t>
-        </is>
-      </c>
-      <c r="E81" t="inlineStr">
-        <is>
-          <t>C-17 | C-18</t>
+          <t>batti</t>
+        </is>
+      </c>
+      <c r="F81" t="inlineStr">
+        <is>
+          <t>C-19</t>
         </is>
       </c>
       <c r="J81" t="inlineStr">
@@ -3248,34 +3300,24 @@
       </c>
       <c r="P81" t="inlineStr">
         <is>
-          <t>Io e mia sorella non obbediamo a nessuno. | Battete me e C-18, e vi seguirò.</t>
+          <t>Sono diventato Super Saiyan anch'io. | Dimostrami che sei alla mia altezza: batti {obiettivo}.</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>C-17</t>
+          <t>Super Vegeta</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>combattimento</t>
-        </is>
-      </c>
-      <c r="C82" t="inlineStr">
-        <is>
-          <t>2v2</t>
-        </is>
-      </c>
-      <c r="D82" t="inlineStr">
-        <is>
-          <t>vincere</t>
-        </is>
-      </c>
-      <c r="E82" t="inlineStr">
-        <is>
-          <t>C-17 | C-18</t>
+          <t>batti</t>
+        </is>
+      </c>
+      <c r="F82" t="inlineStr">
+        <is>
+          <t>Cell (forma perfetta)</t>
         </is>
       </c>
       <c r="J82" t="inlineStr">
@@ -3286,45 +3328,28 @@
       <c r="L82" t="n">
         <v>400</v>
       </c>
-      <c r="N82" t="inlineStr">
-        <is>
-          <t>Cell (prima forma)</t>
-        </is>
-      </c>
       <c r="O82" t="n">
         <v>1</v>
       </c>
       <c r="P82" t="inlineStr">
         <is>
-          <t>Cell ci sta cercando, ma noi non abbiamo paura. | Battete me e C-18, e la strada per Cell sarà aperta.</t>
+          <t>Ho lasciato che Cell diventasse perfetto, per batterlo al suo meglio. | Batti {obiettivo} e verrò con te.</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>C-18</t>
+          <t>Son Gohan (ragazzo)</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>combattimento</t>
-        </is>
-      </c>
-      <c r="C83" t="inlineStr">
-        <is>
-          <t>2v2</t>
-        </is>
-      </c>
-      <c r="D83" t="inlineStr">
-        <is>
-          <t>vincere</t>
-        </is>
-      </c>
-      <c r="E83" t="inlineStr">
-        <is>
-          <t>C-18 | C-17</t>
-        </is>
+          <t>salta turni</t>
+        </is>
+      </c>
+      <c r="H83" t="n">
+        <v>1</v>
       </c>
       <c r="J83" t="inlineStr">
         <is>
@@ -3332,41 +3357,31 @@
         </is>
       </c>
       <c r="L83" t="n">
-        <v>400</v>
+        <v>900</v>
       </c>
       <c r="O83" t="n">
         <v>1</v>
       </c>
       <c r="P83" t="inlineStr">
         <is>
-          <t>Mio fratello e io ci annoiamo. | Battete tutti e due e verrò con voi.</t>
+          <t>Papà mi allena nella Stanza dello Spirito e del Tempo. | Entra con noi per {n} turno e poi verrò con te.</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>C-16</t>
+          <t>Son Gohan (ragazzo) SSJ</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>combattimento</t>
-        </is>
-      </c>
-      <c r="C84" t="inlineStr">
-        <is>
-          <t>3v3</t>
-        </is>
-      </c>
-      <c r="D84" t="inlineStr">
-        <is>
-          <t>vincere</t>
-        </is>
-      </c>
-      <c r="E84" t="inlineStr">
-        <is>
-          <t>C-16 | C-17 | C-18</t>
+          <t>batti</t>
+        </is>
+      </c>
+      <c r="F84" t="inlineStr">
+        <is>
+          <t>Cell (forma perfetta)</t>
         </is>
       </c>
       <c r="J84" t="inlineStr">
@@ -3382,34 +3397,24 @@
       </c>
       <c r="P84" t="inlineStr">
         <is>
-          <t>Non voglio combattere... ma C-17 e C-18 non mi lasciano scelta. | Battete tutti e tre e verrò con voi.</t>
+          <t>I Cell Jr. non mi fanno paura. | Batti {obiettivo} e verrò con te.</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>C-19</t>
+          <t>Son Gohan (ragazzo) SSJ2</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>combattimento</t>
-        </is>
-      </c>
-      <c r="C85" t="inlineStr">
-        <is>
-          <t>2v2</t>
-        </is>
-      </c>
-      <c r="D85" t="inlineStr">
-        <is>
-          <t>vincere</t>
-        </is>
-      </c>
-      <c r="E85" t="inlineStr">
-        <is>
-          <t>C-19 | Dr. Gero (C-20)</t>
+          <t>batti</t>
+        </is>
+      </c>
+      <c r="F85" t="inlineStr">
+        <is>
+          <t>Cell (forma perfetta)</t>
         </is>
       </c>
       <c r="J85" t="inlineStr">
@@ -3425,34 +3430,24 @@
       </c>
       <c r="P85" t="inlineStr">
         <is>
-          <t>Assorbirò la vostra energia. | Battete me e il dottor Gero, e vi seguirò.</t>
+          <t>Papà dice che tocca a me. | Batti {obiettivo} e combatterò per te.</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>Dr. Gero (C-20)</t>
+          <t>Piccolo (fine)</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>combattimento</t>
-        </is>
-      </c>
-      <c r="C86" t="inlineStr">
-        <is>
-          <t>2v2</t>
-        </is>
-      </c>
-      <c r="D86" t="inlineStr">
-        <is>
-          <t>vincere</t>
-        </is>
-      </c>
-      <c r="E86" t="inlineStr">
-        <is>
-          <t>Dr. Gero (C-20) | C-19</t>
+          <t>batti</t>
+        </is>
+      </c>
+      <c r="F86" t="inlineStr">
+        <is>
+          <t>C-17</t>
         </is>
       </c>
       <c r="J86" t="inlineStr">
@@ -3468,14 +3463,14 @@
       </c>
       <c r="P86" t="inlineStr">
         <is>
-          <t>Ho studiato Son Goku per anni. | Battete me e C-19, e lavorerò per voi.</t>
+          <t>Mi sono fuso con Kami per affrontare i cyborg. | Batti {obiettivo} e combatterò al tuo fianco.</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>Cell (seconda forma)</t>
+          <t>C-17</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -3483,9 +3478,19 @@
           <t>combattimento</t>
         </is>
       </c>
+      <c r="C87" t="inlineStr">
+        <is>
+          <t>2v2</t>
+        </is>
+      </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>trasformazione</t>
+          <t>vincere</t>
+        </is>
+      </c>
+      <c r="E87" t="inlineStr">
+        <is>
+          <t>C-17 | C-18</t>
         </is>
       </c>
       <c r="J87" t="inlineStr">
@@ -3501,14 +3506,14 @@
       </c>
       <c r="P87" t="inlineStr">
         <is>
-          <t>Ho assorbito C-17. Me ne manca solo una. | Costringimi a trasformarmi e verrò con te.</t>
+          <t>Io e mia sorella non obbediamo a nessuno. | Battete me e C-18, e vi seguirò.</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>Cell (forma perfetta)</t>
+          <t>C-17</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -3528,7 +3533,7 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>Cell (forma perfetta) | Cell Jr.</t>
+          <t>C-17 | C-18</t>
         </is>
       </c>
       <c r="J88" t="inlineStr">
@@ -3539,29 +3544,44 @@
       <c r="L88" t="n">
         <v>400</v>
       </c>
+      <c r="N88" t="inlineStr">
+        <is>
+          <t>Cell (prima forma)</t>
+        </is>
+      </c>
       <c r="O88" t="n">
         <v>1</v>
       </c>
       <c r="P88" t="inlineStr">
         <is>
-          <t>Ti presento mio figlio. | Battete noi due, e verrò con voi.</t>
+          <t>Cell ci sta cercando, ma noi non abbiamo paura. | Battete me e C-18, e la strada per Cell sarà aperta.</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>Son Gohan (futuro)</t>
+          <t>C-18</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>porta</t>
-        </is>
-      </c>
-      <c r="F89" t="inlineStr">
-        <is>
-          <t>Trunks (spada)</t>
+          <t>combattimento</t>
+        </is>
+      </c>
+      <c r="C89" t="inlineStr">
+        <is>
+          <t>2v2</t>
+        </is>
+      </c>
+      <c r="D89" t="inlineStr">
+        <is>
+          <t>vincere</t>
+        </is>
+      </c>
+      <c r="E89" t="inlineStr">
+        <is>
+          <t>C-18 | C-17</t>
         </is>
       </c>
       <c r="J89" t="inlineStr">
@@ -3577,24 +3597,34 @@
       </c>
       <c r="P89" t="inlineStr">
         <is>
-          <t>Nel mio futuro i cyborg hanno distrutto tutto: mi resta solo Trunks. | Portami {obiettivo} e combatteremo insieme.</t>
+          <t>Mio fratello e io ci annoiamo. | Battete tutti e due e verrò con voi.</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>Son Gohan (futuro) SSJ</t>
+          <t>C-18</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>batti</t>
-        </is>
-      </c>
-      <c r="F90" t="inlineStr">
-        <is>
-          <t>C-18</t>
+          <t>combattimento</t>
+        </is>
+      </c>
+      <c r="C90" t="inlineStr">
+        <is>
+          <t>2v2</t>
+        </is>
+      </c>
+      <c r="D90" t="inlineStr">
+        <is>
+          <t>vincere</t>
+        </is>
+      </c>
+      <c r="E90" t="inlineStr">
+        <is>
+          <t>C-18 | C-17</t>
         </is>
       </c>
       <c r="J90" t="inlineStr">
@@ -3605,19 +3635,24 @@
       <c r="L90" t="n">
         <v>400</v>
       </c>
+      <c r="N90" t="inlineStr">
+        <is>
+          <t>Cell (prima forma)</t>
+        </is>
+      </c>
       <c r="O90" t="n">
         <v>1</v>
       </c>
       <c r="P90" t="inlineStr">
         <is>
-          <t>C-17 e C-18 seminano il terrore nel mio tempo. | Batti {obiettivo} e verrò con te.</t>
+          <t>Cell ci sta cercando, ma non ci prenderà. | Battete me e C-17, e la strada per Cell sarà aperta.</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>Cooler (forma finale)</t>
+          <t>C-16</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
@@ -3627,7 +3662,7 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>1v1</t>
+          <t>3v3</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
@@ -3635,6 +3670,11 @@
           <t>vincere</t>
         </is>
       </c>
+      <c r="E91" t="inlineStr">
+        <is>
+          <t>C-16 | C-17 | C-18</t>
+        </is>
+      </c>
       <c r="J91" t="inlineStr">
         <is>
           <t>sì</t>
@@ -3648,14 +3688,14 @@
       </c>
       <c r="P91" t="inlineStr">
         <is>
-          <t>Ora conoscerai la mia forma finale! | Battimi e verrò con te.</t>
+          <t>Non voglio combattere... ma C-17 e C-18 non mi lasciano scelta. | Battete tutti e tre e verrò con voi.</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>C-13</t>
+          <t>C-19</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
@@ -3663,9 +3703,19 @@
           <t>combattimento</t>
         </is>
       </c>
+      <c r="C92" t="inlineStr">
+        <is>
+          <t>2v2</t>
+        </is>
+      </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>trasformazione</t>
+          <t>vincere</t>
+        </is>
+      </c>
+      <c r="E92" t="inlineStr">
+        <is>
+          <t>C-19 | Dr. Gero (C-20)</t>
         </is>
       </c>
       <c r="J92" t="inlineStr">
@@ -3681,14 +3731,14 @@
       </c>
       <c r="P92" t="inlineStr">
         <is>
-          <t>Il dottor Gero mi ha programmato per una cosa sola. | Costringimi a trasformarmi e ti seguirò.</t>
+          <t>Assorbirò la vostra energia. | Battete me e il dottor Gero, e vi seguirò.</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>Turles</t>
+          <t>Dr. Gero (C-20)</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
@@ -3696,9 +3746,19 @@
           <t>combattimento</t>
         </is>
       </c>
+      <c r="C93" t="inlineStr">
+        <is>
+          <t>2v2</t>
+        </is>
+      </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>trasformazione</t>
+          <t>vincere</t>
+        </is>
+      </c>
+      <c r="E93" t="inlineStr">
+        <is>
+          <t>Dr. Gero (C-20) | C-19</t>
         </is>
       </c>
       <c r="J93" t="inlineStr">
@@ -3714,14 +3774,14 @@
       </c>
       <c r="P93" t="inlineStr">
         <is>
-          <t>L'albero della potenza mi rende invincibile! | Costringimi a trasformarmi e ti seguirò.</t>
+          <t>Ho studiato Son Goku per anni. | Battete me e C-19, e lavorerò per voi.</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>Slug</t>
+          <t>Cell (seconda forma)</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
@@ -3747,14 +3807,14 @@
       </c>
       <c r="P94" t="inlineStr">
         <is>
-          <t>Il mio vero potere ha dimensioni enormi. | Costringimi a diventare gigante e verrò con te.</t>
+          <t>Ho assorbito C-17. Me ne manca solo una. | Costringimi a trasformarmi e verrò con te.</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>Broli</t>
+          <t>Cell (seconda forma)</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
@@ -3767,27 +3827,27 @@
           <t>trasformazione</t>
         </is>
       </c>
-      <c r="J95" t="inlineStr">
-        <is>
-          <t>sì</t>
-        </is>
-      </c>
       <c r="L95" t="n">
-        <v>400</v>
+        <v>1200</v>
+      </c>
+      <c r="N95" t="inlineStr">
+        <is>
+          <t>Cell (perfetto, massima potenza)</t>
+        </is>
       </c>
       <c r="O95" t="n">
         <v>1</v>
       </c>
       <c r="P95" t="inlineStr">
         <is>
-          <t>Kakaroth... KAKAROTH! | Se mi fai trasformare, ti seguirò.</t>
+          <t>Ho assorbito C-17: me ne manca solo una. | Costringimi a trasformarmi: la strada si aprirà e avrai {monete} monete.</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>Broli SSJ</t>
+          <t>Cell (forma perfetta)</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
@@ -3795,9 +3855,19 @@
           <t>combattimento</t>
         </is>
       </c>
+      <c r="C96" t="inlineStr">
+        <is>
+          <t>2v2</t>
+        </is>
+      </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>trasformazione</t>
+          <t>vincere</t>
+        </is>
+      </c>
+      <c r="E96" t="inlineStr">
+        <is>
+          <t>Cell (forma perfetta) | Cell Jr.</t>
         </is>
       </c>
       <c r="J96" t="inlineStr">
@@ -3813,14 +3883,14 @@
       </c>
       <c r="P96" t="inlineStr">
         <is>
-          <t>Kakaroth... KAKAROTH! | Costringimi a trasformarmi e verrò con te.</t>
+          <t>Ti presento mio figlio. | Battete noi due, e verrò con voi.</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>Zangya</t>
+          <t>Cell (forma perfetta)</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
@@ -3830,7 +3900,7 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>1v1</t>
+          <t>2v2</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
@@ -3838,47 +3908,42 @@
           <t>vincere</t>
         </is>
       </c>
-      <c r="J97" t="inlineStr">
-        <is>
-          <t>sì</t>
+      <c r="E97" t="inlineStr">
+        <is>
+          <t>Cell (forma perfetta) | Cell Jr.</t>
         </is>
       </c>
       <c r="L97" t="n">
-        <v>400</v>
+        <v>1200</v>
+      </c>
+      <c r="N97" t="inlineStr">
+        <is>
+          <t>Cell (perfetto, massima potenza)</t>
+        </is>
       </c>
       <c r="O97" t="n">
         <v>1</v>
       </c>
       <c r="P97" t="inlineStr">
         <is>
-          <t>Bojack ci ha liberati: ora la Terra è nostra. | Battimi e ti seguirò.</t>
+          <t>Ecco i miei figli, i Cell Jr.! | Battete me e il mio Cell Jr.: la strada si aprirà e avrete {monete} monete.</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>Bojack</t>
+          <t>Son Gohan (futuro)</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>combattimento</t>
-        </is>
-      </c>
-      <c r="C98" t="inlineStr">
-        <is>
-          <t>2v2</t>
-        </is>
-      </c>
-      <c r="D98" t="inlineStr">
-        <is>
-          <t>vincere</t>
-        </is>
-      </c>
-      <c r="E98" t="inlineStr">
-        <is>
-          <t>Bojack | Zangya</t>
+          <t>porta</t>
+        </is>
+      </c>
+      <c r="F98" t="inlineStr">
+        <is>
+          <t>Trunks (spada)</t>
         </is>
       </c>
       <c r="J98" t="inlineStr">
@@ -3894,52 +3959,47 @@
       </c>
       <c r="P98" t="inlineStr">
         <is>
-          <t>Il mio gruppo è libero, finalmente. | Battete me e Zangya, e verrò con voi.</t>
+          <t>Nel mio futuro i cyborg hanno distrutto tutto: mi resta solo Trunks. | Portami {obiettivo} e combatteremo insieme.</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>Bojack</t>
+          <t>Son Gohan (futuro) SSJ</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>combattimento</t>
-        </is>
-      </c>
-      <c r="C99" t="inlineStr">
-        <is>
-          <t>1v1</t>
-        </is>
-      </c>
-      <c r="D99" t="inlineStr">
-        <is>
-          <t>trasformazione</t>
+          <t>batti</t>
+        </is>
+      </c>
+      <c r="F99" t="inlineStr">
+        <is>
+          <t>C-18</t>
+        </is>
+      </c>
+      <c r="J99" t="inlineStr">
+        <is>
+          <t>sì</t>
         </is>
       </c>
       <c r="L99" t="n">
-        <v>1200</v>
-      </c>
-      <c r="N99" t="inlineStr">
-        <is>
-          <t>Bojack (massima potenza)</t>
-        </is>
+        <v>400</v>
       </c>
       <c r="O99" t="n">
         <v>1</v>
       </c>
       <c r="P99" t="inlineStr">
         <is>
-          <t>Il mio vero potere ti spazzerà via. | Costringimi a trasformarmi: ti lascerò passare e avrai {monete} monete.</t>
+          <t>C-17 e C-18 seminano il terrore nel mio tempo. | Batti {obiettivo} e verrò con te.</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>Bojack (massima potenza)</t>
+          <t>Cooler (forma finale)</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
@@ -3970,14 +4030,14 @@
       </c>
       <c r="P100" t="inlineStr">
         <is>
-          <t>Ora vedrai il mio vero potere! | Battimi e ti seguirò.</t>
+          <t>Ora conoscerai la mia forma finale! | Battimi e verrò con te.</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>Janemba</t>
+          <t>C-13</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
@@ -4003,14 +4063,14 @@
       </c>
       <c r="P101" t="inlineStr">
         <is>
-          <t>Il mondo dei morti è sottosopra per colpa mia! | Costringimi a trasformarmi e verrò con te.</t>
+          <t>Il dottor Gero mi ha programmato per una cosa sola. | Costringimi a trasformarmi e ti seguirò.</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>Janemba</t>
+          <t>C-13</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
@@ -4028,7 +4088,7 @@
       </c>
       <c r="N102" t="inlineStr">
         <is>
-          <t>Super Janemba</t>
+          <t>Super C-13</t>
         </is>
       </c>
       <c r="O102" t="n">
@@ -4036,24 +4096,24 @@
       </c>
       <c r="P102" t="inlineStr">
         <is>
-          <t>L'inferno si sta riversando sulla Terra... | Costringimi a trasformarmi: ti lascerò passare e avrai {monete} monete.</t>
+          <t>C-14 e C-15 mi hanno lasciato i loro chip. | Costringimi a trasformarmi: ti lascerò passare e avrai {monete} monete.</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>Paikuhan</t>
+          <t>Turles</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>batti</t>
-        </is>
-      </c>
-      <c r="F103" t="inlineStr">
-        <is>
-          <t>Janemba</t>
+          <t>combattimento</t>
+        </is>
+      </c>
+      <c r="D103" t="inlineStr">
+        <is>
+          <t>trasformazione</t>
         </is>
       </c>
       <c r="J103" t="inlineStr">
@@ -4069,24 +4129,24 @@
       </c>
       <c r="P103" t="inlineStr">
         <is>
-          <t>Nell'aldilà nessuno riesce a fermare Janemba. | Batti {obiettivo} e combatterò con te.</t>
+          <t>L'albero della potenza mi rende invincibile! | Costringimi a trasformarmi e ti seguirò.</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>Super Gogeta</t>
+          <t>Slug</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>batti</t>
-        </is>
-      </c>
-      <c r="F104" t="inlineStr">
-        <is>
-          <t>Super Janemba</t>
+          <t>combattimento</t>
+        </is>
+      </c>
+      <c r="D104" t="inlineStr">
+        <is>
+          <t>trasformazione</t>
         </is>
       </c>
       <c r="J104" t="inlineStr">
@@ -4102,47 +4162,47 @@
       </c>
       <c r="P104" t="inlineStr">
         <is>
-          <t>Goku e Vegeta, fusi per salvare l'aldilà. | Batti {obiettivo} e combatterò con te.</t>
+          <t>Il mio vero potere ha dimensioni enormi. | Costringimi a diventare gigante e verrò con te.</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>Tapion</t>
+          <t>Slug</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>batti</t>
-        </is>
-      </c>
-      <c r="F105" t="inlineStr">
-        <is>
-          <t>Hildegarn</t>
-        </is>
-      </c>
-      <c r="J105" t="inlineStr">
-        <is>
-          <t>sì</t>
+          <t>combattimento</t>
+        </is>
+      </c>
+      <c r="D105" t="inlineStr">
+        <is>
+          <t>trasformazione</t>
         </is>
       </c>
       <c r="L105" t="n">
-        <v>400</v>
+        <v>1200</v>
+      </c>
+      <c r="N105" t="inlineStr">
+        <is>
+          <t>Slug (gigante)</t>
+        </is>
       </c>
       <c r="O105" t="n">
         <v>1</v>
       </c>
       <c r="P105" t="inlineStr">
         <is>
-          <t>Il demone Hildegarn sta per risvegliarsi. | Batti {obiettivo} e il mio flauto suonerà per te.</t>
+          <t>La Terra sarà la mia nuova astronave. | Costringimi a trasformarmi: ti lascerò passare e avrai {monete} monete.</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>Tapion</t>
+          <t>Broli</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
@@ -4150,14 +4210,9 @@
           <t>combattimento</t>
         </is>
       </c>
-      <c r="C106" t="inlineStr">
-        <is>
-          <t>1v1</t>
-        </is>
-      </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>vincere</t>
+          <t>trasformazione</t>
         </is>
       </c>
       <c r="J106" t="inlineStr">
@@ -4168,24 +4223,19 @@
       <c r="L106" t="n">
         <v>400</v>
       </c>
-      <c r="N106" t="inlineStr">
-        <is>
-          <t>Hildegarn</t>
-        </is>
-      </c>
       <c r="O106" t="n">
         <v>1</v>
       </c>
       <c r="P106" t="inlineStr">
         <is>
-          <t>È troppo pericoloso: se non riuscite a battere me, non avete speranze con lui. | Battimi e ti lascerò passare.</t>
+          <t>Kakaroth... KAKAROTH! | Se mi fai trasformare, ti seguirò.</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>Hildegarn</t>
+          <t>Broli</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
@@ -4193,37 +4243,32 @@
           <t>combattimento</t>
         </is>
       </c>
-      <c r="C107" t="inlineStr">
-        <is>
-          <t>3v3</t>
-        </is>
-      </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>vincere</t>
-        </is>
-      </c>
-      <c r="J107" t="inlineStr">
-        <is>
-          <t>sì</t>
+          <t>trasformazione</t>
         </is>
       </c>
       <c r="L107" t="n">
-        <v>400</v>
+        <v>1200</v>
+      </c>
+      <c r="N107" t="inlineStr">
+        <is>
+          <t>Broli SSJ</t>
+        </is>
       </c>
       <c r="O107" t="n">
         <v>1</v>
       </c>
       <c r="P107" t="inlineStr">
         <is>
-          <t>GROOOAAAR! | Battilo con tre guerrieri e il demone sarà tuo.</t>
+          <t>Kakaroth... | Costringimi a trasformarmi: ti lascerò passare e avrai {monete} monete.</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>Arale</t>
+          <t>Broli SSJ</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
@@ -4233,7 +4278,7 @@
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>vincere</t>
+          <t>trasformazione</t>
         </is>
       </c>
       <c r="J108" t="inlineStr">
@@ -4249,57 +4294,62 @@
       </c>
       <c r="P108" t="inlineStr">
         <is>
-          <t>Ncha! Giochiamo a fare la lotta? | Battimi e vengo con te!</t>
+          <t>Kakaroth... KAKAROTH! | Costringimi a trasformarmi e verrò con te.</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>Son Goku (fine)</t>
+          <t>Broli SSJ</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>porta</t>
-        </is>
-      </c>
-      <c r="F109" t="inlineStr">
-        <is>
-          <t>Son Goten</t>
-        </is>
-      </c>
-      <c r="J109" t="inlineStr">
-        <is>
-          <t>sì</t>
+          <t>combattimento</t>
+        </is>
+      </c>
+      <c r="D109" t="inlineStr">
+        <is>
+          <t>trasformazione</t>
         </is>
       </c>
       <c r="L109" t="n">
-        <v>400</v>
+        <v>1200</v>
+      </c>
+      <c r="N109" t="inlineStr">
+        <is>
+          <t>Broli Super Saiyan Leggendario</t>
+        </is>
       </c>
       <c r="O109" t="n">
         <v>1</v>
       </c>
       <c r="P109" t="inlineStr">
         <is>
-          <t>Non ho ancora conosciuto il mio secondo figlio! | Portami {obiettivo} e verrò con te.</t>
+          <t>Il mio potere non ha limiti! | Costringimi a trasformarmi: ti lascerò passare e avrai {monete} monete.</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>Son Goku (fine) SSJ</t>
+          <t>Zangya</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>batti</t>
-        </is>
-      </c>
-      <c r="F110" t="inlineStr">
-        <is>
-          <t>Majin Vegeta</t>
+          <t>combattimento</t>
+        </is>
+      </c>
+      <c r="C110" t="inlineStr">
+        <is>
+          <t>1v1</t>
+        </is>
+      </c>
+      <c r="D110" t="inlineStr">
+        <is>
+          <t>vincere</t>
         </is>
       </c>
       <c r="J110" t="inlineStr">
@@ -4315,24 +4365,34 @@
       </c>
       <c r="P110" t="inlineStr">
         <is>
-          <t>Vegeta si è fatto controllare da Bobbidi pur di combattere con me. | Batti {obiettivo} e verrò con te.</t>
+          <t>Bojack ci ha liberati: ora la Terra è nostra. | Battimi e ti seguirò.</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>Son Goku (fine) SSJ3</t>
+          <t>Bojack</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>batti</t>
-        </is>
-      </c>
-      <c r="F111" t="inlineStr">
-        <is>
-          <t>Majin Buu (puro)</t>
+          <t>combattimento</t>
+        </is>
+      </c>
+      <c r="C111" t="inlineStr">
+        <is>
+          <t>2v2</t>
+        </is>
+      </c>
+      <c r="D111" t="inlineStr">
+        <is>
+          <t>vincere</t>
+        </is>
+      </c>
+      <c r="E111" t="inlineStr">
+        <is>
+          <t>Bojack | Zangya</t>
         </is>
       </c>
       <c r="J111" t="inlineStr">
@@ -4348,14 +4408,14 @@
       </c>
       <c r="P111" t="inlineStr">
         <is>
-          <t>Majin Bu è tornato alla sua forma originale: la più pericolosa. | Batti {obiettivo} e verrò con te.</t>
+          <t>Il mio gruppo è libero, finalmente. | Battete me e Zangya, e verrò con voi.</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>Majin Vegeta</t>
+          <t>Bojack</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
@@ -4370,40 +4430,45 @@
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>vincere</t>
-        </is>
-      </c>
-      <c r="J112" t="inlineStr">
-        <is>
-          <t>sì</t>
+          <t>trasformazione</t>
         </is>
       </c>
       <c r="L112" t="n">
-        <v>400</v>
+        <v>1200</v>
+      </c>
+      <c r="N112" t="inlineStr">
+        <is>
+          <t>Bojack (massima potenza)</t>
+        </is>
       </c>
       <c r="O112" t="n">
         <v>1</v>
       </c>
       <c r="P112" t="inlineStr">
         <is>
-          <t>Bobbidi mi ha dato ciò che volevo: il potere! | Battimi, se ci riesci, e verrò con te.</t>
+          <t>Il mio vero potere ti spazzerà via. | Costringimi a trasformarmi: ti lascerò passare e avrai {monete} monete.</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>Vegeta (seconda forma)</t>
+          <t>Bojack (massima potenza)</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>porta</t>
-        </is>
-      </c>
-      <c r="F113" t="inlineStr">
-        <is>
-          <t>Trunks (bambino)</t>
+          <t>combattimento</t>
+        </is>
+      </c>
+      <c r="C113" t="inlineStr">
+        <is>
+          <t>1v1</t>
+        </is>
+      </c>
+      <c r="D113" t="inlineStr">
+        <is>
+          <t>vincere</t>
         </is>
       </c>
       <c r="J113" t="inlineStr">
@@ -4419,23 +4484,25 @@
       </c>
       <c r="P113" t="inlineStr">
         <is>
-          <t>Trunks deve diventare più forte: lo alleno io. | Portami {obiettivo} e verrò con te.</t>
+          <t>Ora vedrai il mio vero potere! | Battimi e ti seguirò.</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>Trunks (bambino)</t>
+          <t>Janemba</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>attendi</t>
-        </is>
-      </c>
-      <c r="H114" t="n">
-        <v>2</v>
+          <t>combattimento</t>
+        </is>
+      </c>
+      <c r="D114" t="inlineStr">
+        <is>
+          <t>trasformazione</t>
+        </is>
       </c>
       <c r="J114" t="inlineStr">
         <is>
@@ -4443,64 +4510,64 @@
         </is>
       </c>
       <c r="L114" t="n">
-        <v>1400</v>
+        <v>400</v>
       </c>
       <c r="O114" t="n">
         <v>1</v>
       </c>
       <c r="P114" t="inlineStr">
         <is>
-          <t>Sto finendo l'allenamento nella stanza gravitazionale. | Ripassa tra {n} turni e verrò con te.</t>
+          <t>Il mondo dei morti è sottosopra per colpa mia! | Costringimi a trasformarmi e verrò con te.</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>Son Goten</t>
+          <t>Janemba</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>porta</t>
-        </is>
-      </c>
-      <c r="F115" t="inlineStr">
-        <is>
-          <t>Trunks (bambino)</t>
-        </is>
-      </c>
-      <c r="J115" t="inlineStr">
-        <is>
-          <t>sì</t>
+          <t>combattimento</t>
+        </is>
+      </c>
+      <c r="D115" t="inlineStr">
+        <is>
+          <t>trasformazione</t>
         </is>
       </c>
       <c r="L115" t="n">
-        <v>400</v>
+        <v>1200</v>
+      </c>
+      <c r="N115" t="inlineStr">
+        <is>
+          <t>Super Janemba</t>
+        </is>
       </c>
       <c r="O115" t="n">
         <v>1</v>
       </c>
       <c r="P115" t="inlineStr">
         <is>
-          <t>Senza Trunks non vengo da nessuna parte! | Portami {obiettivo} e veniamo tutti e due.</t>
+          <t>L'inferno si sta riversando sulla Terra... | Costringimi a trasformarmi: ti lascerò passare e avrai {monete} monete.</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>Son Goten SSJ</t>
+          <t>Paikuhan</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>porta</t>
+          <t>batti</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Trunks (bambino) SSJ</t>
+          <t>Janemba</t>
         </is>
       </c>
       <c r="J116" t="inlineStr">
@@ -4516,24 +4583,24 @@
       </c>
       <c r="P116" t="inlineStr">
         <is>
-          <t>Io e Trunks abbiamo imparato la danza della fusione! | Portami {obiettivo} e la proviamo subito.</t>
+          <t>Nell'aldilà nessuno riesce a fermare Janemba. | Batti {obiettivo} e combatterò con te.</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>Son Gohan</t>
+          <t>Super Gogeta</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>porta</t>
+          <t>batti</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Videl</t>
+          <t>Super Janemba</t>
         </is>
       </c>
       <c r="J117" t="inlineStr">
@@ -4549,14 +4616,14 @@
       </c>
       <c r="P117" t="inlineStr">
         <is>
-          <t>Videl vuole imparare a volare... | Portami {obiettivo} e verrò con te.</t>
+          <t>Goku e Vegeta, fusi per salvare l'aldilà. | Batti {obiettivo} e combatterò con te.</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>Son Gohan SSJ</t>
+          <t>Tapion</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
@@ -4566,7 +4633,7 @@
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Dabura</t>
+          <t>Hildegarn</t>
         </is>
       </c>
       <c r="J118" t="inlineStr">
@@ -4582,24 +4649,29 @@
       </c>
       <c r="P118" t="inlineStr">
         <is>
-          <t>Dabura ha pietrificato Piccolo e Krilin. | Batti {obiettivo} e combatterò al tuo fianco.</t>
+          <t>Il demone Hildegarn sta per risvegliarsi. | Batti {obiettivo} e il mio flauto suonerà per te.</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>Son Gohan (Ultimate)</t>
+          <t>Tapion</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>batti</t>
-        </is>
-      </c>
-      <c r="F119" t="inlineStr">
-        <is>
-          <t>Super Buu</t>
+          <t>combattimento</t>
+        </is>
+      </c>
+      <c r="C119" t="inlineStr">
+        <is>
+          <t>1v1</t>
+        </is>
+      </c>
+      <c r="D119" t="inlineStr">
+        <is>
+          <t>vincere</t>
         </is>
       </c>
       <c r="J119" t="inlineStr">
@@ -4610,24 +4682,39 @@
       <c r="L119" t="n">
         <v>400</v>
       </c>
+      <c r="N119" t="inlineStr">
+        <is>
+          <t>Hildegarn</t>
+        </is>
+      </c>
       <c r="O119" t="n">
         <v>1</v>
       </c>
       <c r="P119" t="inlineStr">
         <is>
-          <t>Il Vecchio Kaioshin ha risvegliato tutto il mio potere. | Batti {obiettivo} e verrò con te.</t>
+          <t>È troppo pericoloso: se non riuscite a battere me, non avete speranze con lui. | Battimi e ti lascerò passare.</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>Great Saiyaman</t>
+          <t>Hildegarn</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>quiz</t>
+          <t>combattimento</t>
+        </is>
+      </c>
+      <c r="C120" t="inlineStr">
+        <is>
+          <t>3v3</t>
+        </is>
+      </c>
+      <c r="D120" t="inlineStr">
+        <is>
+          <t>vincere</t>
         </is>
       </c>
       <c r="J120" t="inlineStr">
@@ -4643,19 +4730,24 @@
       </c>
       <c r="P120" t="inlineStr">
         <is>
-          <t>La giustizia trionfa sempre! Io sono Great Saiyaman! | Rispondi giusto e combatterò al tuo fianco.</t>
+          <t>GROOOAAAR! | Battilo con tre guerrieri e il demone sarà tuo.</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>Great Saiyaman 2-go</t>
+          <t>Arale</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>quiz</t>
+          <t>combattimento</t>
+        </is>
+      </c>
+      <c r="D121" t="inlineStr">
+        <is>
+          <t>vincere</t>
         </is>
       </c>
       <c r="J121" t="inlineStr">
@@ -4671,24 +4763,24 @@
       </c>
       <c r="P121" t="inlineStr">
         <is>
-          <t>Anch'io combatto per la giustizia! | Rispondi giusto e verrò con te.</t>
+          <t>Ncha! Giochiamo a fare la lotta? | Battimi e vengo con te!</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>Videl</t>
+          <t>Son Goku (fine)</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>batti</t>
+          <t>porta</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Spopovitch</t>
+          <t>Son Goten</t>
         </is>
       </c>
       <c r="J122" t="inlineStr">
@@ -4704,29 +4796,24 @@
       </c>
       <c r="P122" t="inlineStr">
         <is>
-          <t>Al torneo Spopovitch mi ha umiliata. | Batti {obiettivo} e verrò con te.</t>
+          <t>Non ho ancora conosciuto il mio secondo figlio! | Portami {obiettivo} e verrò con te.</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>Spopovitch</t>
+          <t>Son Goku (fine) SSJ</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>combattimento</t>
-        </is>
-      </c>
-      <c r="C123" t="inlineStr">
-        <is>
-          <t>1v1</t>
-        </is>
-      </c>
-      <c r="D123" t="inlineStr">
-        <is>
-          <t>vincere</t>
+          <t>batti</t>
+        </is>
+      </c>
+      <c r="F123" t="inlineStr">
+        <is>
+          <t>Majin Vegeta</t>
         </is>
       </c>
       <c r="J123" t="inlineStr">
@@ -4742,14 +4829,14 @@
       </c>
       <c r="P123" t="inlineStr">
         <is>
-          <t>Bobbidi mi ha dato un potere enorme! | Battimi e verrò con te.</t>
+          <t>Vegeta si è fatto controllare da Bobbidi pur di combattere con me. | Batti {obiettivo} e verrò con te.</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>Kaioshin</t>
+          <t>Son Goku (fine) SSJ3</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
@@ -4759,7 +4846,7 @@
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Bobbidi</t>
+          <t>Majin Buu (puro)</t>
         </is>
       </c>
       <c r="J124" t="inlineStr">
@@ -4775,24 +4862,29 @@
       </c>
       <c r="P124" t="inlineStr">
         <is>
-          <t>Bobbidi vuole risvegliare Majin Bu. | Batti {obiettivo} e verrò con te.</t>
+          <t>Majin Bu è tornato alla sua forma originale: la più pericolosa. | Batti {obiettivo} e verrò con te.</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>Kibitoshin</t>
+          <t>Majin Vegeta</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>batti</t>
-        </is>
-      </c>
-      <c r="F125" t="inlineStr">
-        <is>
-          <t>Dabura</t>
+          <t>combattimento</t>
+        </is>
+      </c>
+      <c r="C125" t="inlineStr">
+        <is>
+          <t>1v1</t>
+        </is>
+      </c>
+      <c r="D125" t="inlineStr">
+        <is>
+          <t>vincere</t>
         </is>
       </c>
       <c r="J125" t="inlineStr">
@@ -4808,14 +4900,14 @@
       </c>
       <c r="P125" t="inlineStr">
         <is>
-          <t>Dabura serve Bobbidi: va fermato. | Batti {obiettivo} e ti aiuterò.</t>
+          <t>Bobbidi mi ha dato ciò che volevo: il potere! | Battimi, se ci riesci, e verrò con te.</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>Majin Buu (buono)</t>
+          <t>Vegeta (seconda forma)</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
@@ -4825,7 +4917,7 @@
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Uub</t>
+          <t>Trunks (bambino)</t>
         </is>
       </c>
       <c r="J126" t="inlineStr">
@@ -4841,25 +4933,23 @@
       </c>
       <c r="P126" t="inlineStr">
         <is>
-          <t>Bu sente che quel bambino, Uub, è come lui. | Portami {obiettivo} e Bu verrà con te.</t>
+          <t>Trunks deve diventare più forte: lo alleno io. | Portami {obiettivo} e verrò con te.</t>
         </is>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>Super Buu</t>
+          <t>Trunks (bambino)</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>combattimento</t>
-        </is>
-      </c>
-      <c r="D127" t="inlineStr">
-        <is>
-          <t>trasformazione</t>
-        </is>
+          <t>attendi</t>
+        </is>
+      </c>
+      <c r="H127" t="n">
+        <v>2</v>
       </c>
       <c r="J127" t="inlineStr">
         <is>
@@ -4867,31 +4957,31 @@
         </is>
       </c>
       <c r="L127" t="n">
-        <v>400</v>
+        <v>1400</v>
       </c>
       <c r="O127" t="n">
         <v>1</v>
       </c>
       <c r="P127" t="inlineStr">
         <is>
-          <t>Buu ha fame... Buu assorbe! | Costringimi a trasformarmi e verrò con te.</t>
+          <t>Sto finendo l'allenamento nella stanza gravitazionale. | Ripassa tra {n} turni e verrò con te.</t>
         </is>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>Super Buu (Gotenks assorbito)</t>
+          <t>Son Goten</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>combattimento</t>
-        </is>
-      </c>
-      <c r="D128" t="inlineStr">
-        <is>
-          <t>trasformazione</t>
+          <t>porta</t>
+        </is>
+      </c>
+      <c r="F128" t="inlineStr">
+        <is>
+          <t>Trunks (bambino)</t>
         </is>
       </c>
       <c r="J128" t="inlineStr">
@@ -4907,24 +4997,24 @@
       </c>
       <c r="P128" t="inlineStr">
         <is>
-          <t>Gotenks è dentro di me, e voglio di più! | Costringimi a trasformarmi e verrò con te.</t>
+          <t>Senza Trunks non vengo da nessuna parte! | Portami {obiettivo} e veniamo tutti e due.</t>
         </is>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>Vegetto</t>
+          <t>Son Goten SSJ</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>batti</t>
+          <t>porta</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>Super Buu (Son Gohan assorbito)</t>
+          <t>Trunks (bambino) SSJ</t>
         </is>
       </c>
       <c r="J129" t="inlineStr">
@@ -4940,24 +5030,24 @@
       </c>
       <c r="P129" t="inlineStr">
         <is>
-          <t>Io sono Vegetto: Goku e Vegeta in un solo guerriero. | Batti {obiettivo} e combatterò con te.</t>
+          <t>Io e Trunks abbiamo imparato la danza della fusione! | Portami {obiettivo} e la proviamo subito.</t>
         </is>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>Uub</t>
+          <t>Son Gohan</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>combattimento</t>
-        </is>
-      </c>
-      <c r="D130" t="inlineStr">
-        <is>
-          <t>vincere</t>
+          <t>porta</t>
+        </is>
+      </c>
+      <c r="F130" t="inlineStr">
+        <is>
+          <t>Videl</t>
         </is>
       </c>
       <c r="J130" t="inlineStr">
@@ -4973,24 +5063,24 @@
       </c>
       <c r="P130" t="inlineStr">
         <is>
-          <t>Il signor Goku mi ha detto di allenarmi. | Battimi e vengo con te!</t>
+          <t>Videl vuole imparare a volare... | Portami {obiettivo} e verrò con te.</t>
         </is>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>Pan</t>
+          <t>Son Gohan SSJ</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>porta</t>
+          <t>batti</t>
         </is>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>Son Goku (GT)</t>
+          <t>Dabura</t>
         </is>
       </c>
       <c r="J131" t="inlineStr">
@@ -5006,24 +5096,24 @@
       </c>
       <c r="P131" t="inlineStr">
         <is>
-          <t>Nonno Goku viene con noi? | Portami {obiettivo} e partiamo!</t>
+          <t>Dabura ha pietrificato Piccolo e Krilin. | Batti {obiettivo} e combatterò al tuo fianco.</t>
         </is>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>Son Goku (GT)</t>
+          <t>Son Gohan (Ultimate)</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>porta</t>
+          <t>batti</t>
         </is>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>Trunks</t>
+          <t>Super Buu</t>
         </is>
       </c>
       <c r="J132" t="inlineStr">
@@ -5039,24 +5129,19 @@
       </c>
       <c r="P132" t="inlineStr">
         <is>
-          <t>Ci serve qualcuno che sappia pilotare l'astronave. | Portami {obiettivo} e verrò con te.</t>
+          <t>Il Vecchio Kaioshin ha risvegliato tutto il mio potere. | Batti {obiettivo} e verrò con te.</t>
         </is>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>Son Goku (GT) SSJ</t>
+          <t>Great Saiyaman</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>batti</t>
-        </is>
-      </c>
-      <c r="F133" t="inlineStr">
-        <is>
-          <t>Baby Vegeta</t>
+          <t>quiz</t>
         </is>
       </c>
       <c r="J133" t="inlineStr">
@@ -5072,24 +5157,19 @@
       </c>
       <c r="P133" t="inlineStr">
         <is>
-          <t>Baby ha preso il corpo di Vegeta. | Batti {obiettivo} e verrò con te.</t>
+          <t>La giustizia trionfa sempre! Io sono Great Saiyaman! | Rispondi giusto e combatterò al tuo fianco.</t>
         </is>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>Son Goku (GT) SSJ3</t>
+          <t>Great Saiyaman 2-go</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>batti</t>
-        </is>
-      </c>
-      <c r="F134" t="inlineStr">
-        <is>
-          <t>Super Baby 2</t>
+          <t>quiz</t>
         </is>
       </c>
       <c r="J134" t="inlineStr">
@@ -5105,14 +5185,14 @@
       </c>
       <c r="P134" t="inlineStr">
         <is>
-          <t>Baby controlla tutta la Terra. | Batti {obiettivo} e verrò con te.</t>
+          <t>Anch'io combatto per la giustizia! | Rispondi giusto e verrò con te.</t>
         </is>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>Son Goku SSJ4</t>
+          <t>Videl</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
@@ -5122,7 +5202,7 @@
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>Baby Oozaru</t>
+          <t>Spopovitch</t>
         </is>
       </c>
       <c r="J135" t="inlineStr">
@@ -5138,24 +5218,29 @@
       </c>
       <c r="P135" t="inlineStr">
         <is>
-          <t>Ho riavuto la coda: ora sono Super Saiyan 4. | Batti {obiettivo} e verrò con te.</t>
+          <t>Al torneo Spopovitch mi ha umiliata. | Batti {obiettivo} e verrò con te.</t>
         </is>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>Vegeta SSJ4</t>
+          <t>Spopovitch</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>porta</t>
-        </is>
-      </c>
-      <c r="F136" t="inlineStr">
-        <is>
-          <t>Son Goku SSJ4</t>
+          <t>combattimento</t>
+        </is>
+      </c>
+      <c r="C136" t="inlineStr">
+        <is>
+          <t>1v1</t>
+        </is>
+      </c>
+      <c r="D136" t="inlineStr">
+        <is>
+          <t>vincere</t>
         </is>
       </c>
       <c r="J136" t="inlineStr">
@@ -5171,14 +5256,14 @@
       </c>
       <c r="P136" t="inlineStr">
         <is>
-          <t>Bulma ha trovato il modo di farmi diventare Super Saiyan 4. | Portami {obiettivo}: è ora della fusione.</t>
+          <t>Bobbidi mi ha dato un potere enorme! | Battimi e verrò con te.</t>
         </is>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>Gogeta SSJ4</t>
+          <t>Kaioshin</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
@@ -5188,7 +5273,7 @@
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>Super Ii Shenron</t>
+          <t>Bobbidi</t>
         </is>
       </c>
       <c r="J137" t="inlineStr">
@@ -5204,29 +5289,24 @@
       </c>
       <c r="P137" t="inlineStr">
         <is>
-          <t>Il drago più forte è nato dalle sfere del drago. | Batti {obiettivo} e combatterò con te.</t>
+          <t>Bobbidi vuole risvegliare Majin Bu. | Batti {obiettivo} e verrò con te.</t>
         </is>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>Super C-17</t>
+          <t>Kibitoshin</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>combattimento</t>
-        </is>
-      </c>
-      <c r="C138" t="inlineStr">
-        <is>
-          <t>1v1</t>
-        </is>
-      </c>
-      <c r="D138" t="inlineStr">
-        <is>
-          <t>vincere</t>
+          <t>batti</t>
+        </is>
+      </c>
+      <c r="F138" t="inlineStr">
+        <is>
+          <t>Dabura</t>
         </is>
       </c>
       <c r="J138" t="inlineStr">
@@ -5242,24 +5322,24 @@
       </c>
       <c r="P138" t="inlineStr">
         <is>
-          <t>Due C-17 in uno: nessuno può fermarmi. | Battimi e verrò con te.</t>
+          <t>Dabura serve Bobbidi: va fermato. | Batti {obiettivo} e ti aiuterò.</t>
         </is>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>Baby Vegeta</t>
+          <t>Majin Buu (buono)</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>combattimento</t>
-        </is>
-      </c>
-      <c r="D139" t="inlineStr">
-        <is>
-          <t>trasformazione</t>
+          <t>porta</t>
+        </is>
+      </c>
+      <c r="F139" t="inlineStr">
+        <is>
+          <t>Uub</t>
         </is>
       </c>
       <c r="J139" t="inlineStr">
@@ -5275,24 +5355,29 @@
       </c>
       <c r="P139" t="inlineStr">
         <is>
-          <t>Mi vendicherò dei Saiyan! | Costringimi a trasformarmi e ti seguirò.</t>
+          <t>Bu sente che quel bambino, Uub, è come lui. | Portami {obiettivo} e Bu verrà con te.</t>
         </is>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>Super Uub</t>
+          <t>Majin Buu (puro male)</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>batti</t>
-        </is>
-      </c>
-      <c r="F140" t="inlineStr">
-        <is>
-          <t>Super Baby 2</t>
+          <t>combattimento</t>
+        </is>
+      </c>
+      <c r="C140" t="inlineStr">
+        <is>
+          <t>1v1</t>
+        </is>
+      </c>
+      <c r="D140" t="inlineStr">
+        <is>
+          <t>vincere</t>
         </is>
       </c>
       <c r="J140" t="inlineStr">
@@ -5303,45 +5388,692 @@
       <c r="L140" t="n">
         <v>400</v>
       </c>
+      <c r="N140" t="inlineStr">
+        <is>
+          <t>Super Buu</t>
+        </is>
+      </c>
       <c r="O140" t="n">
         <v>1</v>
       </c>
       <c r="P140" t="inlineStr">
         <is>
-          <t>Con Majin Bu dentro di me ho una forza nuova. | Batti {obiettivo} e verrò con te.</t>
+          <t>Il Bu cattivo è uscito... e vuole tutto. | Battimi e vedrai che cosa diventerò.</t>
         </is>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
+          <t>Super Buu</t>
+        </is>
+      </c>
+      <c r="B141" t="inlineStr">
+        <is>
+          <t>combattimento</t>
+        </is>
+      </c>
+      <c r="D141" t="inlineStr">
+        <is>
+          <t>trasformazione</t>
+        </is>
+      </c>
+      <c r="J141" t="inlineStr">
+        <is>
+          <t>sì</t>
+        </is>
+      </c>
+      <c r="L141" t="n">
+        <v>400</v>
+      </c>
+      <c r="O141" t="n">
+        <v>1</v>
+      </c>
+      <c r="P141" t="inlineStr">
+        <is>
+          <t>Buu ha fame... Buu assorbe! | Costringimi a trasformarmi e verrò con te.</t>
+        </is>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" t="inlineStr">
+        <is>
+          <t>Super Buu</t>
+        </is>
+      </c>
+      <c r="B142" t="inlineStr">
+        <is>
+          <t>combattimento</t>
+        </is>
+      </c>
+      <c r="D142" t="inlineStr">
+        <is>
+          <t>trasformazione</t>
+        </is>
+      </c>
+      <c r="L142" t="n">
+        <v>1200</v>
+      </c>
+      <c r="N142" t="inlineStr">
+        <is>
+          <t>Super Buu (Son Gohan assorbito)</t>
+        </is>
+      </c>
+      <c r="O142" t="n">
+        <v>1</v>
+      </c>
+      <c r="P142" t="inlineStr">
+        <is>
+          <t>Buu vuole assorbire qualcuno di forte... | Costringimi a trasformarmi: ti lascerò passare e avrai {monete} monete.</t>
+        </is>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" t="inlineStr">
+        <is>
+          <t>Super Buu (Gotenks assorbito)</t>
+        </is>
+      </c>
+      <c r="B143" t="inlineStr">
+        <is>
+          <t>combattimento</t>
+        </is>
+      </c>
+      <c r="D143" t="inlineStr">
+        <is>
+          <t>trasformazione</t>
+        </is>
+      </c>
+      <c r="J143" t="inlineStr">
+        <is>
+          <t>sì</t>
+        </is>
+      </c>
+      <c r="L143" t="n">
+        <v>400</v>
+      </c>
+      <c r="O143" t="n">
+        <v>1</v>
+      </c>
+      <c r="P143" t="inlineStr">
+        <is>
+          <t>Gotenks è dentro di me, e voglio di più! | Costringimi a trasformarmi e verrò con te.</t>
+        </is>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" t="inlineStr">
+        <is>
+          <t>Vegetto</t>
+        </is>
+      </c>
+      <c r="B144" t="inlineStr">
+        <is>
+          <t>batti</t>
+        </is>
+      </c>
+      <c r="F144" t="inlineStr">
+        <is>
+          <t>Super Buu (Son Gohan assorbito)</t>
+        </is>
+      </c>
+      <c r="J144" t="inlineStr">
+        <is>
+          <t>sì</t>
+        </is>
+      </c>
+      <c r="L144" t="n">
+        <v>400</v>
+      </c>
+      <c r="O144" t="n">
+        <v>1</v>
+      </c>
+      <c r="P144" t="inlineStr">
+        <is>
+          <t>Io sono Vegetto: Goku e Vegeta in un solo guerriero. | Batti {obiettivo} e combatterò con te.</t>
+        </is>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" t="inlineStr">
+        <is>
+          <t>Uub</t>
+        </is>
+      </c>
+      <c r="B145" t="inlineStr">
+        <is>
+          <t>combattimento</t>
+        </is>
+      </c>
+      <c r="D145" t="inlineStr">
+        <is>
+          <t>vincere</t>
+        </is>
+      </c>
+      <c r="J145" t="inlineStr">
+        <is>
+          <t>sì</t>
+        </is>
+      </c>
+      <c r="L145" t="n">
+        <v>400</v>
+      </c>
+      <c r="O145" t="n">
+        <v>1</v>
+      </c>
+      <c r="P145" t="inlineStr">
+        <is>
+          <t>Il signor Goku mi ha detto di allenarmi. | Battimi e vengo con te!</t>
+        </is>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" t="inlineStr">
+        <is>
+          <t>Pan</t>
+        </is>
+      </c>
+      <c r="B146" t="inlineStr">
+        <is>
+          <t>porta</t>
+        </is>
+      </c>
+      <c r="F146" t="inlineStr">
+        <is>
+          <t>Son Goku (GT)</t>
+        </is>
+      </c>
+      <c r="J146" t="inlineStr">
+        <is>
+          <t>sì</t>
+        </is>
+      </c>
+      <c r="L146" t="n">
+        <v>400</v>
+      </c>
+      <c r="O146" t="n">
+        <v>1</v>
+      </c>
+      <c r="P146" t="inlineStr">
+        <is>
+          <t>Nonno Goku viene con noi? | Portami {obiettivo} e partiamo!</t>
+        </is>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" t="inlineStr">
+        <is>
+          <t>Son Goku (GT)</t>
+        </is>
+      </c>
+      <c r="B147" t="inlineStr">
+        <is>
+          <t>porta</t>
+        </is>
+      </c>
+      <c r="F147" t="inlineStr">
+        <is>
+          <t>Trunks</t>
+        </is>
+      </c>
+      <c r="J147" t="inlineStr">
+        <is>
+          <t>sì</t>
+        </is>
+      </c>
+      <c r="L147" t="n">
+        <v>400</v>
+      </c>
+      <c r="O147" t="n">
+        <v>1</v>
+      </c>
+      <c r="P147" t="inlineStr">
+        <is>
+          <t>Ci serve qualcuno che sappia pilotare l'astronave. | Portami {obiettivo} e verrò con te.</t>
+        </is>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" t="inlineStr">
+        <is>
+          <t>Son Goku (GT) SSJ</t>
+        </is>
+      </c>
+      <c r="B148" t="inlineStr">
+        <is>
+          <t>batti</t>
+        </is>
+      </c>
+      <c r="F148" t="inlineStr">
+        <is>
+          <t>Baby Vegeta</t>
+        </is>
+      </c>
+      <c r="J148" t="inlineStr">
+        <is>
+          <t>sì</t>
+        </is>
+      </c>
+      <c r="L148" t="n">
+        <v>400</v>
+      </c>
+      <c r="O148" t="n">
+        <v>1</v>
+      </c>
+      <c r="P148" t="inlineStr">
+        <is>
+          <t>Baby ha preso il corpo di Vegeta. | Batti {obiettivo} e verrò con te.</t>
+        </is>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" t="inlineStr">
+        <is>
+          <t>Son Goku (GT) SSJ3</t>
+        </is>
+      </c>
+      <c r="B149" t="inlineStr">
+        <is>
+          <t>batti</t>
+        </is>
+      </c>
+      <c r="F149" t="inlineStr">
+        <is>
+          <t>Super Baby 2</t>
+        </is>
+      </c>
+      <c r="J149" t="inlineStr">
+        <is>
+          <t>sì</t>
+        </is>
+      </c>
+      <c r="L149" t="n">
+        <v>400</v>
+      </c>
+      <c r="O149" t="n">
+        <v>1</v>
+      </c>
+      <c r="P149" t="inlineStr">
+        <is>
+          <t>Baby controlla tutta la Terra. | Batti {obiettivo} e verrò con te.</t>
+        </is>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" t="inlineStr">
+        <is>
+          <t>Son Goku SSJ4</t>
+        </is>
+      </c>
+      <c r="B150" t="inlineStr">
+        <is>
+          <t>batti</t>
+        </is>
+      </c>
+      <c r="F150" t="inlineStr">
+        <is>
+          <t>Baby Oozaru</t>
+        </is>
+      </c>
+      <c r="J150" t="inlineStr">
+        <is>
+          <t>sì</t>
+        </is>
+      </c>
+      <c r="L150" t="n">
+        <v>400</v>
+      </c>
+      <c r="O150" t="n">
+        <v>1</v>
+      </c>
+      <c r="P150" t="inlineStr">
+        <is>
+          <t>Ho riavuto la coda: ora sono Super Saiyan 4. | Batti {obiettivo} e verrò con te.</t>
+        </is>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" t="inlineStr">
+        <is>
+          <t>Vegeta SSJ4</t>
+        </is>
+      </c>
+      <c r="B151" t="inlineStr">
+        <is>
+          <t>porta</t>
+        </is>
+      </c>
+      <c r="F151" t="inlineStr">
+        <is>
+          <t>Son Goku SSJ4</t>
+        </is>
+      </c>
+      <c r="J151" t="inlineStr">
+        <is>
+          <t>sì</t>
+        </is>
+      </c>
+      <c r="L151" t="n">
+        <v>400</v>
+      </c>
+      <c r="O151" t="n">
+        <v>1</v>
+      </c>
+      <c r="P151" t="inlineStr">
+        <is>
+          <t>Bulma ha trovato il modo di farmi diventare Super Saiyan 4. | Portami {obiettivo}: è ora della fusione.</t>
+        </is>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" t="inlineStr">
+        <is>
+          <t>Gogeta SSJ4</t>
+        </is>
+      </c>
+      <c r="B152" t="inlineStr">
+        <is>
+          <t>batti</t>
+        </is>
+      </c>
+      <c r="F152" t="inlineStr">
+        <is>
+          <t>Super Ii Shenron</t>
+        </is>
+      </c>
+      <c r="J152" t="inlineStr">
+        <is>
+          <t>sì</t>
+        </is>
+      </c>
+      <c r="L152" t="n">
+        <v>400</v>
+      </c>
+      <c r="O152" t="n">
+        <v>1</v>
+      </c>
+      <c r="P152" t="inlineStr">
+        <is>
+          <t>Il drago più forte è nato dalle sfere del drago. | Batti {obiettivo} e combatterò con te.</t>
+        </is>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" t="inlineStr">
+        <is>
+          <t>Super C-17</t>
+        </is>
+      </c>
+      <c r="B153" t="inlineStr">
+        <is>
+          <t>combattimento</t>
+        </is>
+      </c>
+      <c r="C153" t="inlineStr">
+        <is>
+          <t>1v1</t>
+        </is>
+      </c>
+      <c r="D153" t="inlineStr">
+        <is>
+          <t>vincere</t>
+        </is>
+      </c>
+      <c r="J153" t="inlineStr">
+        <is>
+          <t>sì</t>
+        </is>
+      </c>
+      <c r="L153" t="n">
+        <v>400</v>
+      </c>
+      <c r="O153" t="n">
+        <v>1</v>
+      </c>
+      <c r="P153" t="inlineStr">
+        <is>
+          <t>Due C-17 in uno: nessuno può fermarmi. | Battimi e verrò con te.</t>
+        </is>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" t="inlineStr">
+        <is>
+          <t>Baby Vegeta</t>
+        </is>
+      </c>
+      <c r="B154" t="inlineStr">
+        <is>
+          <t>combattimento</t>
+        </is>
+      </c>
+      <c r="D154" t="inlineStr">
+        <is>
+          <t>trasformazione</t>
+        </is>
+      </c>
+      <c r="J154" t="inlineStr">
+        <is>
+          <t>sì</t>
+        </is>
+      </c>
+      <c r="L154" t="n">
+        <v>400</v>
+      </c>
+      <c r="O154" t="n">
+        <v>1</v>
+      </c>
+      <c r="P154" t="inlineStr">
+        <is>
+          <t>Mi vendicherò dei Saiyan! | Costringimi a trasformarmi e ti seguirò.</t>
+        </is>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" t="inlineStr">
+        <is>
+          <t>Baby Vegeta</t>
+        </is>
+      </c>
+      <c r="B155" t="inlineStr">
+        <is>
+          <t>combattimento</t>
+        </is>
+      </c>
+      <c r="D155" t="inlineStr">
+        <is>
+          <t>trasformazione</t>
+        </is>
+      </c>
+      <c r="L155" t="n">
+        <v>1200</v>
+      </c>
+      <c r="N155" t="inlineStr">
+        <is>
+          <t>Super Baby 1</t>
+        </is>
+      </c>
+      <c r="O155" t="n">
+        <v>1</v>
+      </c>
+      <c r="P155" t="inlineStr">
+        <is>
+          <t>Il corpo di Vegeta è perfetto per me. | Costringimi a trasformarmi: ti lascerò passare e avrai {monete} monete.</t>
+        </is>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" t="inlineStr">
+        <is>
+          <t>Super Baby 2</t>
+        </is>
+      </c>
+      <c r="B156" t="inlineStr">
+        <is>
+          <t>combattimento</t>
+        </is>
+      </c>
+      <c r="D156" t="inlineStr">
+        <is>
+          <t>trasformazione</t>
+        </is>
+      </c>
+      <c r="L156" t="n">
+        <v>1200</v>
+      </c>
+      <c r="N156" t="inlineStr">
+        <is>
+          <t>Baby Oozaru</t>
+        </is>
+      </c>
+      <c r="O156" t="n">
+        <v>1</v>
+      </c>
+      <c r="P156" t="inlineStr">
+        <is>
+          <t>Con la luce Blutz diventerò inarrestabile! | Costringimi a trasformarmi: ti lascerò passare e avrai {monete} monete.</t>
+        </is>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" t="inlineStr">
+        <is>
+          <t>Super Uub</t>
+        </is>
+      </c>
+      <c r="B157" t="inlineStr">
+        <is>
+          <t>batti</t>
+        </is>
+      </c>
+      <c r="F157" t="inlineStr">
+        <is>
+          <t>Super Baby 2</t>
+        </is>
+      </c>
+      <c r="J157" t="inlineStr">
+        <is>
+          <t>sì</t>
+        </is>
+      </c>
+      <c r="L157" t="n">
+        <v>400</v>
+      </c>
+      <c r="O157" t="n">
+        <v>1</v>
+      </c>
+      <c r="P157" t="inlineStr">
+        <is>
+          <t>Con Majin Bu dentro di me ho una forza nuova. | Batti {obiettivo} e verrò con te.</t>
+        </is>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" t="inlineStr">
+        <is>
           <t>Ii Shenron</t>
         </is>
       </c>
-      <c r="B141" t="inlineStr">
-        <is>
-          <t>combattimento</t>
-        </is>
-      </c>
-      <c r="D141" t="inlineStr">
+      <c r="B158" t="inlineStr">
+        <is>
+          <t>combattimento</t>
+        </is>
+      </c>
+      <c r="D158" t="inlineStr">
         <is>
           <t>trasformazione</t>
         </is>
       </c>
-      <c r="J141" t="inlineStr">
-        <is>
-          <t>sì</t>
-        </is>
-      </c>
-      <c r="L141" t="n">
-        <v>400</v>
-      </c>
-      <c r="O141" t="n">
-        <v>1</v>
-      </c>
-      <c r="P141" t="inlineStr">
+      <c r="J158" t="inlineStr">
+        <is>
+          <t>sì</t>
+        </is>
+      </c>
+      <c r="L158" t="n">
+        <v>400</v>
+      </c>
+      <c r="O158" t="n">
+        <v>1</v>
+      </c>
+      <c r="P158" t="inlineStr">
         <is>
           <t>Dentro di me ci sono tutte e sette le sfere del drago. | Costringimi a usarle e verrò con te.</t>
+        </is>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" t="inlineStr">
+        <is>
+          <t>Ii Shenron</t>
+        </is>
+      </c>
+      <c r="B159" t="inlineStr">
+        <is>
+          <t>combattimento</t>
+        </is>
+      </c>
+      <c r="D159" t="inlineStr">
+        <is>
+          <t>trasformazione</t>
+        </is>
+      </c>
+      <c r="L159" t="n">
+        <v>1200</v>
+      </c>
+      <c r="N159" t="inlineStr">
+        <is>
+          <t>Super Ii Shenron</t>
+        </is>
+      </c>
+      <c r="O159" t="n">
+        <v>1</v>
+      </c>
+      <c r="P159" t="inlineStr">
+        <is>
+          <t>Le altre sfere nere stanno per diventare mie. | Costringimi a trasformarmi: ti lascerò passare e avrai {monete} monete.</t>
+        </is>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" t="inlineStr">
+        <is>
+          <t>Su Shenron</t>
+        </is>
+      </c>
+      <c r="B160" t="inlineStr">
+        <is>
+          <t>combattimento</t>
+        </is>
+      </c>
+      <c r="C160" t="inlineStr">
+        <is>
+          <t>1v1</t>
+        </is>
+      </c>
+      <c r="D160" t="inlineStr">
+        <is>
+          <t>vincere</t>
+        </is>
+      </c>
+      <c r="J160" t="inlineStr">
+        <is>
+          <t>sì</t>
+        </is>
+      </c>
+      <c r="L160" t="n">
+        <v>400</v>
+      </c>
+      <c r="N160" t="inlineStr">
+        <is>
+          <t>Ii Shenron</t>
+        </is>
+      </c>
+      <c r="O160" t="n">
+        <v>1</v>
+      </c>
+      <c r="P160" t="inlineStr">
+        <is>
+          <t>Sono il drago della sfera a quattro stelle. | Battimi e potrai affrontare il più forte dei draghi neri.</t>
         </is>
       </c>
     </row>

--- a/docs/missioni-bt3.xlsx
+++ b/docs/missioni-bt3.xlsx
@@ -10,7 +10,7 @@
     <sheet name="missioni" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'missioni'!$A$1:$P$129</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'missioni'!$A$1:$P$163</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -419,7 +419,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P160"/>
+  <dimension ref="A1:P163"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -6077,8 +6077,77 @@
         </is>
       </c>
     </row>
+    <row r="161">
+      <c r="A161" t="inlineStr">
+        <is>
+          <t>Livio</t>
+        </is>
+      </c>
+      <c r="B161" t="inlineStr">
+        <is>
+          <t>quiz</t>
+        </is>
+      </c>
+      <c r="L161" t="n">
+        <v>1500</v>
+      </c>
+      <c r="O161" t="n">
+        <v>1</v>
+      </c>
+      <c r="P161" t="inlineStr">
+        <is>
+          <t>Oggi mi sento istrionico: vediamo la tua fortuna. | Trova la mia vera Lisa e avrai {premio}.</t>
+        </is>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" t="inlineStr">
+        <is>
+          <t>Maggi</t>
+        </is>
+      </c>
+      <c r="B162" t="inlineStr">
+        <is>
+          <t>quiz</t>
+        </is>
+      </c>
+      <c r="L162" t="n">
+        <v>1500</v>
+      </c>
+      <c r="O162" t="n">
+        <v>1</v>
+      </c>
+      <c r="P162" t="inlineStr">
+        <is>
+          <t>Rispondi giusto e avrai {premio}.</t>
+        </is>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163" t="inlineStr">
+        <is>
+          <t>Meliador</t>
+        </is>
+      </c>
+      <c r="B163" t="inlineStr">
+        <is>
+          <t>quiz</t>
+        </is>
+      </c>
+      <c r="L163" t="n">
+        <v>1500</v>
+      </c>
+      <c r="O163" t="n">
+        <v>1</v>
+      </c>
+      <c r="P163" t="inlineStr">
+        <is>
+          <t>Rispondi giusto e avrai {premio}.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:P129"/>
+  <autoFilter ref="A1:P163"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/docs/missioni-bt3.xlsx
+++ b/docs/missioni-bt3.xlsx
@@ -1197,7 +1197,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Bobbidi</t>
+          <t>Babidi</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -4228,7 +4228,7 @@
       </c>
       <c r="P106" t="inlineStr">
         <is>
-          <t>Kakaroth... KAKAROTH! | Se mi fai trasformare, ti seguirò.</t>
+          <t>(Fissa il vuoto, senza dire una parola.) | Fallo trasformare e si unirà a te.</t>
         </is>
       </c>
     </row>
@@ -4261,7 +4261,7 @@
       </c>
       <c r="P107" t="inlineStr">
         <is>
-          <t>Kakaroth... | Costringimi a trasformarmi: ti lascerò passare e avrai {monete} monete.</t>
+          <t>(Il suo sguardo è perso nel vuoto.) | Costringilo a trasformarsi: ti lascerà passare e avrai {monete} monete.</t>
         </is>
       </c>
     </row>
@@ -4294,7 +4294,7 @@
       </c>
       <c r="P108" t="inlineStr">
         <is>
-          <t>Kakaroth... KAKAROTH! | Costringimi a trasformarmi e verrò con te.</t>
+          <t>(Non parla: immobile, guarda nel vuoto.) | Costringilo a trasformarsi e verrà con te.</t>
         </is>
       </c>
     </row>
@@ -4327,7 +4327,7 @@
       </c>
       <c r="P109" t="inlineStr">
         <is>
-          <t>Il mio potere non ha limiti! | Costringimi a trasformarmi: ti lascerò passare e avrai {monete} monete.</t>
+          <t>Kakaroth... KAKAROTH! | Costringilo a trasformarsi: ti lascerà passare e avrai {monete} monete.</t>
         </is>
       </c>
     </row>
@@ -4517,7 +4517,7 @@
       </c>
       <c r="P114" t="inlineStr">
         <is>
-          <t>Il mondo dei morti è sottosopra per colpa mia! | Costringimi a trasformarmi e verrò con te.</t>
+          <t>(Ghigna e fa un verso gutturale.) | Costringilo a trasformarsi e verrà con te.</t>
         </is>
       </c>
     </row>
@@ -4550,7 +4550,7 @@
       </c>
       <c r="P115" t="inlineStr">
         <is>
-          <t>L'inferno si sta riversando sulla Terra... | Costringimi a trasformarmi: ti lascerò passare e avrai {monete} monete.</t>
+          <t>(Un ruggito basso fa tremare l'aria.) | Costringilo a trasformarsi: ti lascerà passare e avrai {monete} monete.</t>
         </is>
       </c>
     </row>
@@ -4829,7 +4829,7 @@
       </c>
       <c r="P123" t="inlineStr">
         <is>
-          <t>Vegeta si è fatto controllare da Bobbidi pur di combattere con me. | Batti {obiettivo} e verrò con te.</t>
+          <t>Vegeta si è fatto controllare da Babidi pur di combattere con me. | Batti {obiettivo} e verrò con te.</t>
         </is>
       </c>
     </row>
@@ -4900,7 +4900,7 @@
       </c>
       <c r="P125" t="inlineStr">
         <is>
-          <t>Bobbidi mi ha dato ciò che volevo: il potere! | Battimi, se ci riesci, e verrò con te.</t>
+          <t>Babidi mi ha dato ciò che volevo: il potere! | Battimi, se ci riesci, e verrò con te.</t>
         </is>
       </c>
     </row>
@@ -5256,7 +5256,7 @@
       </c>
       <c r="P136" t="inlineStr">
         <is>
-          <t>Bobbidi mi ha dato un potere enorme! | Battimi e verrò con te.</t>
+          <t>Babidi mi ha dato un potere enorme! | Battimi e verrò con te.</t>
         </is>
       </c>
     </row>
@@ -5273,7 +5273,7 @@
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>Bobbidi</t>
+          <t>Babidi</t>
         </is>
       </c>
       <c r="J137" t="inlineStr">
@@ -5289,7 +5289,7 @@
       </c>
       <c r="P137" t="inlineStr">
         <is>
-          <t>Bobbidi vuole risvegliare Majin Bu. | Batti {obiettivo} e verrò con te.</t>
+          <t>Babidi vuole risvegliare Majin Bu. | Batti {obiettivo} e verrò con te.</t>
         </is>
       </c>
     </row>
@@ -5322,7 +5322,7 @@
       </c>
       <c r="P138" t="inlineStr">
         <is>
-          <t>Dabura serve Bobbidi: va fermato. | Batti {obiettivo} e ti aiuterò.</t>
+          <t>Dabura serve Babidi: va fermato. | Batti {obiettivo} e ti aiuterò.</t>
         </is>
       </c>
     </row>

--- a/docs/missioni-bt3.xlsx
+++ b/docs/missioni-bt3.xlsx
@@ -756,11 +756,11 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>attendi</t>
+          <t>ripassa</t>
         </is>
       </c>
       <c r="H9" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="J9" t="inlineStr">
         <is>
@@ -768,7 +768,7 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>1400</v>
+        <v>2400</v>
       </c>
       <c r="O9" t="n">
         <v>1</v>
@@ -818,14 +818,14 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>attendi</t>
+          <t>ripassa</t>
         </is>
       </c>
       <c r="H11" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="L11" t="n">
-        <v>1500</v>
+        <v>2500</v>
       </c>
       <c r="O11" t="n">
         <v>2</v>
@@ -893,11 +893,11 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>attendi</t>
+          <t>ripassa</t>
         </is>
       </c>
       <c r="H14" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="K14" t="inlineStr">
         <is>
@@ -905,7 +905,7 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>1500</v>
+        <v>2800</v>
       </c>
       <c r="O14" t="n">
         <v>2</v>
@@ -947,11 +947,11 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>attendi</t>
+          <t>ripassa</t>
         </is>
       </c>
       <c r="H16" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="K16" t="inlineStr">
         <is>
@@ -959,7 +959,7 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>1500</v>
+        <v>2800</v>
       </c>
       <c r="O16" t="n">
         <v>1</v>
@@ -4945,11 +4945,11 @@
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>attendi</t>
+          <t>ripassa</t>
         </is>
       </c>
       <c r="H127" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="J127" t="inlineStr">
         <is>
@@ -4957,7 +4957,7 @@
         </is>
       </c>
       <c r="L127" t="n">
-        <v>1400</v>
+        <v>2400</v>
       </c>
       <c r="O127" t="n">
         <v>1</v>
